--- a/stories/arbres/TREE-AUT-015.xlsx
+++ b/stories/arbres/TREE-AUT-015.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Jules est avec maman, près de la fenêtre. Jules a envie de jouer. maman est là, tout près. On va apprendre : Préparer son sac. Voici le geste : mettre dans le sac. Jules écoute maman. Jules entend les mots : sac, ce que l'adulte a dit.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Jules va vers le bac à sable. Le sol est un peu froid. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Jules se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On rit un peu. maman dit : je suis là. On reste ensemble.</t>
+          <t>Jules va vers le bac à sable. Le sol est un peu froid. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Jules se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On rit un peu. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1676,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Jules va vers le bac à sable. Le sol est un peu froid. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Jules se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On rit un peu.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1862,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Préparer son sac.</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2035,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : mettre dans le sac. Jules respire. Jules retient : sac, ce que l'adulte a dit. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2183,6 +2226,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2345,6 +2393,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi le ballon. L'eau coule, tout petit bruit. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Jules répète tout bas : sac, ce que l'adulte a dit. On range un objet. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2533,6 +2586,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2697,6 +2755,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Tom. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de le bac à sable, le ballon et Tom. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2859,6 +2922,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3021,6 +3089,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Léa. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de le bac à sable, le ballon et Léa. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3183,6 +3256,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3345,6 +3423,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Sami. Les chaussures font toc toc. On se tient la main. Cette fin-là est celle de le bac à sable, le ballon et Sami. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3507,6 +3590,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3669,6 +3757,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi le seau. Un vélo passe au loin. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Jules répète tout bas : sac, ce que l'adulte a dit. On dit merci. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3857,6 +3950,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -4021,6 +4119,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Tom. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de le bac à sable, le seau et Tom. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4183,6 +4286,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4345,6 +4453,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Léa. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de le bac à sable, le seau et Léa. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4507,6 +4620,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4669,6 +4787,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Sami. La couverture est douce. On se tient la main. Cette fin-là est celle de le bac à sable, le seau et Sami. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4831,6 +4954,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4993,6 +5121,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi le doudou. La lumière est claire. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Jules répète tout bas : sac, ce que l'adulte a dit. On souffle doucement. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5181,6 +5314,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -5345,6 +5483,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Tom. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de le bac à sable, le doudou et Tom. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5507,6 +5650,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5669,6 +5817,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Léa. La couverture est douce. On se tait une seconde. Cette fin-là est celle de le bac à sable, le doudou et Léa. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5831,6 +5984,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5993,6 +6151,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Sami. On entend un oiseau. On se tient la main. Cette fin-là est celle de le bac à sable, le doudou et Sami. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6155,6 +6318,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6179,7 +6347,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Jules va vers le toboggan. Une feuille tombe. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Jules se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On se tait une seconde. maman dit : je suis là. On reste ensemble.</t>
+          <t>Jules va vers le toboggan. Une feuille tombe. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Jules se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On se tait une seconde. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6317,6 +6485,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Jules va vers le toboggan. Une feuille tombe. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Jules se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On se tait une seconde.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6497,6 +6671,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Préparer son sac.</t>
         </is>
       </c>
     </row>
@@ -6665,6 +6844,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : mettre dans le sac. Jules respire. Jules retient : sac, ce que l'adulte a dit. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6851,6 +7035,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7013,6 +7202,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi le ballon. Il y a des miettes sur la table. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Jules répète tout bas : sac, ce que l'adulte a dit. On range un objet. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7201,6 +7395,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7365,6 +7564,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Tom. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de le toboggan, le ballon et Tom. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7527,6 +7731,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7689,6 +7898,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Léa. Les chaussures font toc toc. On se tient la main. Cette fin-là est celle de le toboggan, le ballon et Léa. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7851,6 +8065,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8013,6 +8232,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Sami. La couverture est douce. On range un objet. Cette fin-là est celle de le toboggan, le ballon et Sami. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8175,6 +8399,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8337,6 +8566,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi le seau. Un chat miaule une fois. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Jules répète tout bas : sac, ce que l'adulte a dit. On dit merci. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8525,6 +8759,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -8689,6 +8928,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Tom. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de le toboggan, le seau et Tom. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8851,6 +9095,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9013,6 +9262,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Léa. La couverture est douce. On se tient la main. Cette fin-là est celle de le toboggan, le seau et Léa. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9175,6 +9429,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9337,6 +9596,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Sami. On entend un oiseau. On range un objet. Cette fin-là est celle de le toboggan, le seau et Sami. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9499,6 +9763,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9661,6 +9930,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi le doudou. Les chaussures font toc toc. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Jules répète tout bas : sac, ce que l'adulte a dit. On souffle doucement. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9849,6 +10123,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -10013,6 +10292,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Tom. La couverture est douce. On se tait une seconde. Cette fin-là est celle de le toboggan, le doudou et Tom. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10175,6 +10459,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10337,6 +10626,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Léa. On entend un oiseau. On se tient la main. Cette fin-là est celle de le toboggan, le doudou et Léa. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10499,6 +10793,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10661,6 +10960,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Sami. Ça sent le pain chaud. On range un objet. Cette fin-là est celle de le toboggan, le doudou et Sami. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10823,6 +11127,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10847,7 +11156,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Jules va vers les balançoires. L'eau coule, tout petit bruit. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Jules se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On se tient la main. maman dit : je suis là. On reste ensemble.</t>
+          <t>Jules va vers les balançoires. L'eau coule, tout petit bruit. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Jules se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On se tient la main. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10985,6 +11294,12 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Jules va vers les balançoires. L'eau coule, tout petit bruit. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Jules se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On se tient la main.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11165,6 +11480,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Préparer son sac.</t>
         </is>
       </c>
     </row>
@@ -11333,6 +11653,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : mettre dans le sac. Jules respire. Jules retient : sac, ce que l'adulte a dit. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11519,6 +11844,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11681,6 +12011,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi le ballon. La couverture est douce. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Jules répète tout bas : sac, ce que l'adulte a dit. On range un objet. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11869,6 +12204,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -12033,6 +12373,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Tom. Les chaussures font toc toc. On se tient la main. Cette fin-là est celle de les balançoires, le ballon et Tom. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12195,6 +12540,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12357,6 +12707,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Léa. La couverture est douce. On range un objet. Cette fin-là est celle de les balançoires, le ballon et Léa. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12519,6 +12874,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12681,6 +13041,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Sami. On entend un oiseau. On dit merci. Cette fin-là est celle de les balançoires, le ballon et Sami. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12843,6 +13208,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13005,6 +13375,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi le seau. On entend un oiseau. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Jules répète tout bas : sac, ce que l'adulte a dit. On dit merci. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13193,6 +13568,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -13357,6 +13737,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Tom. La couverture est douce. On se tient la main. Cette fin-là est celle de les balançoires, le seau et Tom. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13519,6 +13904,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13681,6 +14071,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Léa. On entend un oiseau. On range un objet. Cette fin-là est celle de les balançoires, le seau et Léa. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13843,6 +14238,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14005,6 +14405,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Sami. Ça sent le pain chaud. On dit merci. Cette fin-là est celle de les balançoires, le seau et Sami. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14167,6 +14572,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14329,6 +14739,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi le doudou. Ça sent le pain chaud. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Jules répète tout bas : sac, ce que l'adulte a dit. On souffle doucement. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14517,6 +14932,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -14681,6 +15101,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Tom. On entend un oiseau. On se tient la main. Cette fin-là est celle de les balançoires, le doudou et Tom. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14843,6 +15268,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15005,6 +15435,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Léa. Ça sent le pain chaud. On range un objet. Cette fin-là est celle de les balançoires, le doudou et Léa. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15167,6 +15602,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15329,6 +15769,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Sami. Le vent est doux. On dit merci. Cette fin-là est celle de les balançoires, le doudou et Sami. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15491,6 +15936,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15509,7 +15959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15582,6 +16032,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-AUT-015.xlsx
+++ b/stories/arbres/TREE-AUT-015.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Jules est avec maman, près de la fenêtre. Jules a envie de jouer. maman est là, tout près. On va apprendre : Préparer son sac. Voici le geste : mettre dans le sac. Jules écoute maman. Jules entend les mots : sac, ce que l'adulte a dit.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1682,6 +1689,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1869,6 +1877,7 @@
           <t>narrateur|Que fait-on ? Préparer son sac.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2040,6 +2049,7 @@
           <t>narrateur|Oui. Voici le geste : mettre dans le sac. Jules respire. Jules retient : sac, ce que l'adulte a dit. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2231,6 +2241,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2398,6 +2409,7 @@
           <t>narrateur|Jules a choisi le ballon. L'eau coule, tout petit bruit. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Jules répète tout bas : sac, ce que l'adulte a dit. On range un objet. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2593,6 +2605,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2760,6 +2773,7 @@
           <t>narrateur|Jules rejoint Tom. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de le bac à sable, le ballon et Tom. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2927,6 +2941,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3094,6 +3109,7 @@
           <t>narrateur|Jules rejoint Léa. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de le bac à sable, le ballon et Léa. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3261,6 +3277,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3428,6 +3445,7 @@
           <t>narrateur|Jules rejoint Sami. Les chaussures font toc toc. On se tient la main. Cette fin-là est celle de le bac à sable, le ballon et Sami. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3595,6 +3613,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3762,6 +3781,7 @@
           <t>narrateur|Jules a choisi le seau. Un vélo passe au loin. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Jules répète tout bas : sac, ce que l'adulte a dit. On dit merci. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3957,6 +3977,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4124,6 +4145,7 @@
           <t>narrateur|Jules rejoint Tom. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de le bac à sable, le seau et Tom. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4291,6 +4313,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4458,6 +4481,7 @@
           <t>narrateur|Jules rejoint Léa. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de le bac à sable, le seau et Léa. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4625,6 +4649,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4792,6 +4817,7 @@
           <t>narrateur|Jules rejoint Sami. La couverture est douce. On se tient la main. Cette fin-là est celle de le bac à sable, le seau et Sami. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4959,6 +4985,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5126,6 +5153,7 @@
           <t>narrateur|Jules a choisi le doudou. La lumière est claire. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Jules répète tout bas : sac, ce que l'adulte a dit. On souffle doucement. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5321,6 +5349,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5488,6 +5517,7 @@
           <t>narrateur|Jules rejoint Tom. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de le bac à sable, le doudou et Tom. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5655,6 +5685,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5822,6 +5853,7 @@
           <t>narrateur|Jules rejoint Léa. La couverture est douce. On se tait une seconde. Cette fin-là est celle de le bac à sable, le doudou et Léa. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5989,6 +6021,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6156,6 +6189,7 @@
           <t>narrateur|Jules rejoint Sami. On entend un oiseau. On se tient la main. Cette fin-là est celle de le bac à sable, le doudou et Sami. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6323,6 +6357,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6491,6 +6526,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6678,6 +6714,7 @@
           <t>narrateur|Que fait-on ? Préparer son sac.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6849,6 +6886,7 @@
           <t>narrateur|Oui. Voici le geste : mettre dans le sac. Jules respire. Jules retient : sac, ce que l'adulte a dit. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7040,6 +7078,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7207,6 +7246,7 @@
           <t>narrateur|Jules a choisi le ballon. Il y a des miettes sur la table. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Jules répète tout bas : sac, ce que l'adulte a dit. On range un objet. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7402,6 +7442,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7569,6 +7610,7 @@
           <t>narrateur|Jules rejoint Tom. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de le toboggan, le ballon et Tom. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7736,6 +7778,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7903,6 +7946,7 @@
           <t>narrateur|Jules rejoint Léa. Les chaussures font toc toc. On se tient la main. Cette fin-là est celle de le toboggan, le ballon et Léa. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8070,6 +8114,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8237,6 +8282,7 @@
           <t>narrateur|Jules rejoint Sami. La couverture est douce. On range un objet. Cette fin-là est celle de le toboggan, le ballon et Sami. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8404,6 +8450,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8571,6 +8618,7 @@
           <t>narrateur|Jules a choisi le seau. Un chat miaule une fois. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Jules répète tout bas : sac, ce que l'adulte a dit. On dit merci. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8766,6 +8814,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8933,6 +8982,7 @@
           <t>narrateur|Jules rejoint Tom. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de le toboggan, le seau et Tom. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9100,6 +9150,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9267,6 +9318,7 @@
           <t>narrateur|Jules rejoint Léa. La couverture est douce. On se tient la main. Cette fin-là est celle de le toboggan, le seau et Léa. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9434,6 +9486,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9601,6 +9654,7 @@
           <t>narrateur|Jules rejoint Sami. On entend un oiseau. On range un objet. Cette fin-là est celle de le toboggan, le seau et Sami. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9768,6 +9822,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9935,6 +9990,7 @@
           <t>narrateur|Jules a choisi le doudou. Les chaussures font toc toc. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Jules répète tout bas : sac, ce que l'adulte a dit. On souffle doucement. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10130,6 +10186,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10297,6 +10354,7 @@
           <t>narrateur|Jules rejoint Tom. La couverture est douce. On se tait une seconde. Cette fin-là est celle de le toboggan, le doudou et Tom. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10464,6 +10522,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10631,6 +10690,7 @@
           <t>narrateur|Jules rejoint Léa. On entend un oiseau. On se tient la main. Cette fin-là est celle de le toboggan, le doudou et Léa. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10798,6 +10858,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10965,6 +11026,7 @@
           <t>narrateur|Jules rejoint Sami. Ça sent le pain chaud. On range un objet. Cette fin-là est celle de le toboggan, le doudou et Sami. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11132,6 +11194,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11300,6 +11363,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11487,6 +11551,7 @@
           <t>narrateur|Que fait-on ? Préparer son sac.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11658,6 +11723,7 @@
           <t>narrateur|Oui. Voici le geste : mettre dans le sac. Jules respire. Jules retient : sac, ce que l'adulte a dit. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11849,6 +11915,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12016,6 +12083,7 @@
           <t>narrateur|Jules a choisi le ballon. La couverture est douce. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Jules répète tout bas : sac, ce que l'adulte a dit. On range un objet. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12211,6 +12279,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12378,6 +12447,7 @@
           <t>narrateur|Jules rejoint Tom. Les chaussures font toc toc. On se tient la main. Cette fin-là est celle de les balançoires, le ballon et Tom. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12545,6 +12615,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12712,6 +12783,7 @@
           <t>narrateur|Jules rejoint Léa. La couverture est douce. On range un objet. Cette fin-là est celle de les balançoires, le ballon et Léa. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12879,6 +12951,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13046,6 +13119,7 @@
           <t>narrateur|Jules rejoint Sami. On entend un oiseau. On dit merci. Cette fin-là est celle de les balançoires, le ballon et Sami. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13213,6 +13287,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13380,6 +13455,7 @@
           <t>narrateur|Jules a choisi le seau. On entend un oiseau. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Jules répète tout bas : sac, ce que l'adulte a dit. On dit merci. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13575,6 +13651,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13742,6 +13819,7 @@
           <t>narrateur|Jules rejoint Tom. La couverture est douce. On se tient la main. Cette fin-là est celle de les balançoires, le seau et Tom. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13909,6 +13987,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14076,6 +14155,7 @@
           <t>narrateur|Jules rejoint Léa. On entend un oiseau. On range un objet. Cette fin-là est celle de les balançoires, le seau et Léa. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14243,6 +14323,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14410,6 +14491,7 @@
           <t>narrateur|Jules rejoint Sami. Ça sent le pain chaud. On dit merci. Cette fin-là est celle de les balançoires, le seau et Sami. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14577,6 +14659,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14744,6 +14827,7 @@
           <t>narrateur|Jules a choisi le doudou. Ça sent le pain chaud. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Jules répète tout bas : sac, ce que l'adulte a dit. On souffle doucement. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14939,6 +15023,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15106,6 +15191,7 @@
           <t>narrateur|Jules rejoint Tom. On entend un oiseau. On se tient la main. Cette fin-là est celle de les balançoires, le doudou et Tom. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15273,6 +15359,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15440,6 +15527,7 @@
           <t>narrateur|Jules rejoint Léa. Ça sent le pain chaud. On range un objet. Cette fin-là est celle de les balançoires, le doudou et Léa. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15607,6 +15695,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15774,6 +15863,7 @@
           <t>narrateur|Jules rejoint Sami. Le vent est doux. On dit merci. Cette fin-là est celle de les balançoires, le doudou et Sami. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15941,6 +16031,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15959,7 +16050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16039,6 +16130,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16053,7 +16158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16240,6 +16345,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-AUT-015.xlsx
+++ b/stories/arbres/TREE-AUT-015.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Préparer son sac — près de la fenêtre</t>
+          <t>Le sac de Nina près de la fenêtre</t>
         </is>
       </c>
     </row>
@@ -843,6 +843,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nina veut aller au parc. Près de la fenêtre embuée, elle prépare son sac bleu avec ce que maman a dit. Au parc, elle choisit un lieu, un jeu, puis une dernière chose à mettre dans le sac.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Aujourd'hui, Jules est avec maman, près de la fenêtre. Jules a envie de jouer. maman est là, tout près. On va apprendre : Préparer son sac. Voici le geste : mettre dans le sac. Jules écoute maman. Jules entend les mots : sac, ce que l'adulte a dit.</t>
+          <t>La vitre près de la cuisine est un peu embuée. Un moineau tapote le rebord mouillé. Le soleil revient sur le plancher de bois. Il dessine des carrés chauds, tout jaunes. Ça sent le cacao dans la petite casserole. Un sac bleu est ouvert sur la chaise. Les sangles pendent, molles et lisses. Les chaussettes rouges de Nina sèchent près du radiateur. Nina, la gourde est dans le placard. Je te la passe. On prépare le sac avant le parc. On met ce que j'ai dit. La gourde, le doudou, et le petit livre. En ce moment, Nina est près de la fenêtre. Maman et papa sont avec elle. Nina a envie d'aller au parc. Elle écoute maman jusqu'au bout. Elle prend la gourde bleue. Le plastique est frais sous ses doigts. Elle la met dans le sac. Ça fait un petit bruit de plastique. Elle prend le doudou, tout doux. Elle le met dans le sac. Elle prend le petit livre. Elle le met dans le sac, comme maman a dit. Nina appuie sur la fermeture. Ça fait zzz. Bravo, Nina. Tu as fait du bon travail. Tu as mis ce que l'adulte a dit ? Oui, maman. Le sac est prêt. Le sac est fermé. Il attend près de la fenêtre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,10 +1337,44 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Aujourd'hui, Jules est avec maman, près de la fenêtre. Jules a envie de jouer. maman est là, tout près. On va apprendre : Préparer son sac. Voici le geste : mettre dans le sac. Jules écoute maman. Jules entend les mots : sac, ce que l'adulte a dit.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|La vitre près de la cuisine est un peu embuée.
+narrateur|Un moineau tapote le rebord mouillé.
+narrateur|Le soleil revient sur le plancher de bois.
+narrateur|Il dessine des carrés chauds, tout jaunes.
+narrateur|Ça sent le cacao dans la petite casserole.
+narrateur|Un sac bleu est ouvert sur la chaise.
+narrateur|Les sangles pendent, molles et lisses.
+narrateur|Les chaussettes rouges de Nina sèchent près du radiateur.
+papa|Nina, la gourde est dans le placard.
+papa|Je te la passe.
+maman|On prépare le sac avant le parc.
+maman|On met ce que j'ai dit.
+maman|La gourde, le doudou, et le petit livre.
+narrateur|En ce moment, Nina est près de la fenêtre.
+narrateur|Maman et papa sont avec elle.
+narrateur|Nina a envie d'aller au parc.
+narrateur|Elle écoute maman jusqu'au bout.
+narrateur|Elle prend la gourde bleue.
+narrateur|Le plastique est frais sous ses doigts.
+narrateur|Elle la met dans le sac.
+narrateur|Ça fait un petit bruit de plastique.
+narrateur|Elle prend le doudou, tout doux.
+narrateur|Elle le met dans le sac.
+narrateur|Elle prend le petit livre.
+narrateur|Elle le met dans le sac, comme maman a dit.
+narrateur|Nina appuie sur la fermeture.
+narrateur|Ça fait zzz.
+papa|Bravo, Nina. Tu as fait du bon travail.
+maman|Tu as mis ce que l'adulte a dit ?
+enfant-f|Oui, maman. Le sac est prêt.
+narrateur|Le sac est fermé. Il attend près de la fenêtre.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1353,7 +1399,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+          <t>On va au parc. Où va-t-on d'abord ? On peut aller au bac à sable, au toboggan, ou aux balançoires.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1517,10 +1563,10 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>maman|On va au parc. Où va-t-on d'abord ?
+narrateur|On peut aller au bac à sable, au toboggan, ou aux balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1545,7 +1591,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Jules va vers le bac à sable. Le sol est un peu froid. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Jules se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On rit un peu. Je suis là. On reste ensemble.</t>
+          <t>Nina marche vers le bac à sable. Le sable est un peu froid, tout fin. Il glisse entre les doigts. Le bois du rebord sent le soleil. Le sac bleu est posé contre le rebord. On pose le sac ici, près de nous. Tu te souviens ? On met dans le sac ce que l'adulte a dit. Nina ouvre un peu le sac. Elle vérifie le doudou et le livre. Ils sont dans le sac. Bravo. Tu as écouté. Un oiseau chante tout près. Le vent soulève un peu de sable clair.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1685,11 +1731,26 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Jules va vers le bac à sable. Le sol est un peu froid. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Jules se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On rit un peu.
-maman|Je suis là. On reste ensemble.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Nina marche vers le bac à sable.
+narrateur|Le sable est un peu froid, tout fin.
+narrateur|Il glisse entre les doigts.
+narrateur|Le bois du rebord sent le soleil.
+narrateur|Le sac bleu est posé contre le rebord.
+maman|On pose le sac ici, près de nous.
+papa|Tu te souviens ? On met dans le sac ce que l'adulte a dit.
+narrateur|Nina ouvre un peu le sac.
+narrateur|Elle vérifie le doudou et le livre.
+enfant-f|Ils sont dans le sac.
+maman|Bravo. Tu as écouté.
+narrateur|Un oiseau chante tout près.
+narrateur|Le vent soulève un peu de sable clair.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1714,7 +1775,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Préparer son sac.</t>
+          <t>Nina prépare le sac. Que met-elle ?</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1874,10 +1935,10 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Préparer son sac.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Nina prépare le sac.
+narrateur|Que met-elle ?</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1902,7 +1963,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : mettre dans le sac. Jules respire. Jules retient : sac, ce que l'adulte a dit. On continue, avec maman.</t>
+          <t>Oui. Nina met dans le sac ce que l'adulte a dit. Bravo. C'est ça. On continue. Le sac reste avec nous. Nina respire. Le sable est froid sous ses mains.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2046,10 +2107,12 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : mettre dans le sac. Jules respire. Jules retient : sac, ce que l'adulte a dit. On continue, avec maman.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Oui. Nina met dans le sac ce que l'adulte a dit.
+maman|Bravo. C'est ça.
+papa|On continue. Le sac reste avec nous.
+narrateur|Nina respire. Le sable est froid sous ses mains.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2074,7 +2137,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>Qu'est-ce qu'on met encore dans le sac ? On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2238,10 +2301,10 @@
       <c r="AV7" s="2" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr"/>
+          <t>papa|Qu'est-ce qu'on met encore dans le sac ?
+narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2266,7 +2329,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Jules a choisi le ballon. L'eau coule, tout petit bruit. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Jules répète tout bas : sac, ce que l'adulte a dit. On range un objet. papa n'est pas loin.</t>
+          <t>Nina a choisi le ballon. Il est rouge, un peu poussiéreux. Il sent le caoutchouc chaud. Le ballon, on le met dans le sac. Nina pousse le ballon dans l'ouverture. Le sac devient tout rond. Bravo. Tu as mis ce que l'adulte a dit. Le ballon est dans le sac. Un peu d'eau goutte d'un robinet, tout près.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2406,10 +2469,17 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|Jules a choisi le ballon. L'eau coule, tout petit bruit. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Jules répète tout bas : sac, ce que l'adulte a dit. On range un objet. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr"/>
+          <t>narrateur|Nina a choisi le ballon.
+narrateur|Il est rouge, un peu poussiéreux.
+narrateur|Il sent le caoutchouc chaud.
+maman|Le ballon, on le met dans le sac.
+narrateur|Nina pousse le ballon dans l'ouverture.
+narrateur|Le sac devient tout rond.
+papa|Bravo. Tu as mis ce que l'adulte a dit.
+enfant-f|Le ballon est dans le sac.
+narrateur|Un peu d'eau goutte d'un robinet, tout près.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2434,7 +2504,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Il reste une chose à mettre dans le sac. On peut prendre la gourde, le goûter, ou la casquette.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2602,10 +2672,10 @@
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr"/>
+          <t>maman|Il reste une chose à mettre dans le sac.
+narrateur|On peut prendre la gourde, le goûter, ou la casquette.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2630,7 +2700,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint Tom. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de le bac à sable, le ballon et Tom. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
+          <t>Nina prend la gourde. Elle est bleue. L'eau chante un peu dedans. La gourde, on la met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Le ballon fait une bosse dans le sac. Le sable reste froid sous les chaussures. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2770,10 +2840,21 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint Tom. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de le bac à sable, le ballon et Tom. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr"/>
+          <t>narrateur|Nina prend la gourde.
+narrateur|Elle est bleue.
+narrateur|L'eau chante un peu dedans.
+maman|La gourde, on la met dans le sac.
+narrateur|Nina l'écoute. Elle met la chose dans le sac.
+narrateur|C'est ce que l'adulte a dit.
+papa|Bravo. Tu as fait du bon travail.
+enfant-f|Le sac est prêt.
+narrateur|Le ballon fait une bosse dans le sac.
+narrateur|Le sable reste froid sous les chaussures.
+maman|On a mis ce qu'il fallait. On rentre ?
+papa|Oui. Le sac vient avec nous.
+narrateur|Nina dit merci. Les chaussures font toc toc.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2798,7 +2879,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué vers le bac à sable. Elle a mis le ballon dans le sac. Elle a mis la gourde aussi. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2938,10 +3019,16 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr"/>
+          <t>narrateur|Nina a joué vers le bac à sable.
+narrateur|Elle a mis le ballon dans le sac.
+narrateur|Elle a mis la gourde aussi.
+narrateur|Le sac est sur le dos, lourd et doux.
+maman|Merci, Nina. Tu as écouté.
+papa|Bravo. On rentre à la maison.
+narrateur|La fenêtre les attend, encore un peu embuée.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2966,7 +3053,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint Léa. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de le bac à sable, le ballon et Léa. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
+          <t>Nina prend le goûter. Il est dans un linge. Ça sent la pomme douce. Le goûter, on le met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Le ballon fait une bosse dans le sac. Le sable reste froid sous les chaussures. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3106,10 +3193,21 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint Léa. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de le bac à sable, le ballon et Léa. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr"/>
+          <t>narrateur|Nina prend le goûter.
+narrateur|Il est dans un linge.
+narrateur|Ça sent la pomme douce.
+papa|Le goûter, on le met dans le sac.
+narrateur|Nina l'écoute. Elle met la chose dans le sac.
+narrateur|C'est ce que l'adulte a dit.
+maman|Bravo. Tu as fait du bon travail.
+enfant-f|Le sac est prêt.
+narrateur|Le ballon fait une bosse dans le sac.
+narrateur|Le sable reste froid sous les chaussures.
+maman|On a mis ce qu'il fallait. On rentre ?
+papa|Oui. Le sac vient avec nous.
+narrateur|Nina dit merci. Les chaussures font toc toc.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3134,7 +3232,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué vers le bac à sable. Elle a mis le ballon dans le sac. Elle a mis le goûter aussi. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3274,10 +3372,16 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr"/>
+          <t>narrateur|Nina a joué vers le bac à sable.
+narrateur|Elle a mis le ballon dans le sac.
+narrateur|Elle a mis le goûter aussi.
+narrateur|Le sac est sur le dos, lourd et doux.
+maman|Merci, Nina. Tu as écouté.
+papa|Bravo. On rentre à la maison.
+narrateur|La fenêtre les attend, encore un peu embuée.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3302,7 +3406,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint Sami. Les chaussures font toc toc. On se tient la main. Cette fin-là est celle de le bac à sable, le ballon et Sami. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
+          <t>Nina prend la casquette. Elle est à visière. Le tissu est un peu rêche. La casquette, on la met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Le ballon fait une bosse dans le sac. Le sable reste froid sous les chaussures. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3442,10 +3546,21 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint Sami. Les chaussures font toc toc. On se tient la main. Cette fin-là est celle de le bac à sable, le ballon et Sami. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr"/>
+          <t>narrateur|Nina prend la casquette.
+narrateur|Elle est à visière.
+narrateur|Le tissu est un peu rêche.
+maman|La casquette, on la met dans le sac.
+narrateur|Nina l'écoute. Elle met la chose dans le sac.
+narrateur|C'est ce que l'adulte a dit.
+papa|Bravo. Tu as fait du bon travail.
+enfant-f|Le sac est prêt.
+narrateur|Le ballon fait une bosse dans le sac.
+narrateur|Le sable reste froid sous les chaussures.
+maman|On a mis ce qu'il fallait. On rentre ?
+papa|Oui. Le sac vient avec nous.
+narrateur|Nina dit merci. Les chaussures font toc toc.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3470,7 +3585,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué vers le bac à sable. Elle a mis le ballon dans le sac. Elle a mis la casquette aussi. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3610,10 +3725,16 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr"/>
+          <t>narrateur|Nina a joué vers le bac à sable.
+narrateur|Elle a mis le ballon dans le sac.
+narrateur|Elle a mis la casquette aussi.
+narrateur|Le sac est sur le dos, lourd et doux.
+maman|Merci, Nina. Tu as écouté.
+papa|Bravo. On rentre à la maison.
+narrateur|La fenêtre les attend, encore un peu embuée.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3638,7 +3759,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Jules a choisi le seau. Un vélo passe au loin. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Jules répète tout bas : sac, ce que l'adulte a dit. On dit merci. papa n'est pas loin.</t>
+          <t>Nina a choisi le seau. Il est jaune. L'anse est un peu rêche. Il y a du sable au fond, tout fin. Le seau, on le met dans le sac aussi. Nina le glisse à côté du doudou. Tu as fini de mettre le seau ? Oui. Il est dans le sac. Bravo, Nina. Bon travail. Un vélo passe au loin, tout léger.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3778,10 +3899,22 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Jules a choisi le seau. Un vélo passe au loin. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Jules répète tout bas : sac, ce que l'adulte a dit. On dit merci. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr"/>
+          <t>narrateur|Nina a choisi le seau.
+narrateur|Il est jaune. L'anse est un peu rêche.
+narrateur|Il y a du sable au fond, tout fin.
+papa|Le seau, on le met dans le sac aussi.
+narrateur|Nina le glisse à côté du doudou.
+maman|Tu as fini de mettre le seau ?
+enfant-f|Oui. Il est dans le sac.
+papa|Bravo, Nina. Bon travail.
+narrateur|Un vélo passe au loin, tout léger.</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>voiture_passe</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3806,7 +3939,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Il reste une chose à mettre dans le sac. On peut prendre la gourde, le goûter, ou la casquette.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3974,10 +4107,10 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr"/>
+          <t>maman|Il reste une chose à mettre dans le sac.
+narrateur|On peut prendre la gourde, le goûter, ou la casquette.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4002,7 +4135,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint Tom. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de le bac à sable, le seau et Tom. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
+          <t>Nina prend la gourde. Elle est bleue. L'eau chante un peu dedans. La gourde, on la met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. L'anse du seau dépasse un tout petit peu. Le sable reste froid sous les chaussures. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4142,10 +4275,21 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint Tom. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de le bac à sable, le seau et Tom. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr"/>
+          <t>narrateur|Nina prend la gourde.
+narrateur|Elle est bleue.
+narrateur|L'eau chante un peu dedans.
+maman|La gourde, on la met dans le sac.
+narrateur|Nina l'écoute. Elle met la chose dans le sac.
+narrateur|C'est ce que l'adulte a dit.
+papa|Bravo. Tu as fait du bon travail.
+enfant-f|Le sac est prêt.
+narrateur|L'anse du seau dépasse un tout petit peu.
+narrateur|Le sable reste froid sous les chaussures.
+maman|On a mis ce qu'il fallait. On rentre ?
+papa|Oui. Le sac vient avec nous.
+narrateur|Nina dit merci. Les chaussures font toc toc.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4170,7 +4314,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué vers le bac à sable. Elle a mis le seau dans le sac. Elle a mis la gourde aussi. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4310,10 +4454,16 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr"/>
+          <t>narrateur|Nina a joué vers le bac à sable.
+narrateur|Elle a mis le seau dans le sac.
+narrateur|Elle a mis la gourde aussi.
+narrateur|Le sac est sur le dos, lourd et doux.
+maman|Merci, Nina. Tu as écouté.
+papa|Bravo. On rentre à la maison.
+narrateur|La fenêtre les attend, encore un peu embuée.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4338,7 +4488,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint Léa. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de le bac à sable, le seau et Léa. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
+          <t>Nina prend le goûter. Il est dans un linge. Ça sent la pomme douce. Le goûter, on le met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. L'anse du seau dépasse un tout petit peu. Le sable reste froid sous les chaussures. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4478,10 +4628,21 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint Léa. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de le bac à sable, le seau et Léa. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr"/>
+          <t>narrateur|Nina prend le goûter.
+narrateur|Il est dans un linge.
+narrateur|Ça sent la pomme douce.
+papa|Le goûter, on le met dans le sac.
+narrateur|Nina l'écoute. Elle met la chose dans le sac.
+narrateur|C'est ce que l'adulte a dit.
+maman|Bravo. Tu as fait du bon travail.
+enfant-f|Le sac est prêt.
+narrateur|L'anse du seau dépasse un tout petit peu.
+narrateur|Le sable reste froid sous les chaussures.
+maman|On a mis ce qu'il fallait. On rentre ?
+papa|Oui. Le sac vient avec nous.
+narrateur|Nina dit merci. Les chaussures font toc toc.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4506,7 +4667,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué vers le bac à sable. Elle a mis le seau dans le sac. Elle a mis le goûter aussi. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4646,10 +4807,16 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr"/>
+          <t>narrateur|Nina a joué vers le bac à sable.
+narrateur|Elle a mis le seau dans le sac.
+narrateur|Elle a mis le goûter aussi.
+narrateur|Le sac est sur le dos, lourd et doux.
+maman|Merci, Nina. Tu as écouté.
+papa|Bravo. On rentre à la maison.
+narrateur|La fenêtre les attend, encore un peu embuée.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4674,7 +4841,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint Sami. La couverture est douce. On se tient la main. Cette fin-là est celle de le bac à sable, le seau et Sami. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
+          <t>Nina prend la casquette. Elle est à visière. Le tissu est un peu rêche. La casquette, on la met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. L'anse du seau dépasse un tout petit peu. Le sable reste froid sous les chaussures. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4814,10 +4981,21 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint Sami. La couverture est douce. On se tient la main. Cette fin-là est celle de le bac à sable, le seau et Sami. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr"/>
+          <t>narrateur|Nina prend la casquette.
+narrateur|Elle est à visière.
+narrateur|Le tissu est un peu rêche.
+maman|La casquette, on la met dans le sac.
+narrateur|Nina l'écoute. Elle met la chose dans le sac.
+narrateur|C'est ce que l'adulte a dit.
+papa|Bravo. Tu as fait du bon travail.
+enfant-f|Le sac est prêt.
+narrateur|L'anse du seau dépasse un tout petit peu.
+narrateur|Le sable reste froid sous les chaussures.
+maman|On a mis ce qu'il fallait. On rentre ?
+papa|Oui. Le sac vient avec nous.
+narrateur|Nina dit merci. Les chaussures font toc toc.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4842,7 +5020,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué vers le bac à sable. Elle a mis le seau dans le sac. Elle a mis la casquette aussi. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -4982,10 +5160,16 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr"/>
+          <t>narrateur|Nina a joué vers le bac à sable.
+narrateur|Elle a mis le seau dans le sac.
+narrateur|Elle a mis la casquette aussi.
+narrateur|Le sac est sur le dos, lourd et doux.
+maman|Merci, Nina. Tu as écouté.
+papa|Bravo. On rentre à la maison.
+narrateur|La fenêtre les attend, encore un peu embuée.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5010,7 +5194,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Jules a choisi le doudou. La lumière est claire. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Jules répète tout bas : sac, ce que l'adulte a dit. On souffle doucement. papa n'est pas loin.</t>
+          <t>Nina a choisi le doudou. Il est déjà un peu dans le sac. Nina le pousse bien au fond, tout doux. Le doudou reste dans le sac. Comme j'ai dit. Le tissu sent la maison. Bravo. Tu as mis ce que l'adulte a dit. Mon doudou est prêt. La lumière est claire sur le tissu bleu. On souffle un peu. Puis on continue.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5150,10 +5334,17 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|Jules a choisi le doudou. La lumière est claire. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Jules répète tout bas : sac, ce que l'adulte a dit. On souffle doucement. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr"/>
+          <t>narrateur|Nina a choisi le doudou.
+narrateur|Il est déjà un peu dans le sac.
+narrateur|Nina le pousse bien au fond, tout doux.
+maman|Le doudou reste dans le sac. Comme j'ai dit.
+narrateur|Le tissu sent la maison.
+papa|Bravo. Tu as mis ce que l'adulte a dit.
+enfant-f|Mon doudou est prêt.
+narrateur|La lumière est claire sur le tissu bleu.
+maman|On souffle un peu. Puis on continue.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5178,7 +5369,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Il reste une chose à mettre dans le sac. On peut prendre la gourde, le goûter, ou la casquette.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5346,10 +5537,10 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
-        </is>
-      </c>
-      <c r="AX25" t="inlineStr"/>
+          <t>maman|Il reste une chose à mettre dans le sac.
+narrateur|On peut prendre la gourde, le goûter, ou la casquette.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5374,7 +5565,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint Tom. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de le bac à sable, le doudou et Tom. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
+          <t>Nina prend la gourde. Elle est bleue. L'eau chante un peu dedans. La gourde, on la met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Le doudou chauffe le fond du sac. Le sable reste froid sous les chaussures. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5514,10 +5705,21 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint Tom. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de le bac à sable, le doudou et Tom. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr"/>
+          <t>narrateur|Nina prend la gourde.
+narrateur|Elle est bleue.
+narrateur|L'eau chante un peu dedans.
+maman|La gourde, on la met dans le sac.
+narrateur|Nina l'écoute. Elle met la chose dans le sac.
+narrateur|C'est ce que l'adulte a dit.
+papa|Bravo. Tu as fait du bon travail.
+enfant-f|Le sac est prêt.
+narrateur|Le doudou chauffe le fond du sac.
+narrateur|Le sable reste froid sous les chaussures.
+maman|On a mis ce qu'il fallait. On rentre ?
+papa|Oui. Le sac vient avec nous.
+narrateur|Nina dit merci. Les chaussures font toc toc.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5542,7 +5744,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué vers le bac à sable. Elle a mis le doudou dans le sac. Elle a mis la gourde aussi. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5682,10 +5884,16 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX27" t="inlineStr"/>
+          <t>narrateur|Nina a joué vers le bac à sable.
+narrateur|Elle a mis le doudou dans le sac.
+narrateur|Elle a mis la gourde aussi.
+narrateur|Le sac est sur le dos, lourd et doux.
+maman|Merci, Nina. Tu as écouté.
+papa|Bravo. On rentre à la maison.
+narrateur|La fenêtre les attend, encore un peu embuée.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5710,7 +5918,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint Léa. La couverture est douce. On se tait une seconde. Cette fin-là est celle de le bac à sable, le doudou et Léa. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
+          <t>Nina prend le goûter. Il est dans un linge. Ça sent la pomme douce. Le goûter, on le met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Le doudou chauffe le fond du sac. Le sable reste froid sous les chaussures. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5850,10 +6058,21 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint Léa. La couverture est douce. On se tait une seconde. Cette fin-là est celle de le bac à sable, le doudou et Léa. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX28" t="inlineStr"/>
+          <t>narrateur|Nina prend le goûter.
+narrateur|Il est dans un linge.
+narrateur|Ça sent la pomme douce.
+papa|Le goûter, on le met dans le sac.
+narrateur|Nina l'écoute. Elle met la chose dans le sac.
+narrateur|C'est ce que l'adulte a dit.
+maman|Bravo. Tu as fait du bon travail.
+enfant-f|Le sac est prêt.
+narrateur|Le doudou chauffe le fond du sac.
+narrateur|Le sable reste froid sous les chaussures.
+maman|On a mis ce qu'il fallait. On rentre ?
+papa|Oui. Le sac vient avec nous.
+narrateur|Nina dit merci. Les chaussures font toc toc.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5878,7 +6097,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué vers le bac à sable. Elle a mis le doudou dans le sac. Elle a mis le goûter aussi. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6018,10 +6237,16 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX29" t="inlineStr"/>
+          <t>narrateur|Nina a joué vers le bac à sable.
+narrateur|Elle a mis le doudou dans le sac.
+narrateur|Elle a mis le goûter aussi.
+narrateur|Le sac est sur le dos, lourd et doux.
+maman|Merci, Nina. Tu as écouté.
+papa|Bravo. On rentre à la maison.
+narrateur|La fenêtre les attend, encore un peu embuée.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6046,7 +6271,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint Sami. On entend un oiseau. On se tient la main. Cette fin-là est celle de le bac à sable, le doudou et Sami. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
+          <t>Nina prend la casquette. Elle est à visière. Le tissu est un peu rêche. La casquette, on la met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Le doudou chauffe le fond du sac. Le sable reste froid sous les chaussures. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6186,10 +6411,21 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint Sami. On entend un oiseau. On se tient la main. Cette fin-là est celle de le bac à sable, le doudou et Sami. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr"/>
+          <t>narrateur|Nina prend la casquette.
+narrateur|Elle est à visière.
+narrateur|Le tissu est un peu rêche.
+maman|La casquette, on la met dans le sac.
+narrateur|Nina l'écoute. Elle met la chose dans le sac.
+narrateur|C'est ce que l'adulte a dit.
+papa|Bravo. Tu as fait du bon travail.
+enfant-f|Le sac est prêt.
+narrateur|Le doudou chauffe le fond du sac.
+narrateur|Le sable reste froid sous les chaussures.
+maman|On a mis ce qu'il fallait. On rentre ?
+papa|Oui. Le sac vient avec nous.
+narrateur|Nina dit merci. Les chaussures font toc toc.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6214,7 +6450,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué vers le bac à sable. Elle a mis le doudou dans le sac. Elle a mis la casquette aussi. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6354,10 +6590,16 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX31" t="inlineStr"/>
+          <t>narrateur|Nina a joué vers le bac à sable.
+narrateur|Elle a mis le doudou dans le sac.
+narrateur|Elle a mis la casquette aussi.
+narrateur|Le sac est sur le dos, lourd et doux.
+maman|Merci, Nina. Tu as écouté.
+papa|Bravo. On rentre à la maison.
+narrateur|La fenêtre les attend, encore un peu embuée.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6382,7 +6624,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Jules va vers le toboggan. Une feuille tombe. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Jules se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On se tait une seconde. Je suis là. On reste ensemble.</t>
+          <t>Nina marche vers le toboggan. Le plastique lisse brille au soleil. Les marches métalliques sont tièdes. Nina pose la main dessus, tout doucement. Le sac bleu est au pied du toboggan. On garde le sac près de nous. Avant de jouer, on met ce que j'ai dit. Nina ouvre le sac. Elle voit le doudou et le livre. C'est dans le sac. Bravo, Nina. Tu as fait du bon travail. Une feuille sèche tourne sur le sol. Ça sent l'herbe coupée.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6522,11 +6764,26 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|Jules va vers le toboggan. Une feuille tombe. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Jules se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On se tait une seconde.
-maman|Je suis là. On reste ensemble.</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr"/>
+          <t>narrateur|Nina marche vers le toboggan.
+narrateur|Le plastique lisse brille au soleil.
+narrateur|Les marches métalliques sont tièdes.
+narrateur|Nina pose la main dessus, tout doucement.
+narrateur|Le sac bleu est au pied du toboggan.
+papa|On garde le sac près de nous.
+maman|Avant de jouer, on met ce que j'ai dit.
+narrateur|Nina ouvre le sac.
+narrateur|Elle voit le doudou et le livre.
+enfant-f|C'est dans le sac.
+papa|Bravo, Nina. Tu as fait du bon travail.
+narrateur|Une feuille sèche tourne sur le sol.
+narrateur|Ça sent l'herbe coupée.</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6551,7 +6808,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Préparer son sac.</t>
+          <t>Nina prépare le sac. Que met-elle ?</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -6711,10 +6968,10 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Préparer son sac.</t>
-        </is>
-      </c>
-      <c r="AX33" t="inlineStr"/>
+          <t>narrateur|Nina prépare le sac.
+narrateur|Que met-elle ?</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6739,7 +6996,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : mettre dans le sac. Jules respire. Jules retient : sac, ce que l'adulte a dit. On continue, avec maman.</t>
+          <t>Oui. On met dans le sac ce que l'adulte a dit. Bravo, Nina. Tu as écouté. Le sac est prêt. On peut jouer un peu. Nina pose la main sur la sangle lisse.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6883,10 +7140,12 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : mettre dans le sac. Jules respire. Jules retient : sac, ce que l'adulte a dit. On continue, avec maman.</t>
-        </is>
-      </c>
-      <c r="AX34" t="inlineStr"/>
+          <t>narrateur|Oui. On met dans le sac ce que l'adulte a dit.
+papa|Bravo, Nina. Tu as écouté.
+maman|Le sac est prêt. On peut jouer un peu.
+narrateur|Nina pose la main sur la sangle lisse.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6911,7 +7170,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>Qu'est-ce qu'on met encore dans le sac ? On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -7075,10 +7334,10 @@
       <c r="AV35" s="2" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
-        </is>
-      </c>
-      <c r="AX35" t="inlineStr"/>
+          <t>papa|Qu'est-ce qu'on met encore dans le sac ?
+narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7103,7 +7362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Jules a choisi le ballon. Il y a des miettes sur la table. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Jules répète tout bas : sac, ce que l'adulte a dit. On range un objet. papa n'est pas loin.</t>
+          <t>Nina a choisi le ballon, près du toboggan. Il rebondit une fois, tout mou. On le met dans le sac, maintenant. Nina le prend à deux mains. Elle le glisse dans le sac bleu. C'est ce que l'adulte a dit. Bravo. Le ballon est avec le livre. Il y a des miettes de goûter sur une table basse. On range. Le sac reste fermé.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7243,10 +7502,22 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|Jules a choisi le ballon. Il y a des miettes sur la table. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Jules répète tout bas : sac, ce que l'adulte a dit. On range un objet. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr"/>
+          <t>narrateur|Nina a choisi le ballon, près du toboggan.
+narrateur|Il rebondit une fois, tout mou.
+maman|On le met dans le sac, maintenant.
+narrateur|Nina le prend à deux mains.
+narrateur|Elle le glisse dans le sac bleu.
+papa|C'est ce que l'adulte a dit. Bravo.
+enfant-f|Le ballon est avec le livre.
+narrateur|Il y a des miettes de goûter sur une table basse.
+maman|On range. Le sac reste fermé.</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7271,7 +7542,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Il reste une chose à mettre dans le sac. On peut prendre la gourde, le goûter, ou la casquette.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7439,10 +7710,10 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr"/>
+          <t>maman|Il reste une chose à mettre dans le sac.
+narrateur|On peut prendre la gourde, le goûter, ou la casquette.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7467,7 +7738,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint Tom. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de le toboggan, le ballon et Tom. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
+          <t>Nina prend la gourde. Elle est bleue. L'eau chante un peu dedans. La gourde, on la met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Le ballon fait une bosse dans le sac. Le toboggan brille encore derrière eux. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7607,10 +7878,26 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint Tom. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de le toboggan, le ballon et Tom. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr"/>
+          <t>narrateur|Nina prend la gourde.
+narrateur|Elle est bleue.
+narrateur|L'eau chante un peu dedans.
+maman|La gourde, on la met dans le sac.
+narrateur|Nina l'écoute. Elle met la chose dans le sac.
+narrateur|C'est ce que l'adulte a dit.
+papa|Bravo. Tu as fait du bon travail.
+enfant-f|Le sac est prêt.
+narrateur|Le ballon fait une bosse dans le sac.
+narrateur|Le toboggan brille encore derrière eux.
+maman|On a mis ce qu'il fallait. On rentre ?
+papa|Oui. Le sac vient avec nous.
+narrateur|Nina dit merci. Les chaussures font toc toc.</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7635,7 +7922,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué vers le toboggan. Elle a mis le ballon dans le sac. Elle a mis la gourde aussi. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7775,10 +8062,16 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX39" t="inlineStr"/>
+          <t>narrateur|Nina a joué vers le toboggan.
+narrateur|Elle a mis le ballon dans le sac.
+narrateur|Elle a mis la gourde aussi.
+narrateur|Le sac est sur le dos, lourd et doux.
+maman|Merci, Nina. Tu as écouté.
+papa|Bravo. On rentre à la maison.
+narrateur|La fenêtre les attend, encore un peu embuée.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7803,7 +8096,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint Léa. Les chaussures font toc toc. On se tient la main. Cette fin-là est celle de le toboggan, le ballon et Léa. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
+          <t>Nina prend le goûter. Il est dans un linge. Ça sent la pomme douce. Le goûter, on le met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Le ballon fait une bosse dans le sac. Le toboggan brille encore derrière eux. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7943,10 +8236,26 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint Léa. Les chaussures font toc toc. On se tient la main. Cette fin-là est celle de le toboggan, le ballon et Léa. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr"/>
+          <t>narrateur|Nina prend le goûter.
+narrateur|Il est dans un linge.
+narrateur|Ça sent la pomme douce.
+papa|Le goûter, on le met dans le sac.
+narrateur|Nina l'écoute. Elle met la chose dans le sac.
+narrateur|C'est ce que l'adulte a dit.
+maman|Bravo. Tu as fait du bon travail.
+enfant-f|Le sac est prêt.
+narrateur|Le ballon fait une bosse dans le sac.
+narrateur|Le toboggan brille encore derrière eux.
+maman|On a mis ce qu'il fallait. On rentre ?
+papa|Oui. Le sac vient avec nous.
+narrateur|Nina dit merci. Les chaussures font toc toc.</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7971,7 +8280,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué vers le toboggan. Elle a mis le ballon dans le sac. Elle a mis le goûter aussi. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8111,10 +8420,16 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX41" t="inlineStr"/>
+          <t>narrateur|Nina a joué vers le toboggan.
+narrateur|Elle a mis le ballon dans le sac.
+narrateur|Elle a mis le goûter aussi.
+narrateur|Le sac est sur le dos, lourd et doux.
+maman|Merci, Nina. Tu as écouté.
+papa|Bravo. On rentre à la maison.
+narrateur|La fenêtre les attend, encore un peu embuée.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8139,7 +8454,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint Sami. La couverture est douce. On range un objet. Cette fin-là est celle de le toboggan, le ballon et Sami. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
+          <t>Nina prend la casquette. Elle est à visière. Le tissu est un peu rêche. La casquette, on la met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Le ballon fait une bosse dans le sac. Le toboggan brille encore derrière eux. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8279,10 +8594,26 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint Sami. La couverture est douce. On range un objet. Cette fin-là est celle de le toboggan, le ballon et Sami. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr"/>
+          <t>narrateur|Nina prend la casquette.
+narrateur|Elle est à visière.
+narrateur|Le tissu est un peu rêche.
+maman|La casquette, on la met dans le sac.
+narrateur|Nina l'écoute. Elle met la chose dans le sac.
+narrateur|C'est ce que l'adulte a dit.
+papa|Bravo. Tu as fait du bon travail.
+enfant-f|Le sac est prêt.
+narrateur|Le ballon fait une bosse dans le sac.
+narrateur|Le toboggan brille encore derrière eux.
+maman|On a mis ce qu'il fallait. On rentre ?
+papa|Oui. Le sac vient avec nous.
+narrateur|Nina dit merci. Les chaussures font toc toc.</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8307,7 +8638,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué vers le toboggan. Elle a mis le ballon dans le sac. Elle a mis la casquette aussi. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8447,10 +8778,16 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX43" t="inlineStr"/>
+          <t>narrateur|Nina a joué vers le toboggan.
+narrateur|Elle a mis le ballon dans le sac.
+narrateur|Elle a mis la casquette aussi.
+narrateur|Le sac est sur le dos, lourd et doux.
+maman|Merci, Nina. Tu as écouté.
+papa|Bravo. On rentre à la maison.
+narrateur|La fenêtre les attend, encore un peu embuée.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8475,7 +8812,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Jules a choisi le seau. Un chat miaule une fois. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Jules répète tout bas : sac, ce que l'adulte a dit. On dit merci. papa n'est pas loin.</t>
+          <t>Nina a choisi le seau, au pied du toboggan. Un chat miaule une fois, tout près. Le seau va dans le sac. Nina le pose sur le doudou. Tu as mis ce que j'ai dit ? Oui. Le seau est dedans. Bravo. On dit merci au seau, tout bas. Nina rit un peu. L'anse cliquette.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8615,10 +8952,21 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Jules a choisi le seau. Un chat miaule une fois. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Jules répète tout bas : sac, ce que l'adulte a dit. On dit merci. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr"/>
+          <t>narrateur|Nina a choisi le seau, au pied du toboggan.
+narrateur|Un chat miaule une fois, tout près.
+papa|Le seau va dans le sac.
+narrateur|Nina le pose sur le doudou.
+maman|Tu as mis ce que j'ai dit ?
+enfant-f|Oui. Le seau est dedans.
+papa|Bravo. On dit merci au seau, tout bas.
+narrateur|Nina rit un peu. L'anse cliquette.</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8643,7 +8991,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Il reste une chose à mettre dans le sac. On peut prendre la gourde, le goûter, ou la casquette.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -8811,10 +9159,10 @@
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
-        </is>
-      </c>
-      <c r="AX45" t="inlineStr"/>
+          <t>maman|Il reste une chose à mettre dans le sac.
+narrateur|On peut prendre la gourde, le goûter, ou la casquette.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8839,7 +9187,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint Tom. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de le toboggan, le seau et Tom. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
+          <t>Nina prend la gourde. Elle est bleue. L'eau chante un peu dedans. La gourde, on la met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. L'anse du seau dépasse un tout petit peu. Le toboggan brille encore derrière eux. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8979,10 +9327,26 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint Tom. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de le toboggan, le seau et Tom. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX46" t="inlineStr"/>
+          <t>narrateur|Nina prend la gourde.
+narrateur|Elle est bleue.
+narrateur|L'eau chante un peu dedans.
+maman|La gourde, on la met dans le sac.
+narrateur|Nina l'écoute. Elle met la chose dans le sac.
+narrateur|C'est ce que l'adulte a dit.
+papa|Bravo. Tu as fait du bon travail.
+enfant-f|Le sac est prêt.
+narrateur|L'anse du seau dépasse un tout petit peu.
+narrateur|Le toboggan brille encore derrière eux.
+maman|On a mis ce qu'il fallait. On rentre ?
+papa|Oui. Le sac vient avec nous.
+narrateur|Nina dit merci. Les chaussures font toc toc.</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9007,7 +9371,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué vers le toboggan. Elle a mis le seau dans le sac. Elle a mis la gourde aussi. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9147,10 +9511,16 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX47" t="inlineStr"/>
+          <t>narrateur|Nina a joué vers le toboggan.
+narrateur|Elle a mis le seau dans le sac.
+narrateur|Elle a mis la gourde aussi.
+narrateur|Le sac est sur le dos, lourd et doux.
+maman|Merci, Nina. Tu as écouté.
+papa|Bravo. On rentre à la maison.
+narrateur|La fenêtre les attend, encore un peu embuée.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9175,7 +9545,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint Léa. La couverture est douce. On se tient la main. Cette fin-là est celle de le toboggan, le seau et Léa. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
+          <t>Nina prend le goûter. Il est dans un linge. Ça sent la pomme douce. Le goûter, on le met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. L'anse du seau dépasse un tout petit peu. Le toboggan brille encore derrière eux. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9315,10 +9685,26 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint Léa. La couverture est douce. On se tient la main. Cette fin-là est celle de le toboggan, le seau et Léa. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX48" t="inlineStr"/>
+          <t>narrateur|Nina prend le goûter.
+narrateur|Il est dans un linge.
+narrateur|Ça sent la pomme douce.
+papa|Le goûter, on le met dans le sac.
+narrateur|Nina l'écoute. Elle met la chose dans le sac.
+narrateur|C'est ce que l'adulte a dit.
+maman|Bravo. Tu as fait du bon travail.
+enfant-f|Le sac est prêt.
+narrateur|L'anse du seau dépasse un tout petit peu.
+narrateur|Le toboggan brille encore derrière eux.
+maman|On a mis ce qu'il fallait. On rentre ?
+papa|Oui. Le sac vient avec nous.
+narrateur|Nina dit merci. Les chaussures font toc toc.</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9343,7 +9729,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué vers le toboggan. Elle a mis le seau dans le sac. Elle a mis le goûter aussi. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9483,10 +9869,16 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX49" t="inlineStr"/>
+          <t>narrateur|Nina a joué vers le toboggan.
+narrateur|Elle a mis le seau dans le sac.
+narrateur|Elle a mis le goûter aussi.
+narrateur|Le sac est sur le dos, lourd et doux.
+maman|Merci, Nina. Tu as écouté.
+papa|Bravo. On rentre à la maison.
+narrateur|La fenêtre les attend, encore un peu embuée.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9511,7 +9903,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint Sami. On entend un oiseau. On range un objet. Cette fin-là est celle de le toboggan, le seau et Sami. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
+          <t>Nina prend la casquette. Elle est à visière. Le tissu est un peu rêche. La casquette, on la met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. L'anse du seau dépasse un tout petit peu. Le toboggan brille encore derrière eux. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9651,10 +10043,26 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint Sami. On entend un oiseau. On range un objet. Cette fin-là est celle de le toboggan, le seau et Sami. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX50" t="inlineStr"/>
+          <t>narrateur|Nina prend la casquette.
+narrateur|Elle est à visière.
+narrateur|Le tissu est un peu rêche.
+maman|La casquette, on la met dans le sac.
+narrateur|Nina l'écoute. Elle met la chose dans le sac.
+narrateur|C'est ce que l'adulte a dit.
+papa|Bravo. Tu as fait du bon travail.
+enfant-f|Le sac est prêt.
+narrateur|L'anse du seau dépasse un tout petit peu.
+narrateur|Le toboggan brille encore derrière eux.
+maman|On a mis ce qu'il fallait. On rentre ?
+papa|Oui. Le sac vient avec nous.
+narrateur|Nina dit merci. Les chaussures font toc toc.</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9679,7 +10087,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué vers le toboggan. Elle a mis le seau dans le sac. Elle a mis la casquette aussi. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9819,10 +10227,16 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX51" t="inlineStr"/>
+          <t>narrateur|Nina a joué vers le toboggan.
+narrateur|Elle a mis le seau dans le sac.
+narrateur|Elle a mis la casquette aussi.
+narrateur|Le sac est sur le dos, lourd et doux.
+maman|Merci, Nina. Tu as écouté.
+papa|Bravo. On rentre à la maison.
+narrateur|La fenêtre les attend, encore un peu embuée.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9847,7 +10261,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Jules a choisi le doudou. Les chaussures font toc toc. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Jules répète tout bas : sac, ce que l'adulte a dit. On souffle doucement. papa n'est pas loin.</t>
+          <t>Nina a choisi le doudou, près des marches. Les chaussures font toc toc sur le métal. Le doudou, on le met bien dans le sac. Nina l'enfonce tout doucement. Bravo. Tu as écouté. Il est au chaud dans le sac. Nina souffle. Le toboggan brille encore. On continue. Il reste une chose.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9987,10 +10401,21 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Jules a choisi le doudou. Les chaussures font toc toc. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Jules répète tout bas : sac, ce que l'adulte a dit. On souffle doucement. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX52" t="inlineStr"/>
+          <t>narrateur|Nina a choisi le doudou, près des marches.
+narrateur|Les chaussures font toc toc sur le métal.
+maman|Le doudou, on le met bien dans le sac.
+narrateur|Nina l'enfonce tout doucement.
+papa|Bravo. Tu as écouté.
+enfant-f|Il est au chaud dans le sac.
+narrateur|Nina souffle. Le toboggan brille encore.
+maman|On continue. Il reste une chose.</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10015,7 +10440,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Il reste une chose à mettre dans le sac. On peut prendre la gourde, le goûter, ou la casquette.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10183,10 +10608,10 @@
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
-        </is>
-      </c>
-      <c r="AX53" t="inlineStr"/>
+          <t>maman|Il reste une chose à mettre dans le sac.
+narrateur|On peut prendre la gourde, le goûter, ou la casquette.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10211,7 +10636,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint Tom. La couverture est douce. On se tait une seconde. Cette fin-là est celle de le toboggan, le doudou et Tom. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
+          <t>Nina prend la gourde. Elle est bleue. L'eau chante un peu dedans. La gourde, on la met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Le doudou chauffe le fond du sac. Le toboggan brille encore derrière eux. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10351,10 +10776,26 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint Tom. La couverture est douce. On se tait une seconde. Cette fin-là est celle de le toboggan, le doudou et Tom. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX54" t="inlineStr"/>
+          <t>narrateur|Nina prend la gourde.
+narrateur|Elle est bleue.
+narrateur|L'eau chante un peu dedans.
+maman|La gourde, on la met dans le sac.
+narrateur|Nina l'écoute. Elle met la chose dans le sac.
+narrateur|C'est ce que l'adulte a dit.
+papa|Bravo. Tu as fait du bon travail.
+enfant-f|Le sac est prêt.
+narrateur|Le doudou chauffe le fond du sac.
+narrateur|Le toboggan brille encore derrière eux.
+maman|On a mis ce qu'il fallait. On rentre ?
+papa|Oui. Le sac vient avec nous.
+narrateur|Nina dit merci. Les chaussures font toc toc.</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10379,7 +10820,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué vers le toboggan. Elle a mis le doudou dans le sac. Elle a mis la gourde aussi. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10519,10 +10960,16 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX55" t="inlineStr"/>
+          <t>narrateur|Nina a joué vers le toboggan.
+narrateur|Elle a mis le doudou dans le sac.
+narrateur|Elle a mis la gourde aussi.
+narrateur|Le sac est sur le dos, lourd et doux.
+maman|Merci, Nina. Tu as écouté.
+papa|Bravo. On rentre à la maison.
+narrateur|La fenêtre les attend, encore un peu embuée.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10547,7 +10994,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint Léa. On entend un oiseau. On se tient la main. Cette fin-là est celle de le toboggan, le doudou et Léa. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
+          <t>Nina prend le goûter. Il est dans un linge. Ça sent la pomme douce. Le goûter, on le met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Le doudou chauffe le fond du sac. Le toboggan brille encore derrière eux. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10687,10 +11134,26 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint Léa. On entend un oiseau. On se tient la main. Cette fin-là est celle de le toboggan, le doudou et Léa. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX56" t="inlineStr"/>
+          <t>narrateur|Nina prend le goûter.
+narrateur|Il est dans un linge.
+narrateur|Ça sent la pomme douce.
+papa|Le goûter, on le met dans le sac.
+narrateur|Nina l'écoute. Elle met la chose dans le sac.
+narrateur|C'est ce que l'adulte a dit.
+maman|Bravo. Tu as fait du bon travail.
+enfant-f|Le sac est prêt.
+narrateur|Le doudou chauffe le fond du sac.
+narrateur|Le toboggan brille encore derrière eux.
+maman|On a mis ce qu'il fallait. On rentre ?
+papa|Oui. Le sac vient avec nous.
+narrateur|Nina dit merci. Les chaussures font toc toc.</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10715,7 +11178,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué vers le toboggan. Elle a mis le doudou dans le sac. Elle a mis le goûter aussi. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10855,10 +11318,16 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX57" t="inlineStr"/>
+          <t>narrateur|Nina a joué vers le toboggan.
+narrateur|Elle a mis le doudou dans le sac.
+narrateur|Elle a mis le goûter aussi.
+narrateur|Le sac est sur le dos, lourd et doux.
+maman|Merci, Nina. Tu as écouté.
+papa|Bravo. On rentre à la maison.
+narrateur|La fenêtre les attend, encore un peu embuée.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10883,7 +11352,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint Sami. Ça sent le pain chaud. On range un objet. Cette fin-là est celle de le toboggan, le doudou et Sami. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
+          <t>Nina prend la casquette. Elle est à visière. Le tissu est un peu rêche. La casquette, on la met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Le doudou chauffe le fond du sac. Le toboggan brille encore derrière eux. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -11023,10 +11492,26 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint Sami. Ça sent le pain chaud. On range un objet. Cette fin-là est celle de le toboggan, le doudou et Sami. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX58" t="inlineStr"/>
+          <t>narrateur|Nina prend la casquette.
+narrateur|Elle est à visière.
+narrateur|Le tissu est un peu rêche.
+maman|La casquette, on la met dans le sac.
+narrateur|Nina l'écoute. Elle met la chose dans le sac.
+narrateur|C'est ce que l'adulte a dit.
+papa|Bravo. Tu as fait du bon travail.
+enfant-f|Le sac est prêt.
+narrateur|Le doudou chauffe le fond du sac.
+narrateur|Le toboggan brille encore derrière eux.
+maman|On a mis ce qu'il fallait. On rentre ?
+papa|Oui. Le sac vient avec nous.
+narrateur|Nina dit merci. Les chaussures font toc toc.</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11051,7 +11536,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué vers le toboggan. Elle a mis le doudou dans le sac. Elle a mis la casquette aussi. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11191,10 +11676,16 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX59" t="inlineStr"/>
+          <t>narrateur|Nina a joué vers le toboggan.
+narrateur|Elle a mis le doudou dans le sac.
+narrateur|Elle a mis la casquette aussi.
+narrateur|Le sac est sur le dos, lourd et doux.
+maman|Merci, Nina. Tu as écouté.
+papa|Bravo. On rentre à la maison.
+narrateur|La fenêtre les attend, encore un peu embuée.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11219,7 +11710,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Jules va vers les balançoires. L'eau coule, tout petit bruit. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Jules se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On se tient la main. Je suis là. On reste ensemble.</t>
+          <t>Nina marche vers les balançoires. Les chaînes font un petit clin clin. Le siège en bois est lisse et chaud. Le vent passe dans les cheveux de Nina. Le sac bleu est posé dans l'herbe. On met le sac ici, à côté de la balançoire. On met dans le sac ce que l'adulte a dit. Nina touche la sangle lisse. Elle sent le doudou à travers le tissu. Le sac est avec nous. Très bien. On reste ensemble. Au loin, un vélo passe tout doux. L'air est frais sur les joues.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11359,11 +11850,26 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|Jules va vers les balançoires. L'eau coule, tout petit bruit. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Jules se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On se tient la main.
-maman|Je suis là. On reste ensemble.</t>
-        </is>
-      </c>
-      <c r="AX60" t="inlineStr"/>
+          <t>narrateur|Nina marche vers les balançoires.
+narrateur|Les chaînes font un petit clin clin.
+narrateur|Le siège en bois est lisse et chaud.
+narrateur|Le vent passe dans les cheveux de Nina.
+narrateur|Le sac bleu est posé dans l'herbe.
+maman|On met le sac ici, à côté de la balançoire.
+papa|On met dans le sac ce que l'adulte a dit.
+narrateur|Nina touche la sangle lisse.
+narrateur|Elle sent le doudou à travers le tissu.
+enfant-f|Le sac est avec nous.
+maman|Très bien. On reste ensemble.
+narrateur|Au loin, un vélo passe tout doux.
+narrateur|L'air est frais sur les joues.</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11388,7 +11894,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Préparer son sac.</t>
+          <t>Nina prépare le sac. Que met-elle ?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -11548,10 +12054,10 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Préparer son sac.</t>
-        </is>
-      </c>
-      <c r="AX61" t="inlineStr"/>
+          <t>narrateur|Nina prépare le sac.
+narrateur|Que met-elle ?</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11576,7 +12082,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : mettre dans le sac. Jules respire. Jules retient : sac, ce que l'adulte a dit. On continue, avec maman.</t>
+          <t>Oui. Nina met les choses dans le sac. Tu as mis ce que j'ai dit. Bravo. On garde le sac près des balançoires. Nina entend encore le clin des chaînes.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11720,10 +12226,17 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : mettre dans le sac. Jules respire. Jules retient : sac, ce que l'adulte a dit. On continue, avec maman.</t>
-        </is>
-      </c>
-      <c r="AX62" t="inlineStr"/>
+          <t>narrateur|Oui. Nina met les choses dans le sac.
+maman|Tu as mis ce que j'ai dit. Bravo.
+papa|On garde le sac près des balançoires.
+narrateur|Nina entend encore le clin des chaînes.</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11748,7 +12261,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>Qu'est-ce qu'on met encore dans le sac ? On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -11912,10 +12425,10 @@
       <c r="AV63" s="2" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
-        </is>
-      </c>
-      <c r="AX63" t="inlineStr"/>
+          <t>papa|Qu'est-ce qu'on met encore dans le sac ?
+narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11940,7 +12453,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Jules a choisi le ballon. La couverture est douce. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Jules répète tout bas : sac, ce que l'adulte a dit. On range un objet. papa n'est pas loin.</t>
+          <t>Nina a choisi le ballon, près des balançoires. Il est rouge comme une pomme. On le met dans le sac, comme maman a dit. Nina ouvre, elle pousse, elle ferme. Bravo. Le ballon est à sa place. Dans le sac ! Les chaînes se taisent une seconde. On a mis ce que l'adulte a dit.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12080,10 +12593,21 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Jules a choisi le ballon. La couverture est douce. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Jules répète tout bas : sac, ce que l'adulte a dit. On range un objet. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr"/>
+          <t>narrateur|Nina a choisi le ballon, près des balançoires.
+narrateur|Il est rouge comme une pomme.
+papa|On le met dans le sac, comme maman a dit.
+narrateur|Nina ouvre, elle pousse, elle ferme.
+maman|Bravo. Le ballon est à sa place.
+enfant-f|Dans le sac !
+narrateur|Les chaînes se taisent une seconde.
+papa|On a mis ce que l'adulte a dit.</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12108,7 +12632,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Il reste une chose à mettre dans le sac. On peut prendre la gourde, le goûter, ou la casquette.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12276,10 +12800,10 @@
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
-        </is>
-      </c>
-      <c r="AX65" t="inlineStr"/>
+          <t>maman|Il reste une chose à mettre dans le sac.
+narrateur|On peut prendre la gourde, le goûter, ou la casquette.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12304,7 +12828,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint Tom. Les chaussures font toc toc. On se tient la main. Cette fin-là est celle de les balançoires, le ballon et Tom. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
+          <t>Nina prend la gourde. Elle est bleue. L'eau chante un peu dedans. La gourde, on la met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Le ballon fait une bosse dans le sac. Les chaînes des balançoires se taisent. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12444,10 +12968,26 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint Tom. Les chaussures font toc toc. On se tient la main. Cette fin-là est celle de les balançoires, le ballon et Tom. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX66" t="inlineStr"/>
+          <t>narrateur|Nina prend la gourde.
+narrateur|Elle est bleue.
+narrateur|L'eau chante un peu dedans.
+maman|La gourde, on la met dans le sac.
+narrateur|Nina l'écoute. Elle met la chose dans le sac.
+narrateur|C'est ce que l'adulte a dit.
+papa|Bravo. Tu as fait du bon travail.
+enfant-f|Le sac est prêt.
+narrateur|Le ballon fait une bosse dans le sac.
+narrateur|Les chaînes des balançoires se taisent.
+maman|On a mis ce qu'il fallait. On rentre ?
+papa|Oui. Le sac vient avec nous.
+narrateur|Nina dit merci. Les chaussures font toc toc.</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12472,7 +13012,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué vers les balançoires. Elle a mis le ballon dans le sac. Elle a mis la gourde aussi. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12612,10 +13152,16 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX67" t="inlineStr"/>
+          <t>narrateur|Nina a joué vers les balançoires.
+narrateur|Elle a mis le ballon dans le sac.
+narrateur|Elle a mis la gourde aussi.
+narrateur|Le sac est sur le dos, lourd et doux.
+maman|Merci, Nina. Tu as écouté.
+papa|Bravo. On rentre à la maison.
+narrateur|La fenêtre les attend, encore un peu embuée.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12640,7 +13186,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint Léa. La couverture est douce. On range un objet. Cette fin-là est celle de les balançoires, le ballon et Léa. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
+          <t>Nina prend le goûter. Il est dans un linge. Ça sent la pomme douce. Le goûter, on le met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Le ballon fait une bosse dans le sac. Les chaînes des balançoires se taisent. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12780,10 +13326,26 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint Léa. La couverture est douce. On range un objet. Cette fin-là est celle de les balançoires, le ballon et Léa. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX68" t="inlineStr"/>
+          <t>narrateur|Nina prend le goûter.
+narrateur|Il est dans un linge.
+narrateur|Ça sent la pomme douce.
+papa|Le goûter, on le met dans le sac.
+narrateur|Nina l'écoute. Elle met la chose dans le sac.
+narrateur|C'est ce que l'adulte a dit.
+maman|Bravo. Tu as fait du bon travail.
+enfant-f|Le sac est prêt.
+narrateur|Le ballon fait une bosse dans le sac.
+narrateur|Les chaînes des balançoires se taisent.
+maman|On a mis ce qu'il fallait. On rentre ?
+papa|Oui. Le sac vient avec nous.
+narrateur|Nina dit merci. Les chaussures font toc toc.</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12808,7 +13370,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué vers les balançoires. Elle a mis le ballon dans le sac. Elle a mis le goûter aussi. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12948,10 +13510,16 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX69" t="inlineStr"/>
+          <t>narrateur|Nina a joué vers les balançoires.
+narrateur|Elle a mis le ballon dans le sac.
+narrateur|Elle a mis le goûter aussi.
+narrateur|Le sac est sur le dos, lourd et doux.
+maman|Merci, Nina. Tu as écouté.
+papa|Bravo. On rentre à la maison.
+narrateur|La fenêtre les attend, encore un peu embuée.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12976,7 +13544,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint Sami. On entend un oiseau. On dit merci. Cette fin-là est celle de les balançoires, le ballon et Sami. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
+          <t>Nina prend la casquette. Elle est à visière. Le tissu est un peu rêche. La casquette, on la met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Le ballon fait une bosse dans le sac. Les chaînes des balançoires se taisent. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13116,10 +13684,26 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint Sami. On entend un oiseau. On dit merci. Cette fin-là est celle de les balançoires, le ballon et Sami. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX70" t="inlineStr"/>
+          <t>narrateur|Nina prend la casquette.
+narrateur|Elle est à visière.
+narrateur|Le tissu est un peu rêche.
+maman|La casquette, on la met dans le sac.
+narrateur|Nina l'écoute. Elle met la chose dans le sac.
+narrateur|C'est ce que l'adulte a dit.
+papa|Bravo. Tu as fait du bon travail.
+enfant-f|Le sac est prêt.
+narrateur|Le ballon fait une bosse dans le sac.
+narrateur|Les chaînes des balançoires se taisent.
+maman|On a mis ce qu'il fallait. On rentre ?
+papa|Oui. Le sac vient avec nous.
+narrateur|Nina dit merci. Les chaussures font toc toc.</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13144,7 +13728,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué vers les balançoires. Elle a mis le ballon dans le sac. Elle a mis la casquette aussi. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13284,10 +13868,16 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX71" t="inlineStr"/>
+          <t>narrateur|Nina a joué vers les balançoires.
+narrateur|Elle a mis le ballon dans le sac.
+narrateur|Elle a mis la casquette aussi.
+narrateur|Le sac est sur le dos, lourd et doux.
+maman|Merci, Nina. Tu as écouté.
+papa|Bravo. On rentre à la maison.
+narrateur|La fenêtre les attend, encore un peu embuée.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13312,7 +13902,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Jules a choisi le seau. On entend un oiseau. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Jules répète tout bas : sac, ce que l'adulte a dit. On dit merci. papa n'est pas loin.</t>
+          <t>Nina a choisi le seau, dans l'herbe. L'anse tape un peu contre le plastique. Le seau, on le met dans le sac. Nina le glisse à côté du livre. Tu as fini de ranger le seau ? Oui, papa. Bravo. Tu as fait du bon travail. Un oiseau répond, tout haut.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13452,10 +14042,16 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|Jules a choisi le seau. On entend un oiseau. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Jules répète tout bas : sac, ce que l'adulte a dit. On dit merci. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX72" t="inlineStr"/>
+          <t>narrateur|Nina a choisi le seau, dans l'herbe.
+narrateur|L'anse tape un peu contre le plastique.
+maman|Le seau, on le met dans le sac.
+narrateur|Nina le glisse à côté du livre.
+papa|Tu as fini de ranger le seau ?
+enfant-f|Oui, papa.
+maman|Bravo. Tu as fait du bon travail.
+narrateur|Un oiseau répond, tout haut.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13480,7 +14076,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Il reste une chose à mettre dans le sac. On peut prendre la gourde, le goûter, ou la casquette.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -13648,10 +14244,10 @@
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
-        </is>
-      </c>
-      <c r="AX73" t="inlineStr"/>
+          <t>maman|Il reste une chose à mettre dans le sac.
+narrateur|On peut prendre la gourde, le goûter, ou la casquette.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13676,7 +14272,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint Tom. La couverture est douce. On se tient la main. Cette fin-là est celle de les balançoires, le seau et Tom. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
+          <t>Nina prend la gourde. Elle est bleue. L'eau chante un peu dedans. La gourde, on la met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. L'anse du seau dépasse un tout petit peu. Les chaînes des balançoires se taisent. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13816,10 +14412,26 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint Tom. La couverture est douce. On se tient la main. Cette fin-là est celle de les balançoires, le seau et Tom. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX74" t="inlineStr"/>
+          <t>narrateur|Nina prend la gourde.
+narrateur|Elle est bleue.
+narrateur|L'eau chante un peu dedans.
+maman|La gourde, on la met dans le sac.
+narrateur|Nina l'écoute. Elle met la chose dans le sac.
+narrateur|C'est ce que l'adulte a dit.
+papa|Bravo. Tu as fait du bon travail.
+enfant-f|Le sac est prêt.
+narrateur|L'anse du seau dépasse un tout petit peu.
+narrateur|Les chaînes des balançoires se taisent.
+maman|On a mis ce qu'il fallait. On rentre ?
+papa|Oui. Le sac vient avec nous.
+narrateur|Nina dit merci. Les chaussures font toc toc.</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13844,7 +14456,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué vers les balançoires. Elle a mis le seau dans le sac. Elle a mis la gourde aussi. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -13984,10 +14596,16 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX75" t="inlineStr"/>
+          <t>narrateur|Nina a joué vers les balançoires.
+narrateur|Elle a mis le seau dans le sac.
+narrateur|Elle a mis la gourde aussi.
+narrateur|Le sac est sur le dos, lourd et doux.
+maman|Merci, Nina. Tu as écouté.
+papa|Bravo. On rentre à la maison.
+narrateur|La fenêtre les attend, encore un peu embuée.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14012,7 +14630,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint Léa. On entend un oiseau. On range un objet. Cette fin-là est celle de les balançoires, le seau et Léa. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
+          <t>Nina prend le goûter. Il est dans un linge. Ça sent la pomme douce. Le goûter, on le met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. L'anse du seau dépasse un tout petit peu. Les chaînes des balançoires se taisent. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14152,10 +14770,26 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint Léa. On entend un oiseau. On range un objet. Cette fin-là est celle de les balançoires, le seau et Léa. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX76" t="inlineStr"/>
+          <t>narrateur|Nina prend le goûter.
+narrateur|Il est dans un linge.
+narrateur|Ça sent la pomme douce.
+papa|Le goûter, on le met dans le sac.
+narrateur|Nina l'écoute. Elle met la chose dans le sac.
+narrateur|C'est ce que l'adulte a dit.
+maman|Bravo. Tu as fait du bon travail.
+enfant-f|Le sac est prêt.
+narrateur|L'anse du seau dépasse un tout petit peu.
+narrateur|Les chaînes des balançoires se taisent.
+maman|On a mis ce qu'il fallait. On rentre ?
+papa|Oui. Le sac vient avec nous.
+narrateur|Nina dit merci. Les chaussures font toc toc.</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14180,7 +14814,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué vers les balançoires. Elle a mis le seau dans le sac. Elle a mis le goûter aussi. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14320,10 +14954,16 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX77" t="inlineStr"/>
+          <t>narrateur|Nina a joué vers les balançoires.
+narrateur|Elle a mis le seau dans le sac.
+narrateur|Elle a mis le goûter aussi.
+narrateur|Le sac est sur le dos, lourd et doux.
+maman|Merci, Nina. Tu as écouté.
+papa|Bravo. On rentre à la maison.
+narrateur|La fenêtre les attend, encore un peu embuée.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14348,7 +14988,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint Sami. Ça sent le pain chaud. On dit merci. Cette fin-là est celle de les balançoires, le seau et Sami. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
+          <t>Nina prend la casquette. Elle est à visière. Le tissu est un peu rêche. La casquette, on la met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. L'anse du seau dépasse un tout petit peu. Les chaînes des balançoires se taisent. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14488,10 +15128,26 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint Sami. Ça sent le pain chaud. On dit merci. Cette fin-là est celle de les balançoires, le seau et Sami. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX78" t="inlineStr"/>
+          <t>narrateur|Nina prend la casquette.
+narrateur|Elle est à visière.
+narrateur|Le tissu est un peu rêche.
+maman|La casquette, on la met dans le sac.
+narrateur|Nina l'écoute. Elle met la chose dans le sac.
+narrateur|C'est ce que l'adulte a dit.
+papa|Bravo. Tu as fait du bon travail.
+enfant-f|Le sac est prêt.
+narrateur|L'anse du seau dépasse un tout petit peu.
+narrateur|Les chaînes des balançoires se taisent.
+maman|On a mis ce qu'il fallait. On rentre ?
+papa|Oui. Le sac vient avec nous.
+narrateur|Nina dit merci. Les chaussures font toc toc.</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14516,7 +15172,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué vers les balançoires. Elle a mis le seau dans le sac. Elle a mis la casquette aussi. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14656,10 +15312,16 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX79" t="inlineStr"/>
+          <t>narrateur|Nina a joué vers les balançoires.
+narrateur|Elle a mis le seau dans le sac.
+narrateur|Elle a mis la casquette aussi.
+narrateur|Le sac est sur le dos, lourd et doux.
+maman|Merci, Nina. Tu as écouté.
+papa|Bravo. On rentre à la maison.
+narrateur|La fenêtre les attend, encore un peu embuée.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14684,7 +15346,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Jules a choisi le doudou. Ça sent le pain chaud. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Jules répète tout bas : sac, ce que l'adulte a dit. On souffle doucement. papa n'est pas loin.</t>
+          <t>Nina a choisi le doudou, contre le sac. La couverture du doudou est douce. On le met dans le sac. C'est ce que l'adulte a dit. Nina le range. Elle appuie un peu. Bravo, Nina. Il est bien. Le vent sent l'herbe et le bois chaud. On souffle. Puis la dernière chose.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14824,10 +15486,16 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|Jules a choisi le doudou. Ça sent le pain chaud. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Jules répète tout bas : sac, ce que l'adulte a dit. On souffle doucement. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX80" t="inlineStr"/>
+          <t>narrateur|Nina a choisi le doudou, contre le sac.
+narrateur|La couverture du doudou est douce.
+papa|On le met dans le sac. C'est ce que l'adulte a dit.
+narrateur|Nina le range. Elle appuie un peu.
+maman|Bravo, Nina.
+enfant-f|Il est bien.
+narrateur|Le vent sent l'herbe et le bois chaud.
+papa|On souffle. Puis la dernière chose.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14852,7 +15520,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Il reste une chose à mettre dans le sac. On peut prendre la gourde, le goûter, ou la casquette.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -15020,10 +15688,10 @@
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
-        </is>
-      </c>
-      <c r="AX81" t="inlineStr"/>
+          <t>maman|Il reste une chose à mettre dans le sac.
+narrateur|On peut prendre la gourde, le goûter, ou la casquette.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15048,7 +15716,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint Tom. On entend un oiseau. On se tient la main. Cette fin-là est celle de les balançoires, le doudou et Tom. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
+          <t>Nina prend la gourde. Elle est bleue. L'eau chante un peu dedans. La gourde, on la met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Le doudou chauffe le fond du sac. Les chaînes des balançoires se taisent. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15188,10 +15856,26 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint Tom. On entend un oiseau. On se tient la main. Cette fin-là est celle de les balançoires, le doudou et Tom. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX82" t="inlineStr"/>
+          <t>narrateur|Nina prend la gourde.
+narrateur|Elle est bleue.
+narrateur|L'eau chante un peu dedans.
+maman|La gourde, on la met dans le sac.
+narrateur|Nina l'écoute. Elle met la chose dans le sac.
+narrateur|C'est ce que l'adulte a dit.
+papa|Bravo. Tu as fait du bon travail.
+enfant-f|Le sac est prêt.
+narrateur|Le doudou chauffe le fond du sac.
+narrateur|Les chaînes des balançoires se taisent.
+maman|On a mis ce qu'il fallait. On rentre ?
+papa|Oui. Le sac vient avec nous.
+narrateur|Nina dit merci. Les chaussures font toc toc.</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15216,7 +15900,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué vers les balançoires. Elle a mis le doudou dans le sac. Elle a mis la gourde aussi. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15356,10 +16040,16 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX83" t="inlineStr"/>
+          <t>narrateur|Nina a joué vers les balançoires.
+narrateur|Elle a mis le doudou dans le sac.
+narrateur|Elle a mis la gourde aussi.
+narrateur|Le sac est sur le dos, lourd et doux.
+maman|Merci, Nina. Tu as écouté.
+papa|Bravo. On rentre à la maison.
+narrateur|La fenêtre les attend, encore un peu embuée.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15384,7 +16074,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint Léa. Ça sent le pain chaud. On range un objet. Cette fin-là est celle de les balançoires, le doudou et Léa. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
+          <t>Nina prend le goûter. Il est dans un linge. Ça sent la pomme douce. Le goûter, on le met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Le doudou chauffe le fond du sac. Les chaînes des balançoires se taisent. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15524,10 +16214,26 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint Léa. Ça sent le pain chaud. On range un objet. Cette fin-là est celle de les balançoires, le doudou et Léa. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX84" t="inlineStr"/>
+          <t>narrateur|Nina prend le goûter.
+narrateur|Il est dans un linge.
+narrateur|Ça sent la pomme douce.
+papa|Le goûter, on le met dans le sac.
+narrateur|Nina l'écoute. Elle met la chose dans le sac.
+narrateur|C'est ce que l'adulte a dit.
+maman|Bravo. Tu as fait du bon travail.
+enfant-f|Le sac est prêt.
+narrateur|Le doudou chauffe le fond du sac.
+narrateur|Les chaînes des balançoires se taisent.
+maman|On a mis ce qu'il fallait. On rentre ?
+papa|Oui. Le sac vient avec nous.
+narrateur|Nina dit merci. Les chaussures font toc toc.</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15552,7 +16258,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué vers les balançoires. Elle a mis le doudou dans le sac. Elle a mis le goûter aussi. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15692,10 +16398,16 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX85" t="inlineStr"/>
+          <t>narrateur|Nina a joué vers les balançoires.
+narrateur|Elle a mis le doudou dans le sac.
+narrateur|Elle a mis le goûter aussi.
+narrateur|Le sac est sur le dos, lourd et doux.
+maman|Merci, Nina. Tu as écouté.
+papa|Bravo. On rentre à la maison.
+narrateur|La fenêtre les attend, encore un peu embuée.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15720,7 +16432,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint Sami. Le vent est doux. On dit merci. Cette fin-là est celle de les balançoires, le doudou et Sami. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
+          <t>Nina prend la casquette. Elle est à visière. Le tissu est un peu rêche. La casquette, on la met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Le doudou chauffe le fond du sac. Les chaînes des balançoires se taisent. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15860,10 +16572,26 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint Sami. Le vent est doux. On dit merci. Cette fin-là est celle de les balançoires, le doudou et Sami. Jules a appris : Préparer son sac. Voici le geste : mettre dans le sac. Jules a entendu : sac, ce que l'adulte a dit. Jules dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX86" t="inlineStr"/>
+          <t>narrateur|Nina prend la casquette.
+narrateur|Elle est à visière.
+narrateur|Le tissu est un peu rêche.
+maman|La casquette, on la met dans le sac.
+narrateur|Nina l'écoute. Elle met la chose dans le sac.
+narrateur|C'est ce que l'adulte a dit.
+papa|Bravo. Tu as fait du bon travail.
+enfant-f|Le sac est prêt.
+narrateur|Le doudou chauffe le fond du sac.
+narrateur|Les chaînes des balançoires se taisent.
+maman|On a mis ce qu'il fallait. On rentre ?
+papa|Oui. Le sac vient avec nous.
+narrateur|Nina dit merci. Les chaussures font toc toc.</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15888,7 +16616,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué vers les balançoires. Elle a mis le doudou dans le sac. Elle a mis la casquette aussi. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -16028,10 +16756,16 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX87" t="inlineStr"/>
+          <t>narrateur|Nina a joué vers les balançoires.
+narrateur|Elle a mis le doudou dans le sac.
+narrateur|Elle a mis la casquette aussi.
+narrateur|Le sac est sur le dos, lourd et doux.
+maman|Merci, Nina. Tu as écouté.
+papa|Bravo. On rentre à la maison.
+narrateur|La fenêtre les attend, encore un peu embuée.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -16050,7 +16784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16144,6 +16878,13 @@
       <c r="A13" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-AUT-015.xlsx
+++ b/stories/arbres/TREE-AUT-015.xlsx
@@ -1364,10 +1364,13 @@
 narrateur|Elle le met dans le sac, comme maman a dit.
 narrateur|Nina appuie sur la fermeture.
 narrateur|Ça fait zzz.
-papa|Bravo, Nina. Tu as fait du bon travail.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
 maman|Tu as mis ce que l'adulte a dit ?
-enfant-f|Oui, maman. Le sac est prêt.
-narrateur|Le sac est fermé. Il attend près de la fenêtre.</t>
+enfant-f|Oui, maman.
+enfant-f|Le sac est prêt.
+narrateur|Le sac est fermé.
+narrateur|Il attend près de la fenêtre.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1563,7 +1566,8 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>maman|On va au parc. Où va-t-on d'abord ?
+          <t>maman|On va au parc.
+maman|Où va-t-on d'abord ?
 narrateur|On peut aller au bac à sable, au toboggan, ou aux balançoires.</t>
         </is>
       </c>
@@ -1737,11 +1741,13 @@
 narrateur|Le bois du rebord sent le soleil.
 narrateur|Le sac bleu est posé contre le rebord.
 maman|On pose le sac ici, près de nous.
-papa|Tu te souviens ? On met dans le sac ce que l'adulte a dit.
+papa|Tu te souviens ?
+papa|On met dans le sac ce que l'adulte a dit.
 narrateur|Nina ouvre un peu le sac.
 narrateur|Elle vérifie le doudou et le livre.
 enfant-f|Ils sont dans le sac.
-maman|Bravo. Tu as écouté.
+maman|Bravo.
+maman|Tu as écouté.
 narrateur|Un oiseau chante tout près.
 narrateur|Le vent soulève un peu de sable clair.</t>
         </is>
@@ -2107,10 +2113,14 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Nina met dans le sac ce que l'adulte a dit.
-maman|Bravo. C'est ça.
-papa|On continue. Le sac reste avec nous.
-narrateur|Nina respire. Le sable est froid sous ses mains.</t>
+          <t>narrateur|Oui.
+narrateur|Nina met dans le sac ce que l'adulte a dit.
+maman|Bravo.
+maman|C'est ça.
+papa|On continue.
+papa|Le sac reste avec nous.
+narrateur|Nina respire.
+narrateur|Le sable est froid sous ses mains.</t>
         </is>
       </c>
     </row>
@@ -2475,7 +2485,8 @@
 maman|Le ballon, on le met dans le sac.
 narrateur|Nina pousse le ballon dans l'ouverture.
 narrateur|Le sac devient tout rond.
-papa|Bravo. Tu as mis ce que l'adulte a dit.
+papa|Bravo.
+papa|Tu as mis ce que l'adulte a dit.
 enfant-f|Le ballon est dans le sac.
 narrateur|Un peu d'eau goutte d'un robinet, tout près.</t>
         </is>
@@ -2700,7 +2711,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Nina prend la gourde. Elle est bleue. L'eau chante un peu dedans. La gourde, on la met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Le ballon fait une bosse dans le sac. Le sable reste froid sous les chaussures. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
+          <t>Nina prend la gourde. Elle est bleue. L'eau chante un peu dedans. La gourde, on la met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Un grain de sable reste collé au sac. Le ballon fait une bosse dans le sac. Le sable reste froid sous les chaussures. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2844,15 +2855,21 @@
 narrateur|Elle est bleue.
 narrateur|L'eau chante un peu dedans.
 maman|La gourde, on la met dans le sac.
-narrateur|Nina l'écoute. Elle met la chose dans le sac.
+narrateur|Nina l'écoute.
+narrateur|Elle met la chose dans le sac.
 narrateur|C'est ce que l'adulte a dit.
-papa|Bravo. Tu as fait du bon travail.
+papa|Bravo.
+papa|Tu as fait du bon travail.
 enfant-f|Le sac est prêt.
+narrateur|Un grain de sable reste collé au sac.
 narrateur|Le ballon fait une bosse dans le sac.
 narrateur|Le sable reste froid sous les chaussures.
-maman|On a mis ce qu'il fallait. On rentre ?
-papa|Oui. Le sac vient avec nous.
-narrateur|Nina dit merci. Les chaussures font toc toc.</t>
+maman|On a mis ce qu'il fallait.
+maman|On rentre ?
+papa|Oui.
+papa|Le sac vient avec nous.
+narrateur|Nina dit merci.
+narrateur|Les chaussures font toc toc.</t>
         </is>
       </c>
     </row>
@@ -2879,7 +2896,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Nina a joué vers le bac à sable. Elle a mis le ballon dans le sac. Elle a mis la gourde aussi. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
+          <t>Nina a joué au bac à sable. Elle a mis le ballon dans le sac. Elle a mis la gourde aussi. Un grain de sable reste collé au sac. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3019,12 +3036,15 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|Nina a joué vers le bac à sable.
+          <t>narrateur|Nina a joué au bac à sable.
 narrateur|Elle a mis le ballon dans le sac.
 narrateur|Elle a mis la gourde aussi.
+narrateur|Un grain de sable reste collé au sac.
 narrateur|Le sac est sur le dos, lourd et doux.
-maman|Merci, Nina. Tu as écouté.
-papa|Bravo. On rentre à la maison.
+maman|Merci, Nina.
+maman|Tu as écouté.
+papa|Bravo.
+papa|On rentre à la maison.
 narrateur|La fenêtre les attend, encore un peu embuée.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -3053,7 +3073,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Nina prend le goûter. Il est dans un linge. Ça sent la pomme douce. Le goûter, on le met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Le ballon fait une bosse dans le sac. Le sable reste froid sous les chaussures. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
+          <t>Nina prend le goûter. Il est dans un linge. Ça sent la pomme douce. Le goûter, on le met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Une fourmi traverse le rebord de bois. Le ballon fait une bosse dans le sac. Le sable reste froid sous les chaussures. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3197,15 +3217,21 @@
 narrateur|Il est dans un linge.
 narrateur|Ça sent la pomme douce.
 papa|Le goûter, on le met dans le sac.
-narrateur|Nina l'écoute. Elle met la chose dans le sac.
+narrateur|Nina l'écoute.
+narrateur|Elle met la chose dans le sac.
 narrateur|C'est ce que l'adulte a dit.
-maman|Bravo. Tu as fait du bon travail.
+maman|Bravo.
+maman|Tu as fait du bon travail.
 enfant-f|Le sac est prêt.
+narrateur|Une fourmi traverse le rebord de bois.
 narrateur|Le ballon fait une bosse dans le sac.
 narrateur|Le sable reste froid sous les chaussures.
-maman|On a mis ce qu'il fallait. On rentre ?
-papa|Oui. Le sac vient avec nous.
-narrateur|Nina dit merci. Les chaussures font toc toc.</t>
+maman|On a mis ce qu'il fallait.
+maman|On rentre ?
+papa|Oui.
+papa|Le sac vient avec nous.
+narrateur|Nina dit merci.
+narrateur|Les chaussures font toc toc.</t>
         </is>
       </c>
     </row>
@@ -3232,7 +3258,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Nina a joué vers le bac à sable. Elle a mis le ballon dans le sac. Elle a mis le goûter aussi. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
+          <t>Nina a joué au bac à sable. Elle a mis le ballon dans le sac. Elle a mis le goûter aussi. Une fourmi traverse le rebord de bois. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3372,12 +3398,15 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|Nina a joué vers le bac à sable.
+          <t>narrateur|Nina a joué au bac à sable.
 narrateur|Elle a mis le ballon dans le sac.
 narrateur|Elle a mis le goûter aussi.
+narrateur|Une fourmi traverse le rebord de bois.
 narrateur|Le sac est sur le dos, lourd et doux.
-maman|Merci, Nina. Tu as écouté.
-papa|Bravo. On rentre à la maison.
+maman|Merci, Nina.
+maman|Tu as écouté.
+papa|Bravo.
+papa|On rentre à la maison.
 narrateur|La fenêtre les attend, encore un peu embuée.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -3406,7 +3435,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Nina prend la casquette. Elle est à visière. Le tissu est un peu rêche. La casquette, on la met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Le ballon fait une bosse dans le sac. Le sable reste froid sous les chaussures. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
+          <t>Nina prend la casquette. Elle est à visière. Le tissu est un peu rêche. La casquette, on la met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Le vent pousse un peu de poussière claire. Le ballon fait une bosse dans le sac. Le sable reste froid sous les chaussures. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3550,15 +3579,21 @@
 narrateur|Elle est à visière.
 narrateur|Le tissu est un peu rêche.
 maman|La casquette, on la met dans le sac.
-narrateur|Nina l'écoute. Elle met la chose dans le sac.
+narrateur|Nina l'écoute.
+narrateur|Elle met la chose dans le sac.
 narrateur|C'est ce que l'adulte a dit.
-papa|Bravo. Tu as fait du bon travail.
+papa|Bravo.
+papa|Tu as fait du bon travail.
 enfant-f|Le sac est prêt.
+narrateur|Le vent pousse un peu de poussière claire.
 narrateur|Le ballon fait une bosse dans le sac.
 narrateur|Le sable reste froid sous les chaussures.
-maman|On a mis ce qu'il fallait. On rentre ?
-papa|Oui. Le sac vient avec nous.
-narrateur|Nina dit merci. Les chaussures font toc toc.</t>
+maman|On a mis ce qu'il fallait.
+maman|On rentre ?
+papa|Oui.
+papa|Le sac vient avec nous.
+narrateur|Nina dit merci.
+narrateur|Les chaussures font toc toc.</t>
         </is>
       </c>
     </row>
@@ -3585,7 +3620,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Nina a joué vers le bac à sable. Elle a mis le ballon dans le sac. Elle a mis la casquette aussi. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
+          <t>Nina a joué au bac à sable. Elle a mis le ballon dans le sac. Elle a mis la casquette aussi. Le vent pousse un peu de poussière claire. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3725,12 +3760,15 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|Nina a joué vers le bac à sable.
+          <t>narrateur|Nina a joué au bac à sable.
 narrateur|Elle a mis le ballon dans le sac.
 narrateur|Elle a mis la casquette aussi.
+narrateur|Le vent pousse un peu de poussière claire.
 narrateur|Le sac est sur le dos, lourd et doux.
-maman|Merci, Nina. Tu as écouté.
-papa|Bravo. On rentre à la maison.
+maman|Merci, Nina.
+maman|Tu as écouté.
+papa|Bravo.
+papa|On rentre à la maison.
 narrateur|La fenêtre les attend, encore un peu embuée.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -3900,13 +3938,16 @@
       <c r="AW16" t="inlineStr">
         <is>
           <t>narrateur|Nina a choisi le seau.
-narrateur|Il est jaune. L'anse est un peu rêche.
+narrateur|Il est jaune.
+narrateur|L'anse est un peu rêche.
 narrateur|Il y a du sable au fond, tout fin.
 papa|Le seau, on le met dans le sac aussi.
 narrateur|Nina le glisse à côté du doudou.
 maman|Tu as fini de mettre le seau ?
-enfant-f|Oui. Il est dans le sac.
-papa|Bravo, Nina. Bon travail.
+enfant-f|Oui.
+enfant-f|Il est dans le sac.
+papa|Bravo, Nina.
+papa|Bon travail.
 narrateur|Un vélo passe au loin, tout léger.</t>
         </is>
       </c>
@@ -4135,7 +4176,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Nina prend la gourde. Elle est bleue. L'eau chante un peu dedans. La gourde, on la met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. L'anse du seau dépasse un tout petit peu. Le sable reste froid sous les chaussures. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
+          <t>Nina prend la gourde. Elle est bleue. L'eau chante un peu dedans. La gourde, on la met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Une feuille sèche tourne près des pieds. L'anse du seau dépasse un tout petit peu. Le sable reste froid sous les chaussures. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4279,15 +4320,21 @@
 narrateur|Elle est bleue.
 narrateur|L'eau chante un peu dedans.
 maman|La gourde, on la met dans le sac.
-narrateur|Nina l'écoute. Elle met la chose dans le sac.
+narrateur|Nina l'écoute.
+narrateur|Elle met la chose dans le sac.
 narrateur|C'est ce que l'adulte a dit.
-papa|Bravo. Tu as fait du bon travail.
+papa|Bravo.
+papa|Tu as fait du bon travail.
 enfant-f|Le sac est prêt.
+narrateur|Une feuille sèche tourne près des pieds.
 narrateur|L'anse du seau dépasse un tout petit peu.
 narrateur|Le sable reste froid sous les chaussures.
-maman|On a mis ce qu'il fallait. On rentre ?
-papa|Oui. Le sac vient avec nous.
-narrateur|Nina dit merci. Les chaussures font toc toc.</t>
+maman|On a mis ce qu'il fallait.
+maman|On rentre ?
+papa|Oui.
+papa|Le sac vient avec nous.
+narrateur|Nina dit merci.
+narrateur|Les chaussures font toc toc.</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4361,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Nina a joué vers le bac à sable. Elle a mis le seau dans le sac. Elle a mis la gourde aussi. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
+          <t>Nina a joué au bac à sable. Elle a mis le seau dans le sac. Elle a mis la gourde aussi. Une feuille sèche tourne près des pieds. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4454,12 +4501,15 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|Nina a joué vers le bac à sable.
+          <t>narrateur|Nina a joué au bac à sable.
 narrateur|Elle a mis le seau dans le sac.
 narrateur|Elle a mis la gourde aussi.
+narrateur|Une feuille sèche tourne près des pieds.
 narrateur|Le sac est sur le dos, lourd et doux.
-maman|Merci, Nina. Tu as écouté.
-papa|Bravo. On rentre à la maison.
+maman|Merci, Nina.
+maman|Tu as écouté.
+papa|Bravo.
+papa|On rentre à la maison.
 narrateur|La fenêtre les attend, encore un peu embuée.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -4488,7 +4538,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Nina prend le goûter. Il est dans un linge. Ça sent la pomme douce. Le goûter, on le met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. L'anse du seau dépasse un tout petit peu. Le sable reste froid sous les chaussures. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
+          <t>Nina prend le goûter. Il est dans un linge. Ça sent la pomme douce. Le goûter, on le met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Un oiseau saute sur le grillage. L'anse du seau dépasse un tout petit peu. Le sable reste froid sous les chaussures. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4632,15 +4682,21 @@
 narrateur|Il est dans un linge.
 narrateur|Ça sent la pomme douce.
 papa|Le goûter, on le met dans le sac.
-narrateur|Nina l'écoute. Elle met la chose dans le sac.
+narrateur|Nina l'écoute.
+narrateur|Elle met la chose dans le sac.
 narrateur|C'est ce que l'adulte a dit.
-maman|Bravo. Tu as fait du bon travail.
+maman|Bravo.
+maman|Tu as fait du bon travail.
 enfant-f|Le sac est prêt.
+narrateur|Un oiseau saute sur le grillage.
 narrateur|L'anse du seau dépasse un tout petit peu.
 narrateur|Le sable reste froid sous les chaussures.
-maman|On a mis ce qu'il fallait. On rentre ?
-papa|Oui. Le sac vient avec nous.
-narrateur|Nina dit merci. Les chaussures font toc toc.</t>
+maman|On a mis ce qu'il fallait.
+maman|On rentre ?
+papa|Oui.
+papa|Le sac vient avec nous.
+narrateur|Nina dit merci.
+narrateur|Les chaussures font toc toc.</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4723,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Nina a joué vers le bac à sable. Elle a mis le seau dans le sac. Elle a mis le goûter aussi. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
+          <t>Nina a joué au bac à sable. Elle a mis le seau dans le sac. Elle a mis le goûter aussi. Un oiseau saute sur le grillage. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4807,12 +4863,15 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|Nina a joué vers le bac à sable.
+          <t>narrateur|Nina a joué au bac à sable.
 narrateur|Elle a mis le seau dans le sac.
 narrateur|Elle a mis le goûter aussi.
+narrateur|Un oiseau saute sur le grillage.
 narrateur|Le sac est sur le dos, lourd et doux.
-maman|Merci, Nina. Tu as écouté.
-papa|Bravo. On rentre à la maison.
+maman|Merci, Nina.
+maman|Tu as écouté.
+papa|Bravo.
+papa|On rentre à la maison.
 narrateur|La fenêtre les attend, encore un peu embuée.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -4841,7 +4900,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Nina prend la casquette. Elle est à visière. Le tissu est un peu rêche. La casquette, on la met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. L'anse du seau dépasse un tout petit peu. Le sable reste froid sous les chaussures. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
+          <t>Nina prend la casquette. Elle est à visière. Le tissu est un peu rêche. La casquette, on la met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Le soleil chauffe la sangle bleue. L'anse du seau dépasse un tout petit peu. Le sable reste froid sous les chaussures. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4985,15 +5044,21 @@
 narrateur|Elle est à visière.
 narrateur|Le tissu est un peu rêche.
 maman|La casquette, on la met dans le sac.
-narrateur|Nina l'écoute. Elle met la chose dans le sac.
+narrateur|Nina l'écoute.
+narrateur|Elle met la chose dans le sac.
 narrateur|C'est ce que l'adulte a dit.
-papa|Bravo. Tu as fait du bon travail.
+papa|Bravo.
+papa|Tu as fait du bon travail.
 enfant-f|Le sac est prêt.
+narrateur|Le soleil chauffe la sangle bleue.
 narrateur|L'anse du seau dépasse un tout petit peu.
 narrateur|Le sable reste froid sous les chaussures.
-maman|On a mis ce qu'il fallait. On rentre ?
-papa|Oui. Le sac vient avec nous.
-narrateur|Nina dit merci. Les chaussures font toc toc.</t>
+maman|On a mis ce qu'il fallait.
+maman|On rentre ?
+papa|Oui.
+papa|Le sac vient avec nous.
+narrateur|Nina dit merci.
+narrateur|Les chaussures font toc toc.</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5085,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Nina a joué vers le bac à sable. Elle a mis le seau dans le sac. Elle a mis la casquette aussi. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
+          <t>Nina a joué au bac à sable. Elle a mis le seau dans le sac. Elle a mis la casquette aussi. Le soleil chauffe la sangle bleue. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -5160,12 +5225,15 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|Nina a joué vers le bac à sable.
+          <t>narrateur|Nina a joué au bac à sable.
 narrateur|Elle a mis le seau dans le sac.
 narrateur|Elle a mis la casquette aussi.
+narrateur|Le soleil chauffe la sangle bleue.
 narrateur|Le sac est sur le dos, lourd et doux.
-maman|Merci, Nina. Tu as écouté.
-papa|Bravo. On rentre à la maison.
+maman|Merci, Nina.
+maman|Tu as écouté.
+papa|Bravo.
+papa|On rentre à la maison.
 narrateur|La fenêtre les attend, encore un peu embuée.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -5337,12 +5405,15 @@
           <t>narrateur|Nina a choisi le doudou.
 narrateur|Il est déjà un peu dans le sac.
 narrateur|Nina le pousse bien au fond, tout doux.
-maman|Le doudou reste dans le sac. Comme j'ai dit.
+maman|Le doudou reste dans le sac.
+maman|Comme j'ai dit.
 narrateur|Le tissu sent la maison.
-papa|Bravo. Tu as mis ce que l'adulte a dit.
+papa|Bravo.
+papa|Tu as mis ce que l'adulte a dit.
 enfant-f|Mon doudou est prêt.
 narrateur|La lumière est claire sur le tissu bleu.
-maman|On souffle un peu. Puis on continue.</t>
+maman|On souffle un peu.
+maman|Puis on continue.</t>
         </is>
       </c>
     </row>
@@ -5565,7 +5636,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Nina prend la gourde. Elle est bleue. L'eau chante un peu dedans. La gourde, on la met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Le doudou chauffe le fond du sac. Le sable reste froid sous les chaussures. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
+          <t>Nina prend la gourde. Elle est bleue. L'eau chante un peu dedans. La gourde, on la met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Une flaque reflète le sac ouvert. Le doudou chauffe le fond du sac. Le sable reste froid sous les chaussures. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5709,15 +5780,21 @@
 narrateur|Elle est bleue.
 narrateur|L'eau chante un peu dedans.
 maman|La gourde, on la met dans le sac.
-narrateur|Nina l'écoute. Elle met la chose dans le sac.
+narrateur|Nina l'écoute.
+narrateur|Elle met la chose dans le sac.
 narrateur|C'est ce que l'adulte a dit.
-papa|Bravo. Tu as fait du bon travail.
+papa|Bravo.
+papa|Tu as fait du bon travail.
 enfant-f|Le sac est prêt.
+narrateur|Une flaque reflète le sac ouvert.
 narrateur|Le doudou chauffe le fond du sac.
 narrateur|Le sable reste froid sous les chaussures.
-maman|On a mis ce qu'il fallait. On rentre ?
-papa|Oui. Le sac vient avec nous.
-narrateur|Nina dit merci. Les chaussures font toc toc.</t>
+maman|On a mis ce qu'il fallait.
+maman|On rentre ?
+papa|Oui.
+papa|Le sac vient avec nous.
+narrateur|Nina dit merci.
+narrateur|Les chaussures font toc toc.</t>
         </is>
       </c>
     </row>
@@ -5744,7 +5821,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Nina a joué vers le bac à sable. Elle a mis le doudou dans le sac. Elle a mis la gourde aussi. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
+          <t>Nina a joué au bac à sable. Elle a mis le doudou dans le sac. Elle a mis la gourde aussi. Une flaque reflète le sac ouvert. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5884,12 +5961,15 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|Nina a joué vers le bac à sable.
+          <t>narrateur|Nina a joué au bac à sable.
 narrateur|Elle a mis le doudou dans le sac.
 narrateur|Elle a mis la gourde aussi.
+narrateur|Une flaque reflète le sac ouvert.
 narrateur|Le sac est sur le dos, lourd et doux.
-maman|Merci, Nina. Tu as écouté.
-papa|Bravo. On rentre à la maison.
+maman|Merci, Nina.
+maman|Tu as écouté.
+papa|Bravo.
+papa|On rentre à la maison.
 narrateur|La fenêtre les attend, encore un peu embuée.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -5918,7 +5998,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Nina prend le goûter. Il est dans un linge. Ça sent la pomme douce. Le goûter, on le met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Le doudou chauffe le fond du sac. Le sable reste froid sous les chaussures. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
+          <t>Nina prend le goûter. Il est dans un linge. Ça sent la pomme douce. Le goûter, on le met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Le bois du banc est tout strié. Le doudou chauffe le fond du sac. Le sable reste froid sous les chaussures. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -6062,15 +6142,21 @@
 narrateur|Il est dans un linge.
 narrateur|Ça sent la pomme douce.
 papa|Le goûter, on le met dans le sac.
-narrateur|Nina l'écoute. Elle met la chose dans le sac.
+narrateur|Nina l'écoute.
+narrateur|Elle met la chose dans le sac.
 narrateur|C'est ce que l'adulte a dit.
-maman|Bravo. Tu as fait du bon travail.
+maman|Bravo.
+maman|Tu as fait du bon travail.
 enfant-f|Le sac est prêt.
+narrateur|Le bois du banc est tout strié.
 narrateur|Le doudou chauffe le fond du sac.
 narrateur|Le sable reste froid sous les chaussures.
-maman|On a mis ce qu'il fallait. On rentre ?
-papa|Oui. Le sac vient avec nous.
-narrateur|Nina dit merci. Les chaussures font toc toc.</t>
+maman|On a mis ce qu'il fallait.
+maman|On rentre ?
+papa|Oui.
+papa|Le sac vient avec nous.
+narrateur|Nina dit merci.
+narrateur|Les chaussures font toc toc.</t>
         </is>
       </c>
     </row>
@@ -6097,7 +6183,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Nina a joué vers le bac à sable. Elle a mis le doudou dans le sac. Elle a mis le goûter aussi. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
+          <t>Nina a joué au bac à sable. Elle a mis le doudou dans le sac. Elle a mis le goûter aussi. Le bois du banc est tout strié. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6237,12 +6323,15 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|Nina a joué vers le bac à sable.
+          <t>narrateur|Nina a joué au bac à sable.
 narrateur|Elle a mis le doudou dans le sac.
 narrateur|Elle a mis le goûter aussi.
+narrateur|Le bois du banc est tout strié.
 narrateur|Le sac est sur le dos, lourd et doux.
-maman|Merci, Nina. Tu as écouté.
-papa|Bravo. On rentre à la maison.
+maman|Merci, Nina.
+maman|Tu as écouté.
+papa|Bravo.
+papa|On rentre à la maison.
 narrateur|La fenêtre les attend, encore un peu embuée.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -6271,7 +6360,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Nina prend la casquette. Elle est à visière. Le tissu est un peu rêche. La casquette, on la met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Le doudou chauffe le fond du sac. Le sable reste froid sous les chaussures. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
+          <t>Nina prend la casquette. Elle est à visière. Le tissu est un peu rêche. La casquette, on la met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Un papillon passe, tout jaune. Le doudou chauffe le fond du sac. Le sable reste froid sous les chaussures. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6415,15 +6504,21 @@
 narrateur|Elle est à visière.
 narrateur|Le tissu est un peu rêche.
 maman|La casquette, on la met dans le sac.
-narrateur|Nina l'écoute. Elle met la chose dans le sac.
+narrateur|Nina l'écoute.
+narrateur|Elle met la chose dans le sac.
 narrateur|C'est ce que l'adulte a dit.
-papa|Bravo. Tu as fait du bon travail.
+papa|Bravo.
+papa|Tu as fait du bon travail.
 enfant-f|Le sac est prêt.
+narrateur|Un papillon passe, tout jaune.
 narrateur|Le doudou chauffe le fond du sac.
 narrateur|Le sable reste froid sous les chaussures.
-maman|On a mis ce qu'il fallait. On rentre ?
-papa|Oui. Le sac vient avec nous.
-narrateur|Nina dit merci. Les chaussures font toc toc.</t>
+maman|On a mis ce qu'il fallait.
+maman|On rentre ?
+papa|Oui.
+papa|Le sac vient avec nous.
+narrateur|Nina dit merci.
+narrateur|Les chaussures font toc toc.</t>
         </is>
       </c>
     </row>
@@ -6450,7 +6545,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Nina a joué vers le bac à sable. Elle a mis le doudou dans le sac. Elle a mis la casquette aussi. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
+          <t>Nina a joué au bac à sable. Elle a mis le doudou dans le sac. Elle a mis la casquette aussi. Un papillon passe, tout jaune. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6590,12 +6685,15 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|Nina a joué vers le bac à sable.
+          <t>narrateur|Nina a joué au bac à sable.
 narrateur|Elle a mis le doudou dans le sac.
 narrateur|Elle a mis la casquette aussi.
+narrateur|Un papillon passe, tout jaune.
 narrateur|Le sac est sur le dos, lourd et doux.
-maman|Merci, Nina. Tu as écouté.
-papa|Bravo. On rentre à la maison.
+maman|Merci, Nina.
+maman|Tu as écouté.
+papa|Bravo.
+papa|On rentre à la maison.
 narrateur|La fenêtre les attend, encore un peu embuée.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -6774,7 +6872,8 @@
 narrateur|Nina ouvre le sac.
 narrateur|Elle voit le doudou et le livre.
 enfant-f|C'est dans le sac.
-papa|Bravo, Nina. Tu as fait du bon travail.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
 narrateur|Une feuille sèche tourne sur le sol.
 narrateur|Ça sent l'herbe coupée.</t>
         </is>
@@ -7140,9 +7239,12 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui. On met dans le sac ce que l'adulte a dit.
-papa|Bravo, Nina. Tu as écouté.
-maman|Le sac est prêt. On peut jouer un peu.
+          <t>narrateur|Oui.
+narrateur|On met dans le sac ce que l'adulte a dit.
+papa|Bravo, Nina.
+papa|Tu as écouté.
+maman|Le sac est prêt.
+maman|On peut jouer un peu.
 narrateur|Nina pose la main sur la sangle lisse.</t>
         </is>
       </c>
@@ -7507,10 +7609,12 @@
 maman|On le met dans le sac, maintenant.
 narrateur|Nina le prend à deux mains.
 narrateur|Elle le glisse dans le sac bleu.
-papa|C'est ce que l'adulte a dit. Bravo.
+papa|C'est ce que l'adulte a dit.
+papa|Bravo.
 enfant-f|Le ballon est avec le livre.
 narrateur|Il y a des miettes de goûter sur une table basse.
-maman|On range. Le sac reste fermé.</t>
+maman|On range.
+maman|Le sac reste fermé.</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
@@ -7738,7 +7842,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Nina prend la gourde. Elle est bleue. L'eau chante un peu dedans. La gourde, on la met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Le ballon fait une bosse dans le sac. Le toboggan brille encore derrière eux. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
+          <t>Nina prend la gourde. Elle est bleue. L'eau chante un peu dedans. La gourde, on la met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. La terre sent l'eau de la nuit. Le ballon fait une bosse dans le sac. Le toboggan brille encore derrière eux. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7882,15 +7986,21 @@
 narrateur|Elle est bleue.
 narrateur|L'eau chante un peu dedans.
 maman|La gourde, on la met dans le sac.
-narrateur|Nina l'écoute. Elle met la chose dans le sac.
+narrateur|Nina l'écoute.
+narrateur|Elle met la chose dans le sac.
 narrateur|C'est ce que l'adulte a dit.
-papa|Bravo. Tu as fait du bon travail.
+papa|Bravo.
+papa|Tu as fait du bon travail.
 enfant-f|Le sac est prêt.
+narrateur|La terre sent l'eau de la nuit.
 narrateur|Le ballon fait une bosse dans le sac.
 narrateur|Le toboggan brille encore derrière eux.
-maman|On a mis ce qu'il fallait. On rentre ?
-papa|Oui. Le sac vient avec nous.
-narrateur|Nina dit merci. Les chaussures font toc toc.</t>
+maman|On a mis ce qu'il fallait.
+maman|On rentre ?
+papa|Oui.
+papa|Le sac vient avec nous.
+narrateur|Nina dit merci.
+narrateur|Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
@@ -7922,7 +8032,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Nina a joué vers le toboggan. Elle a mis le ballon dans le sac. Elle a mis la gourde aussi. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
+          <t>Nina a joué près du toboggan. Elle a mis le ballon dans le sac. Elle a mis la gourde aussi. La terre sent l'eau de la nuit. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -8062,12 +8172,15 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|Nina a joué vers le toboggan.
+          <t>narrateur|Nina a joué près du toboggan.
 narrateur|Elle a mis le ballon dans le sac.
 narrateur|Elle a mis la gourde aussi.
+narrateur|La terre sent l'eau de la nuit.
 narrateur|Le sac est sur le dos, lourd et doux.
-maman|Merci, Nina. Tu as écouté.
-papa|Bravo. On rentre à la maison.
+maman|Merci, Nina.
+maman|Tu as écouté.
+papa|Bravo.
+papa|On rentre à la maison.
 narrateur|La fenêtre les attend, encore un peu embuée.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -8096,7 +8209,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Nina prend le goûter. Il est dans un linge. Ça sent la pomme douce. Le goûter, on le met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Le ballon fait une bosse dans le sac. Le toboggan brille encore derrière eux. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
+          <t>Nina prend le goûter. Il est dans un linge. Ça sent la pomme douce. Le goûter, on le met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Un caillou tapote le seau. Le ballon fait une bosse dans le sac. Le toboggan brille encore derrière eux. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -8240,15 +8353,21 @@
 narrateur|Il est dans un linge.
 narrateur|Ça sent la pomme douce.
 papa|Le goûter, on le met dans le sac.
-narrateur|Nina l'écoute. Elle met la chose dans le sac.
+narrateur|Nina l'écoute.
+narrateur|Elle met la chose dans le sac.
 narrateur|C'est ce que l'adulte a dit.
-maman|Bravo. Tu as fait du bon travail.
+maman|Bravo.
+maman|Tu as fait du bon travail.
 enfant-f|Le sac est prêt.
+narrateur|Un caillou tapote le seau.
 narrateur|Le ballon fait une bosse dans le sac.
 narrateur|Le toboggan brille encore derrière eux.
-maman|On a mis ce qu'il fallait. On rentre ?
-papa|Oui. Le sac vient avec nous.
-narrateur|Nina dit merci. Les chaussures font toc toc.</t>
+maman|On a mis ce qu'il fallait.
+maman|On rentre ?
+papa|Oui.
+papa|Le sac vient avec nous.
+narrateur|Nina dit merci.
+narrateur|Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
@@ -8280,7 +8399,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Nina a joué vers le toboggan. Elle a mis le ballon dans le sac. Elle a mis le goûter aussi. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
+          <t>Nina a joué près du toboggan. Elle a mis le ballon dans le sac. Elle a mis le goûter aussi. Un caillou tapote le seau. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8420,12 +8539,15 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|Nina a joué vers le toboggan.
+          <t>narrateur|Nina a joué près du toboggan.
 narrateur|Elle a mis le ballon dans le sac.
 narrateur|Elle a mis le goûter aussi.
+narrateur|Un caillou tapote le seau.
 narrateur|Le sac est sur le dos, lourd et doux.
-maman|Merci, Nina. Tu as écouté.
-papa|Bravo. On rentre à la maison.
+maman|Merci, Nina.
+maman|Tu as écouté.
+papa|Bravo.
+papa|On rentre à la maison.
 narrateur|La fenêtre les attend, encore un peu embuée.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -8454,7 +8576,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Nina prend la casquette. Elle est à visière. Le tissu est un peu rêche. La casquette, on la met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Le ballon fait une bosse dans le sac. Le toboggan brille encore derrière eux. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
+          <t>Nina prend la casquette. Elle est à visière. Le tissu est un peu rêche. La casquette, on la met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Le toboggan claque tout doux au vent. Le ballon fait une bosse dans le sac. Le toboggan brille encore derrière eux. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8598,15 +8720,21 @@
 narrateur|Elle est à visière.
 narrateur|Le tissu est un peu rêche.
 maman|La casquette, on la met dans le sac.
-narrateur|Nina l'écoute. Elle met la chose dans le sac.
+narrateur|Nina l'écoute.
+narrateur|Elle met la chose dans le sac.
 narrateur|C'est ce que l'adulte a dit.
-papa|Bravo. Tu as fait du bon travail.
+papa|Bravo.
+papa|Tu as fait du bon travail.
 enfant-f|Le sac est prêt.
+narrateur|Le toboggan claque tout doux au vent.
 narrateur|Le ballon fait une bosse dans le sac.
 narrateur|Le toboggan brille encore derrière eux.
-maman|On a mis ce qu'il fallait. On rentre ?
-papa|Oui. Le sac vient avec nous.
-narrateur|Nina dit merci. Les chaussures font toc toc.</t>
+maman|On a mis ce qu'il fallait.
+maman|On rentre ?
+papa|Oui.
+papa|Le sac vient avec nous.
+narrateur|Nina dit merci.
+narrateur|Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
@@ -8638,7 +8766,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Nina a joué vers le toboggan. Elle a mis le ballon dans le sac. Elle a mis la casquette aussi. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
+          <t>Nina a joué près du toboggan. Elle a mis le ballon dans le sac. Elle a mis la casquette aussi. Le toboggan claque tout doux au vent. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8778,12 +8906,15 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|Nina a joué vers le toboggan.
+          <t>narrateur|Nina a joué près du toboggan.
 narrateur|Elle a mis le ballon dans le sac.
 narrateur|Elle a mis la casquette aussi.
+narrateur|Le toboggan claque tout doux au vent.
 narrateur|Le sac est sur le dos, lourd et doux.
-maman|Merci, Nina. Tu as écouté.
-papa|Bravo. On rentre à la maison.
+maman|Merci, Nina.
+maman|Tu as écouté.
+papa|Bravo.
+papa|On rentre à la maison.
 narrateur|La fenêtre les attend, encore un peu embuée.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -8957,9 +9088,12 @@
 papa|Le seau va dans le sac.
 narrateur|Nina le pose sur le doudou.
 maman|Tu as mis ce que j'ai dit ?
-enfant-f|Oui. Le seau est dedans.
-papa|Bravo. On dit merci au seau, tout bas.
-narrateur|Nina rit un peu. L'anse cliquette.</t>
+enfant-f|Oui.
+enfant-f|Le seau est dedans.
+papa|Bravo.
+papa|On dit merci au seau, tout bas.
+narrateur|Nina rit un peu.
+narrateur|L'anse cliquette.</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
@@ -9187,7 +9321,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Nina prend la gourde. Elle est bleue. L'eau chante un peu dedans. La gourde, on la met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. L'anse du seau dépasse un tout petit peu. Le toboggan brille encore derrière eux. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
+          <t>Nina prend la gourde. Elle est bleue. L'eau chante un peu dedans. La gourde, on la met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Une corde de balançoire craque. L'anse du seau dépasse un tout petit peu. Le toboggan brille encore derrière eux. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -9331,15 +9465,21 @@
 narrateur|Elle est bleue.
 narrateur|L'eau chante un peu dedans.
 maman|La gourde, on la met dans le sac.
-narrateur|Nina l'écoute. Elle met la chose dans le sac.
+narrateur|Nina l'écoute.
+narrateur|Elle met la chose dans le sac.
 narrateur|C'est ce que l'adulte a dit.
-papa|Bravo. Tu as fait du bon travail.
+papa|Bravo.
+papa|Tu as fait du bon travail.
 enfant-f|Le sac est prêt.
+narrateur|Une corde de balançoire craque.
 narrateur|L'anse du seau dépasse un tout petit peu.
 narrateur|Le toboggan brille encore derrière eux.
-maman|On a mis ce qu'il fallait. On rentre ?
-papa|Oui. Le sac vient avec nous.
-narrateur|Nina dit merci. Les chaussures font toc toc.</t>
+maman|On a mis ce qu'il fallait.
+maman|On rentre ?
+papa|Oui.
+papa|Le sac vient avec nous.
+narrateur|Nina dit merci.
+narrateur|Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
@@ -9371,7 +9511,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Nina a joué vers le toboggan. Elle a mis le seau dans le sac. Elle a mis la gourde aussi. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
+          <t>Nina a joué près du toboggan. Elle a mis le seau dans le sac. Elle a mis la gourde aussi. Une corde de balançoire craque. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9511,12 +9651,15 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|Nina a joué vers le toboggan.
+          <t>narrateur|Nina a joué près du toboggan.
 narrateur|Elle a mis le seau dans le sac.
 narrateur|Elle a mis la gourde aussi.
+narrateur|Une corde de balançoire craque.
 narrateur|Le sac est sur le dos, lourd et doux.
-maman|Merci, Nina. Tu as écouté.
-papa|Bravo. On rentre à la maison.
+maman|Merci, Nina.
+maman|Tu as écouté.
+papa|Bravo.
+papa|On rentre à la maison.
 narrateur|La fenêtre les attend, encore un peu embuée.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -9545,7 +9688,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Nina prend le goûter. Il est dans un linge. Ça sent la pomme douce. Le goûter, on le met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. L'anse du seau dépasse un tout petit peu. Le toboggan brille encore derrière eux. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
+          <t>Nina prend le goûter. Il est dans un linge. Ça sent la pomme douce. Le goûter, on le met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Le sac fait une bosse ronde. L'anse du seau dépasse un tout petit peu. Le toboggan brille encore derrière eux. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9689,15 +9832,21 @@
 narrateur|Il est dans un linge.
 narrateur|Ça sent la pomme douce.
 papa|Le goûter, on le met dans le sac.
-narrateur|Nina l'écoute. Elle met la chose dans le sac.
+narrateur|Nina l'écoute.
+narrateur|Elle met la chose dans le sac.
 narrateur|C'est ce que l'adulte a dit.
-maman|Bravo. Tu as fait du bon travail.
+maman|Bravo.
+maman|Tu as fait du bon travail.
 enfant-f|Le sac est prêt.
+narrateur|Le sac fait une bosse ronde.
 narrateur|L'anse du seau dépasse un tout petit peu.
 narrateur|Le toboggan brille encore derrière eux.
-maman|On a mis ce qu'il fallait. On rentre ?
-papa|Oui. Le sac vient avec nous.
-narrateur|Nina dit merci. Les chaussures font toc toc.</t>
+maman|On a mis ce qu'il fallait.
+maman|On rentre ?
+papa|Oui.
+papa|Le sac vient avec nous.
+narrateur|Nina dit merci.
+narrateur|Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
@@ -9729,7 +9878,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Nina a joué vers le toboggan. Elle a mis le seau dans le sac. Elle a mis le goûter aussi. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
+          <t>Nina a joué près du toboggan. Elle a mis le seau dans le sac. Elle a mis le goûter aussi. Le sac fait une bosse ronde. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9869,12 +10018,15 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|Nina a joué vers le toboggan.
+          <t>narrateur|Nina a joué près du toboggan.
 narrateur|Elle a mis le seau dans le sac.
 narrateur|Elle a mis le goûter aussi.
+narrateur|Le sac fait une bosse ronde.
 narrateur|Le sac est sur le dos, lourd et doux.
-maman|Merci, Nina. Tu as écouté.
-papa|Bravo. On rentre à la maison.
+maman|Merci, Nina.
+maman|Tu as écouté.
+papa|Bravo.
+papa|On rentre à la maison.
 narrateur|La fenêtre les attend, encore un peu embuée.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -9903,7 +10055,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Nina prend la casquette. Elle est à visière. Le tissu est un peu rêche. La casquette, on la met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. L'anse du seau dépasse un tout petit peu. Le toboggan brille encore derrière eux. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
+          <t>Nina prend la casquette. Elle est à visière. Le tissu est un peu rêche. La casquette, on la met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Nina essuie ses mains à l'herbe. L'anse du seau dépasse un tout petit peu. Le toboggan brille encore derrière eux. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -10047,15 +10199,21 @@
 narrateur|Elle est à visière.
 narrateur|Le tissu est un peu rêche.
 maman|La casquette, on la met dans le sac.
-narrateur|Nina l'écoute. Elle met la chose dans le sac.
+narrateur|Nina l'écoute.
+narrateur|Elle met la chose dans le sac.
 narrateur|C'est ce que l'adulte a dit.
-papa|Bravo. Tu as fait du bon travail.
+papa|Bravo.
+papa|Tu as fait du bon travail.
 enfant-f|Le sac est prêt.
+narrateur|Nina essuie ses mains à l'herbe.
 narrateur|L'anse du seau dépasse un tout petit peu.
 narrateur|Le toboggan brille encore derrière eux.
-maman|On a mis ce qu'il fallait. On rentre ?
-papa|Oui. Le sac vient avec nous.
-narrateur|Nina dit merci. Les chaussures font toc toc.</t>
+maman|On a mis ce qu'il fallait.
+maman|On rentre ?
+papa|Oui.
+papa|Le sac vient avec nous.
+narrateur|Nina dit merci.
+narrateur|Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
@@ -10087,7 +10245,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Nina a joué vers le toboggan. Elle a mis le seau dans le sac. Elle a mis la casquette aussi. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
+          <t>Nina a joué près du toboggan. Elle a mis le seau dans le sac. Elle a mis la casquette aussi. Nina essuie ses mains à l'herbe. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -10227,12 +10385,15 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|Nina a joué vers le toboggan.
+          <t>narrateur|Nina a joué près du toboggan.
 narrateur|Elle a mis le seau dans le sac.
 narrateur|Elle a mis la casquette aussi.
+narrateur|Nina essuie ses mains à l'herbe.
 narrateur|Le sac est sur le dos, lourd et doux.
-maman|Merci, Nina. Tu as écouté.
-papa|Bravo. On rentre à la maison.
+maman|Merci, Nina.
+maman|Tu as écouté.
+papa|Bravo.
+papa|On rentre à la maison.
 narrateur|La fenêtre les attend, encore un peu embuée.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -10405,10 +10566,13 @@
 narrateur|Les chaussures font toc toc sur le métal.
 maman|Le doudou, on le met bien dans le sac.
 narrateur|Nina l'enfonce tout doucement.
-papa|Bravo. Tu as écouté.
+papa|Bravo.
+papa|Tu as écouté.
 enfant-f|Il est au chaud dans le sac.
-narrateur|Nina souffle. Le toboggan brille encore.
-maman|On continue. Il reste une chose.</t>
+narrateur|Nina souffle.
+narrateur|Le toboggan brille encore.
+maman|On continue.
+maman|Il reste une chose.</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
@@ -10636,7 +10800,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Nina prend la gourde. Elle est bleue. L'eau chante un peu dedans. La gourde, on la met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Le doudou chauffe le fond du sac. Le toboggan brille encore derrière eux. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
+          <t>Nina prend la gourde. Elle est bleue. L'eau chante un peu dedans. La gourde, on la met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Papa porte le sac un moment. Le doudou chauffe le fond du sac. Le toboggan brille encore derrière eux. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10780,15 +10944,21 @@
 narrateur|Elle est bleue.
 narrateur|L'eau chante un peu dedans.
 maman|La gourde, on la met dans le sac.
-narrateur|Nina l'écoute. Elle met la chose dans le sac.
+narrateur|Nina l'écoute.
+narrateur|Elle met la chose dans le sac.
 narrateur|C'est ce que l'adulte a dit.
-papa|Bravo. Tu as fait du bon travail.
+papa|Bravo.
+papa|Tu as fait du bon travail.
 enfant-f|Le sac est prêt.
+narrateur|Papa porte le sac un moment.
 narrateur|Le doudou chauffe le fond du sac.
 narrateur|Le toboggan brille encore derrière eux.
-maman|On a mis ce qu'il fallait. On rentre ?
-papa|Oui. Le sac vient avec nous.
-narrateur|Nina dit merci. Les chaussures font toc toc.</t>
+maman|On a mis ce qu'il fallait.
+maman|On rentre ?
+papa|Oui.
+papa|Le sac vient avec nous.
+narrateur|Nina dit merci.
+narrateur|Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
@@ -10820,7 +10990,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Nina a joué vers le toboggan. Elle a mis le doudou dans le sac. Elle a mis la gourde aussi. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
+          <t>Nina a joué près du toboggan. Elle a mis le doudou dans le sac. Elle a mis la gourde aussi. Papa porte le sac un moment. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10960,12 +11130,15 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|Nina a joué vers le toboggan.
+          <t>narrateur|Nina a joué près du toboggan.
 narrateur|Elle a mis le doudou dans le sac.
 narrateur|Elle a mis la gourde aussi.
+narrateur|Papa porte le sac un moment.
 narrateur|Le sac est sur le dos, lourd et doux.
-maman|Merci, Nina. Tu as écouté.
-papa|Bravo. On rentre à la maison.
+maman|Merci, Nina.
+maman|Tu as écouté.
+papa|Bravo.
+papa|On rentre à la maison.
 narrateur|La fenêtre les attend, encore un peu embuée.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -10994,7 +11167,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Nina prend le goûter. Il est dans un linge. Ça sent la pomme douce. Le goûter, on le met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Le doudou chauffe le fond du sac. Le toboggan brille encore derrière eux. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
+          <t>Nina prend le goûter. Il est dans un linge. Ça sent la pomme douce. Le goûter, on le met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Maman ferme la fermeture. Ça fait zzz. Le doudou chauffe le fond du sac. Le toboggan brille encore derrière eux. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -11138,15 +11311,22 @@
 narrateur|Il est dans un linge.
 narrateur|Ça sent la pomme douce.
 papa|Le goûter, on le met dans le sac.
-narrateur|Nina l'écoute. Elle met la chose dans le sac.
+narrateur|Nina l'écoute.
+narrateur|Elle met la chose dans le sac.
 narrateur|C'est ce que l'adulte a dit.
-maman|Bravo. Tu as fait du bon travail.
+maman|Bravo.
+maman|Tu as fait du bon travail.
 enfant-f|Le sac est prêt.
+narrateur|Maman ferme la fermeture.
+narrateur|Ça fait zzz.
 narrateur|Le doudou chauffe le fond du sac.
 narrateur|Le toboggan brille encore derrière eux.
-maman|On a mis ce qu'il fallait. On rentre ?
-papa|Oui. Le sac vient avec nous.
-narrateur|Nina dit merci. Les chaussures font toc toc.</t>
+maman|On a mis ce qu'il fallait.
+maman|On rentre ?
+papa|Oui.
+papa|Le sac vient avec nous.
+narrateur|Nina dit merci.
+narrateur|Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
@@ -11178,7 +11358,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Nina a joué vers le toboggan. Elle a mis le doudou dans le sac. Elle a mis le goûter aussi. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
+          <t>Nina a joué près du toboggan. Elle a mis le doudou dans le sac. Elle a mis le goûter aussi. Maman ferme la fermeture. Ça fait zzz. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -11318,12 +11498,16 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|Nina a joué vers le toboggan.
+          <t>narrateur|Nina a joué près du toboggan.
 narrateur|Elle a mis le doudou dans le sac.
 narrateur|Elle a mis le goûter aussi.
+narrateur|Maman ferme la fermeture.
+narrateur|Ça fait zzz.
 narrateur|Le sac est sur le dos, lourd et doux.
-maman|Merci, Nina. Tu as écouté.
-papa|Bravo. On rentre à la maison.
+maman|Merci, Nina.
+maman|Tu as écouté.
+papa|Bravo.
+papa|On rentre à la maison.
 narrateur|La fenêtre les attend, encore un peu embuée.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -11352,7 +11536,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Nina prend la casquette. Elle est à visière. Le tissu est un peu rêche. La casquette, on la met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Le doudou chauffe le fond du sac. Le toboggan brille encore derrière eux. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
+          <t>Nina prend la casquette. Elle est à visière. Le tissu est un peu rêche. La casquette, on la met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Le chemin du parc sent les pins. Le doudou chauffe le fond du sac. Le toboggan brille encore derrière eux. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -11496,15 +11680,21 @@
 narrateur|Elle est à visière.
 narrateur|Le tissu est un peu rêche.
 maman|La casquette, on la met dans le sac.
-narrateur|Nina l'écoute. Elle met la chose dans le sac.
+narrateur|Nina l'écoute.
+narrateur|Elle met la chose dans le sac.
 narrateur|C'est ce que l'adulte a dit.
-papa|Bravo. Tu as fait du bon travail.
+papa|Bravo.
+papa|Tu as fait du bon travail.
 enfant-f|Le sac est prêt.
+narrateur|Le chemin du parc sent les pins.
 narrateur|Le doudou chauffe le fond du sac.
 narrateur|Le toboggan brille encore derrière eux.
-maman|On a mis ce qu'il fallait. On rentre ?
-papa|Oui. Le sac vient avec nous.
-narrateur|Nina dit merci. Les chaussures font toc toc.</t>
+maman|On a mis ce qu'il fallait.
+maman|On rentre ?
+papa|Oui.
+papa|Le sac vient avec nous.
+narrateur|Nina dit merci.
+narrateur|Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
@@ -11536,7 +11726,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Nina a joué vers le toboggan. Elle a mis le doudou dans le sac. Elle a mis la casquette aussi. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
+          <t>Nina a joué près du toboggan. Elle a mis le doudou dans le sac. Elle a mis la casquette aussi. Le chemin du parc sent les pins. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11676,12 +11866,15 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|Nina a joué vers le toboggan.
+          <t>narrateur|Nina a joué près du toboggan.
 narrateur|Elle a mis le doudou dans le sac.
 narrateur|Elle a mis la casquette aussi.
+narrateur|Le chemin du parc sent les pins.
 narrateur|Le sac est sur le dos, lourd et doux.
-maman|Merci, Nina. Tu as écouté.
-papa|Bravo. On rentre à la maison.
+maman|Merci, Nina.
+maman|Tu as écouté.
+papa|Bravo.
+papa|On rentre à la maison.
 narrateur|La fenêtre les attend, encore un peu embuée.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -11860,7 +12053,8 @@
 narrateur|Nina touche la sangle lisse.
 narrateur|Elle sent le doudou à travers le tissu.
 enfant-f|Le sac est avec nous.
-maman|Très bien. On reste ensemble.
+maman|Très bien.
+maman|On reste ensemble.
 narrateur|Au loin, un vélo passe tout doux.
 narrateur|L'air est frais sur les joues.</t>
         </is>
@@ -12226,8 +12420,10 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Nina met les choses dans le sac.
-maman|Tu as mis ce que j'ai dit. Bravo.
+          <t>narrateur|Oui.
+narrateur|Nina met les choses dans le sac.
+maman|Tu as mis ce que j'ai dit.
+maman|Bravo.
 papa|On garde le sac près des balançoires.
 narrateur|Nina entend encore le clin des chaînes.</t>
         </is>
@@ -12597,7 +12793,8 @@
 narrateur|Il est rouge comme une pomme.
 papa|On le met dans le sac, comme maman a dit.
 narrateur|Nina ouvre, elle pousse, elle ferme.
-maman|Bravo. Le ballon est à sa place.
+maman|Bravo.
+maman|Le ballon est à sa place.
 enfant-f|Dans le sac !
 narrateur|Les chaînes se taisent une seconde.
 papa|On a mis ce que l'adulte a dit.</t>
@@ -12828,7 +13025,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Nina prend la gourde. Elle est bleue. L'eau chante un peu dedans. La gourde, on la met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Le ballon fait une bosse dans le sac. Les chaînes des balançoires se taisent. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
+          <t>Nina prend la gourde. Elle est bleue. L'eau chante un peu dedans. La gourde, on la met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Les chaussures ramassent un peu de sable. Le ballon fait une bosse dans le sac. Les chaînes des balançoires se taisent. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12972,15 +13169,21 @@
 narrateur|Elle est bleue.
 narrateur|L'eau chante un peu dedans.
 maman|La gourde, on la met dans le sac.
-narrateur|Nina l'écoute. Elle met la chose dans le sac.
+narrateur|Nina l'écoute.
+narrateur|Elle met la chose dans le sac.
 narrateur|C'est ce que l'adulte a dit.
-papa|Bravo. Tu as fait du bon travail.
+papa|Bravo.
+papa|Tu as fait du bon travail.
 enfant-f|Le sac est prêt.
+narrateur|Les chaussures ramassent un peu de sable.
 narrateur|Le ballon fait une bosse dans le sac.
 narrateur|Les chaînes des balançoires se taisent.
-maman|On a mis ce qu'il fallait. On rentre ?
-papa|Oui. Le sac vient avec nous.
-narrateur|Nina dit merci. Les chaussures font toc toc.</t>
+maman|On a mis ce qu'il fallait.
+maman|On rentre ?
+papa|Oui.
+papa|Le sac vient avec nous.
+narrateur|Nina dit merci.
+narrateur|Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
@@ -13012,7 +13215,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Nina a joué vers les balançoires. Elle a mis le ballon dans le sac. Elle a mis la gourde aussi. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
+          <t>Nina a joué aux balançoires. Elle a mis le ballon dans le sac. Elle a mis la gourde aussi. Les chaussures ramassent un peu de sable. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -13152,12 +13355,15 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|Nina a joué vers les balançoires.
+          <t>narrateur|Nina a joué aux balançoires.
 narrateur|Elle a mis le ballon dans le sac.
 narrateur|Elle a mis la gourde aussi.
+narrateur|Les chaussures ramassent un peu de sable.
 narrateur|Le sac est sur le dos, lourd et doux.
-maman|Merci, Nina. Tu as écouté.
-papa|Bravo. On rentre à la maison.
+maman|Merci, Nina.
+maman|Tu as écouté.
+papa|Bravo.
+papa|On rentre à la maison.
 narrateur|La fenêtre les attend, encore un peu embuée.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -13186,7 +13392,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Nina prend le goûter. Il est dans un linge. Ça sent la pomme douce. Le goûter, on le met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Le ballon fait une bosse dans le sac. Les chaînes des balançoires se taisent. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
+          <t>Nina prend le goûter. Il est dans un linge. Ça sent la pomme douce. Le goûter, on le met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Un nuage passe sur le toboggan. Le ballon fait une bosse dans le sac. Les chaînes des balançoires se taisent. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -13330,15 +13536,21 @@
 narrateur|Il est dans un linge.
 narrateur|Ça sent la pomme douce.
 papa|Le goûter, on le met dans le sac.
-narrateur|Nina l'écoute. Elle met la chose dans le sac.
+narrateur|Nina l'écoute.
+narrateur|Elle met la chose dans le sac.
 narrateur|C'est ce que l'adulte a dit.
-maman|Bravo. Tu as fait du bon travail.
+maman|Bravo.
+maman|Tu as fait du bon travail.
 enfant-f|Le sac est prêt.
+narrateur|Un nuage passe sur le toboggan.
 narrateur|Le ballon fait une bosse dans le sac.
 narrateur|Les chaînes des balançoires se taisent.
-maman|On a mis ce qu'il fallait. On rentre ?
-papa|Oui. Le sac vient avec nous.
-narrateur|Nina dit merci. Les chaussures font toc toc.</t>
+maman|On a mis ce qu'il fallait.
+maman|On rentre ?
+papa|Oui.
+papa|Le sac vient avec nous.
+narrateur|Nina dit merci.
+narrateur|Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
@@ -13370,7 +13582,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Nina a joué vers les balançoires. Elle a mis le ballon dans le sac. Elle a mis le goûter aussi. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
+          <t>Nina a joué aux balançoires. Elle a mis le ballon dans le sac. Elle a mis le goûter aussi. Un nuage passe sur le toboggan. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -13510,12 +13722,15 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|Nina a joué vers les balançoires.
+          <t>narrateur|Nina a joué aux balançoires.
 narrateur|Elle a mis le ballon dans le sac.
 narrateur|Elle a mis le goûter aussi.
+narrateur|Un nuage passe sur le toboggan.
 narrateur|Le sac est sur le dos, lourd et doux.
-maman|Merci, Nina. Tu as écouté.
-papa|Bravo. On rentre à la maison.
+maman|Merci, Nina.
+maman|Tu as écouté.
+papa|Bravo.
+papa|On rentre à la maison.
 narrateur|La fenêtre les attend, encore un peu embuée.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -13544,7 +13759,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Nina prend la casquette. Elle est à visière. Le tissu est un peu rêche. La casquette, on la met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Le ballon fait une bosse dans le sac. Les chaînes des balançoires se taisent. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
+          <t>Nina prend la casquette. Elle est à visière. Le tissu est un peu rêche. La casquette, on la met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. La visière de la casquette fait de l'ombre. Le ballon fait une bosse dans le sac. Les chaînes des balançoires se taisent. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13688,15 +13903,21 @@
 narrateur|Elle est à visière.
 narrateur|Le tissu est un peu rêche.
 maman|La casquette, on la met dans le sac.
-narrateur|Nina l'écoute. Elle met la chose dans le sac.
+narrateur|Nina l'écoute.
+narrateur|Elle met la chose dans le sac.
 narrateur|C'est ce que l'adulte a dit.
-papa|Bravo. Tu as fait du bon travail.
+papa|Bravo.
+papa|Tu as fait du bon travail.
 enfant-f|Le sac est prêt.
+narrateur|La visière de la casquette fait de l'ombre.
 narrateur|Le ballon fait une bosse dans le sac.
 narrateur|Les chaînes des balançoires se taisent.
-maman|On a mis ce qu'il fallait. On rentre ?
-papa|Oui. Le sac vient avec nous.
-narrateur|Nina dit merci. Les chaussures font toc toc.</t>
+maman|On a mis ce qu'il fallait.
+maman|On rentre ?
+papa|Oui.
+papa|Le sac vient avec nous.
+narrateur|Nina dit merci.
+narrateur|Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
@@ -13728,7 +13949,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Nina a joué vers les balançoires. Elle a mis le ballon dans le sac. Elle a mis la casquette aussi. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
+          <t>Nina a joué aux balançoires. Elle a mis le ballon dans le sac. Elle a mis la casquette aussi. La visière de la casquette fait de l'ombre. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13868,12 +14089,15 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|Nina a joué vers les balançoires.
+          <t>narrateur|Nina a joué aux balançoires.
 narrateur|Elle a mis le ballon dans le sac.
 narrateur|Elle a mis la casquette aussi.
+narrateur|La visière de la casquette fait de l'ombre.
 narrateur|Le sac est sur le dos, lourd et doux.
-maman|Merci, Nina. Tu as écouté.
-papa|Bravo. On rentre à la maison.
+maman|Merci, Nina.
+maman|Tu as écouté.
+papa|Bravo.
+papa|On rentre à la maison.
 narrateur|La fenêtre les attend, encore un peu embuée.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -14048,7 +14272,8 @@
 narrateur|Nina le glisse à côté du livre.
 papa|Tu as fini de ranger le seau ?
 enfant-f|Oui, papa.
-maman|Bravo. Tu as fait du bon travail.
+maman|Bravo.
+maman|Tu as fait du bon travail.
 narrateur|Un oiseau répond, tout haut.</t>
         </is>
       </c>
@@ -14272,7 +14497,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Nina prend la gourde. Elle est bleue. L'eau chante un peu dedans. La gourde, on la met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. L'anse du seau dépasse un tout petit peu. Les chaînes des balançoires se taisent. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
+          <t>Nina prend la gourde. Elle est bleue. L'eau chante un peu dedans. La gourde, on la met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. La pomme du goûter roule un peu. L'anse du seau dépasse un tout petit peu. Les chaînes des balançoires se taisent. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -14416,15 +14641,21 @@
 narrateur|Elle est bleue.
 narrateur|L'eau chante un peu dedans.
 maman|La gourde, on la met dans le sac.
-narrateur|Nina l'écoute. Elle met la chose dans le sac.
+narrateur|Nina l'écoute.
+narrateur|Elle met la chose dans le sac.
 narrateur|C'est ce que l'adulte a dit.
-papa|Bravo. Tu as fait du bon travail.
+papa|Bravo.
+papa|Tu as fait du bon travail.
 enfant-f|Le sac est prêt.
+narrateur|La pomme du goûter roule un peu.
 narrateur|L'anse du seau dépasse un tout petit peu.
 narrateur|Les chaînes des balançoires se taisent.
-maman|On a mis ce qu'il fallait. On rentre ?
-papa|Oui. Le sac vient avec nous.
-narrateur|Nina dit merci. Les chaussures font toc toc.</t>
+maman|On a mis ce qu'il fallait.
+maman|On rentre ?
+papa|Oui.
+papa|Le sac vient avec nous.
+narrateur|Nina dit merci.
+narrateur|Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
@@ -14456,7 +14687,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Nina a joué vers les balançoires. Elle a mis le seau dans le sac. Elle a mis la gourde aussi. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
+          <t>Nina a joué aux balançoires. Elle a mis le seau dans le sac. Elle a mis la gourde aussi. La pomme du goûter roule un peu. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -14596,12 +14827,15 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|Nina a joué vers les balançoires.
+          <t>narrateur|Nina a joué aux balançoires.
 narrateur|Elle a mis le seau dans le sac.
 narrateur|Elle a mis la gourde aussi.
+narrateur|La pomme du goûter roule un peu.
 narrateur|Le sac est sur le dos, lourd et doux.
-maman|Merci, Nina. Tu as écouté.
-papa|Bravo. On rentre à la maison.
+maman|Merci, Nina.
+maman|Tu as écouté.
+papa|Bravo.
+papa|On rentre à la maison.
 narrateur|La fenêtre les attend, encore un peu embuée.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -14630,7 +14864,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Nina prend le goûter. Il est dans un linge. Ça sent la pomme douce. Le goûter, on le met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. L'anse du seau dépasse un tout petit peu. Les chaînes des balançoires se taisent. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
+          <t>Nina prend le goûter. Il est dans un linge. Ça sent la pomme douce. Le goûter, on le met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. L'eau de la gourde cliquette. L'anse du seau dépasse un tout petit peu. Les chaînes des balançoires se taisent. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14774,15 +15008,21 @@
 narrateur|Il est dans un linge.
 narrateur|Ça sent la pomme douce.
 papa|Le goûter, on le met dans le sac.
-narrateur|Nina l'écoute. Elle met la chose dans le sac.
+narrateur|Nina l'écoute.
+narrateur|Elle met la chose dans le sac.
 narrateur|C'est ce que l'adulte a dit.
-maman|Bravo. Tu as fait du bon travail.
+maman|Bravo.
+maman|Tu as fait du bon travail.
 enfant-f|Le sac est prêt.
+narrateur|L'eau de la gourde cliquette.
 narrateur|L'anse du seau dépasse un tout petit peu.
 narrateur|Les chaînes des balançoires se taisent.
-maman|On a mis ce qu'il fallait. On rentre ?
-papa|Oui. Le sac vient avec nous.
-narrateur|Nina dit merci. Les chaussures font toc toc.</t>
+maman|On a mis ce qu'il fallait.
+maman|On rentre ?
+papa|Oui.
+papa|Le sac vient avec nous.
+narrateur|Nina dit merci.
+narrateur|Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
@@ -14814,7 +15054,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Nina a joué vers les balançoires. Elle a mis le seau dans le sac. Elle a mis le goûter aussi. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
+          <t>Nina a joué aux balançoires. Elle a mis le seau dans le sac. Elle a mis le goûter aussi. L'eau de la gourde cliquette. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14954,12 +15194,15 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|Nina a joué vers les balançoires.
+          <t>narrateur|Nina a joué aux balançoires.
 narrateur|Elle a mis le seau dans le sac.
 narrateur|Elle a mis le goûter aussi.
+narrateur|L'eau de la gourde cliquette.
 narrateur|Le sac est sur le dos, lourd et doux.
-maman|Merci, Nina. Tu as écouté.
-papa|Bravo. On rentre à la maison.
+maman|Merci, Nina.
+maman|Tu as écouté.
+papa|Bravo.
+papa|On rentre à la maison.
 narrateur|La fenêtre les attend, encore un peu embuée.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -14988,7 +15231,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Nina prend la casquette. Elle est à visière. Le tissu est un peu rêche. La casquette, on la met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. L'anse du seau dépasse un tout petit peu. Les chaînes des balançoires se taisent. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
+          <t>Nina prend la casquette. Elle est à visière. Le tissu est un peu rêche. La casquette, on la met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Nina serre la sangle contre son ventre. L'anse du seau dépasse un tout petit peu. Les chaînes des balançoires se taisent. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -15132,15 +15375,21 @@
 narrateur|Elle est à visière.
 narrateur|Le tissu est un peu rêche.
 maman|La casquette, on la met dans le sac.
-narrateur|Nina l'écoute. Elle met la chose dans le sac.
+narrateur|Nina l'écoute.
+narrateur|Elle met la chose dans le sac.
 narrateur|C'est ce que l'adulte a dit.
-papa|Bravo. Tu as fait du bon travail.
+papa|Bravo.
+papa|Tu as fait du bon travail.
 enfant-f|Le sac est prêt.
+narrateur|Nina serre la sangle contre son ventre.
 narrateur|L'anse du seau dépasse un tout petit peu.
 narrateur|Les chaînes des balançoires se taisent.
-maman|On a mis ce qu'il fallait. On rentre ?
-papa|Oui. Le sac vient avec nous.
-narrateur|Nina dit merci. Les chaussures font toc toc.</t>
+maman|On a mis ce qu'il fallait.
+maman|On rentre ?
+papa|Oui.
+papa|Le sac vient avec nous.
+narrateur|Nina dit merci.
+narrateur|Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
@@ -15172,7 +15421,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Nina a joué vers les balançoires. Elle a mis le seau dans le sac. Elle a mis la casquette aussi. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
+          <t>Nina a joué aux balançoires. Elle a mis le seau dans le sac. Elle a mis la casquette aussi. Nina serre la sangle contre son ventre. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -15312,12 +15561,15 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|Nina a joué vers les balançoires.
+          <t>narrateur|Nina a joué aux balançoires.
 narrateur|Elle a mis le seau dans le sac.
 narrateur|Elle a mis la casquette aussi.
+narrateur|Nina serre la sangle contre son ventre.
 narrateur|Le sac est sur le dos, lourd et doux.
-maman|Merci, Nina. Tu as écouté.
-papa|Bravo. On rentre à la maison.
+maman|Merci, Nina.
+maman|Tu as écouté.
+papa|Bravo.
+papa|On rentre à la maison.
 narrateur|La fenêtre les attend, encore un peu embuée.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -15488,12 +15740,15 @@
         <is>
           <t>narrateur|Nina a choisi le doudou, contre le sac.
 narrateur|La couverture du doudou est douce.
-papa|On le met dans le sac. C'est ce que l'adulte a dit.
-narrateur|Nina le range. Elle appuie un peu.
+papa|On le met dans le sac.
+papa|C'est ce que l'adulte a dit.
+narrateur|Nina le range.
+narrateur|Elle appuie un peu.
 maman|Bravo, Nina.
 enfant-f|Il est bien.
 narrateur|Le vent sent l'herbe et le bois chaud.
-papa|On souffle. Puis la dernière chose.</t>
+papa|On souffle.
+papa|Puis la dernière chose.</t>
         </is>
       </c>
     </row>
@@ -15716,7 +15971,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Nina prend la gourde. Elle est bleue. L'eau chante un peu dedans. La gourde, on la met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Le doudou chauffe le fond du sac. Les chaînes des balançoires se taisent. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
+          <t>Nina prend la gourde. Elle est bleue. L'eau chante un peu dedans. La gourde, on la met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Le portail du parc grince une fois. Le doudou chauffe le fond du sac. Les chaînes des balançoires se taisent. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15860,15 +16115,21 @@
 narrateur|Elle est bleue.
 narrateur|L'eau chante un peu dedans.
 maman|La gourde, on la met dans le sac.
-narrateur|Nina l'écoute. Elle met la chose dans le sac.
+narrateur|Nina l'écoute.
+narrateur|Elle met la chose dans le sac.
 narrateur|C'est ce que l'adulte a dit.
-papa|Bravo. Tu as fait du bon travail.
+papa|Bravo.
+papa|Tu as fait du bon travail.
 enfant-f|Le sac est prêt.
+narrateur|Le portail du parc grince une fois.
 narrateur|Le doudou chauffe le fond du sac.
 narrateur|Les chaînes des balançoires se taisent.
-maman|On a mis ce qu'il fallait. On rentre ?
-papa|Oui. Le sac vient avec nous.
-narrateur|Nina dit merci. Les chaussures font toc toc.</t>
+maman|On a mis ce qu'il fallait.
+maman|On rentre ?
+papa|Oui.
+papa|Le sac vient avec nous.
+narrateur|Nina dit merci.
+narrateur|Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
@@ -15900,7 +16161,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Nina a joué vers les balançoires. Elle a mis le doudou dans le sac. Elle a mis la gourde aussi. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
+          <t>Nina a joué aux balançoires. Elle a mis le doudou dans le sac. Elle a mis la gourde aussi. Le portail du parc grince une fois. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -16040,12 +16301,15 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|Nina a joué vers les balançoires.
+          <t>narrateur|Nina a joué aux balançoires.
 narrateur|Elle a mis le doudou dans le sac.
 narrateur|Elle a mis la gourde aussi.
+narrateur|Le portail du parc grince une fois.
 narrateur|Le sac est sur le dos, lourd et doux.
-maman|Merci, Nina. Tu as écouté.
-papa|Bravo. On rentre à la maison.
+maman|Merci, Nina.
+maman|Tu as écouté.
+papa|Bravo.
+papa|On rentre à la maison.
 narrateur|La fenêtre les attend, encore un peu embuée.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -16074,7 +16338,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Nina prend le goûter. Il est dans un linge. Ça sent la pomme douce. Le goûter, on le met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Le doudou chauffe le fond du sac. Les chaînes des balançoires se taisent. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
+          <t>Nina prend le goûter. Il est dans un linge. Ça sent la pomme douce. Le goûter, on le met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Le sac tape doucement la hanche. Le doudou chauffe le fond du sac. Les chaînes des balançoires se taisent. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -16218,15 +16482,21 @@
 narrateur|Il est dans un linge.
 narrateur|Ça sent la pomme douce.
 papa|Le goûter, on le met dans le sac.
-narrateur|Nina l'écoute. Elle met la chose dans le sac.
+narrateur|Nina l'écoute.
+narrateur|Elle met la chose dans le sac.
 narrateur|C'est ce que l'adulte a dit.
-maman|Bravo. Tu as fait du bon travail.
+maman|Bravo.
+maman|Tu as fait du bon travail.
 enfant-f|Le sac est prêt.
+narrateur|Le sac tape doucement la hanche.
 narrateur|Le doudou chauffe le fond du sac.
 narrateur|Les chaînes des balançoires se taisent.
-maman|On a mis ce qu'il fallait. On rentre ?
-papa|Oui. Le sac vient avec nous.
-narrateur|Nina dit merci. Les chaussures font toc toc.</t>
+maman|On a mis ce qu'il fallait.
+maman|On rentre ?
+papa|Oui.
+papa|Le sac vient avec nous.
+narrateur|Nina dit merci.
+narrateur|Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
@@ -16258,7 +16528,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Nina a joué vers les balançoires. Elle a mis le doudou dans le sac. Elle a mis le goûter aussi. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
+          <t>Nina a joué aux balançoires. Elle a mis le doudou dans le sac. Elle a mis le goûter aussi. Le sac tape doucement la hanche. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -16398,12 +16668,15 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|Nina a joué vers les balançoires.
+          <t>narrateur|Nina a joué aux balançoires.
 narrateur|Elle a mis le doudou dans le sac.
 narrateur|Elle a mis le goûter aussi.
+narrateur|Le sac tape doucement la hanche.
 narrateur|Le sac est sur le dos, lourd et doux.
-maman|Merci, Nina. Tu as écouté.
-papa|Bravo. On rentre à la maison.
+maman|Merci, Nina.
+maman|Tu as écouté.
+papa|Bravo.
+papa|On rentre à la maison.
 narrateur|La fenêtre les attend, encore un peu embuée.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -16432,7 +16705,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Nina prend la casquette. Elle est à visière. Le tissu est un peu rêche. La casquette, on la met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. Le doudou chauffe le fond du sac. Les chaînes des balançoires se taisent. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
+          <t>Nina prend la casquette. Elle est à visière. Le tissu est un peu rêche. La casquette, on la met dans le sac. Nina l'écoute. Elle met la chose dans le sac. C'est ce que l'adulte a dit. Bravo. Tu as fait du bon travail. Le sac est prêt. La fenêtre de la maison brille déjà. Le doudou chauffe le fond du sac. Les chaînes des balançoires se taisent. On a mis ce qu'il fallait. On rentre ? Oui. Le sac vient avec nous. Nina dit merci. Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -16576,15 +16849,21 @@
 narrateur|Elle est à visière.
 narrateur|Le tissu est un peu rêche.
 maman|La casquette, on la met dans le sac.
-narrateur|Nina l'écoute. Elle met la chose dans le sac.
+narrateur|Nina l'écoute.
+narrateur|Elle met la chose dans le sac.
 narrateur|C'est ce que l'adulte a dit.
-papa|Bravo. Tu as fait du bon travail.
+papa|Bravo.
+papa|Tu as fait du bon travail.
 enfant-f|Le sac est prêt.
+narrateur|La fenêtre de la maison brille déjà.
 narrateur|Le doudou chauffe le fond du sac.
 narrateur|Les chaînes des balançoires se taisent.
-maman|On a mis ce qu'il fallait. On rentre ?
-papa|Oui. Le sac vient avec nous.
-narrateur|Nina dit merci. Les chaussures font toc toc.</t>
+maman|On a mis ce qu'il fallait.
+maman|On rentre ?
+papa|Oui.
+papa|Le sac vient avec nous.
+narrateur|Nina dit merci.
+narrateur|Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
@@ -16616,7 +16895,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Nina a joué vers les balançoires. Elle a mis le doudou dans le sac. Elle a mis la casquette aussi. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
+          <t>Nina a joué aux balançoires. Elle a mis le doudou dans le sac. Elle a mis la casquette aussi. La fenêtre de la maison brille déjà. Le sac est sur le dos, lourd et doux. Merci, Nina. Tu as écouté. Bravo. On rentre à la maison. La fenêtre les attend, encore un peu embuée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -16756,12 +17035,15 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|Nina a joué vers les balançoires.
+          <t>narrateur|Nina a joué aux balançoires.
 narrateur|Elle a mis le doudou dans le sac.
 narrateur|Elle a mis la casquette aussi.
+narrateur|La fenêtre de la maison brille déjà.
 narrateur|Le sac est sur le dos, lourd et doux.
-maman|Merci, Nina. Tu as écouté.
-papa|Bravo. On rentre à la maison.
+maman|Merci, Nina.
+maman|Tu as écouté.
+papa|Bravo.
+papa|On rentre à la maison.
 narrateur|La fenêtre les attend, encore un peu embuée.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -16784,7 +17066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16883,6 +17165,27 @@
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>

--- a/stories/arbres/TREE-AUT-015.xlsx
+++ b/stories/arbres/TREE-AUT-015.xlsx
@@ -3112,17 +3112,17 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Le ballon dans le sac, et la pomme dans le creux ! Nina souffle, puis avance une main. Elle suit le grain de sel, jusqu'au bouton de bois. Le ballon rentre, la pomme se cale, ronde. Le bouton ferme, net, sur le grain. Le grain a parlé, très bas. La pomme a un nid, maintenant ! Le trou a failli tout garder. Une miette de pomme dort dans le sable. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.</t>
+          <t>Le ballon dans le sac, et la pomme dans le creux ! Nina souffle, puis avance une main. Le grain de sel guide sa main, vers le bouton. Le ballon rentre, la pomme se cale, ronde. Le sac se ferme, grain au milieu. Le grain a parlé, très bas. La pomme a un nid, maintenant ! Le trou a failli tout garder. Une miette de pomme dort dans le sable. Le grain est là, tu le sens ? Oui, c'est celui de la buée.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le ballon dans le sac, et la pomme dans le creux ! Nina souffle, puis avance une main. Elle suit le &lt;emphasis level="moderate"&gt;grain de sel&lt;/emphasis&gt;, jusqu'au bouton de bois. Le ballon rentre, la pomme se cale, ronde. Le bouton ferme, net, sur le grain. Le grain a parlé, très bas. La pomme a un nid, maintenant ! Le trou a failli tout garder. Une miette de pomme dort dans le sable. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le ballon dans le sac, et la pomme dans le creux ! Nina souffle, puis avance une main. Le &lt;emphasis level="moderate"&gt;grain de sel&lt;/emphasis&gt; guide sa main, vers le bouton. Le ballon rentre, la pomme se cale, ronde. Le sac se ferme, grain au milieu. Le grain a parlé, très bas. La pomme a un nid, maintenant ! Le trou a failli tout garder. Une miette de pomme dort dans le sable. Le grain est là, tu le sens ? Oui, c'est celui de la buée.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Le ballon dans le sac, et la pomme dans le creux ! Nina souffle, puis avance une main. Elle suit le &lt;emphasis&gt;grain de sel&lt;/emphasis&gt;, jusqu'au bouton de bois. Le ballon rentre, la pomme se cale, ronde. Le bouton ferme, net, sur le grain. Le grain a parlé, très bas. La pomme a un nid, maintenant ! Le trou a failli tout garder. Une miette de pomme dort dans le sable. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine. [pause]</t>
+          <t>Le ballon dans le sac, et la pomme dans le creux ! Nina souffle, puis avance une main. Le &lt;emphasis&gt;grain de sel&lt;/emphasis&gt; guide sa main, vers le bouton. Le ballon rentre, la pomme se cale, ronde. Le sac se ferme, grain au milieu. Le grain a parlé, très bas. La pomme a un nid, maintenant ! Le trou a failli tout garder. Une miette de pomme dort dans le sable. Le grain est là, tu le sens ? Oui, c'est celui de la buée. [pause]</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
@@ -3258,15 +3258,15 @@
         <is>
           <t>enfant-f|Le ballon dans le sac, et la pomme dans le creux !
 narrateur|Nina souffle, puis avance une main.
-narrateur|Elle suit le grain de sel, jusqu'au bouton de bois.
+narrateur|Le grain de sel guide sa main, vers le bouton.
 narrateur|Le ballon rentre, la pomme se cale, ronde.
-narrateur|Le bouton ferme, net, sur le grain.
+narrateur|Le sac se ferme, grain au milieu.
 papa|Le grain a parlé, très bas.
 enfant-f|La pomme a un nid, maintenant !
 maman|Le trou a failli tout garder.
 narrateur|Une miette de pomme dort dans le sable.
-papa|Tu as vu le grain, sur le bouton ?
-enfant-f|Il était sur la vitre, à la cuisine.</t>
+papa|Le grain est là, tu le sens ?
+enfant-f|Oui, c'est celui de la buée.</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -3481,17 +3481,17 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Le ballon sous la visière, dans le sac ! Nina refuse de creuser plus fort. Elle suit le grain de sel, jusqu'au bouton de bois. La casquette accueille le ballon, puis rentre. Le bouton ferme, net, sur le grain. Le grain a parlé, comme une lanterne. La visière a fait un nid ! Le trou a failli tout garder. La visière garde un voile de sable. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.</t>
+          <t>Le ballon sous la visière, dans le sac ! Nina refuse de creuser plus fort. Nina retrouve le grain, collé au bois. La casquette accueille le ballon, puis rentre. Le bouton de bois pince le grain, et tient. Le grain a parlé, comme une lanterne. La visière a fait un nid ! Le trou a failli tout garder. La visière garde un voile de sable. Tu reconnais le grain, du verre ? Il a glissé du verre, tout petit.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le ballon sous la visière, dans le sac ! Nina refuse de creuser plus fort. Elle suit le &lt;emphasis level="moderate"&gt;grain de sel&lt;/emphasis&gt;, jusqu'au bouton de bois. La casquette accueille le ballon, puis rentre. Le bouton ferme, net, sur le grain. Le grain a parlé, comme une lanterne. La visière a fait un nid ! Le trou a failli tout garder. La visière garde un voile de sable. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le ballon sous la visière, dans le sac ! Nina refuse de creuser plus fort. Nina retrouve le grain, collé au bois. La casquette accueille le ballon, puis rentre. Le bouton de bois pince le grain, et tient. Le grain a parlé, comme une lanterne. La visière a fait un nid ! Le trou a failli tout garder. La visière garde un voile de sable. Tu reconnais le grain, du verre ? Il a glissé du verre, tout petit.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Le ballon sous la visière, dans le sac ! Nina refuse de creuser plus fort. Elle suit le &lt;emphasis&gt;grain de sel&lt;/emphasis&gt;, jusqu'au bouton de bois. La casquette accueille le ballon, puis rentre. Le bouton ferme, net, sur le grain. Le grain a parlé, comme une lanterne. La visière a fait un nid ! Le trou a failli tout garder. La visière garde un voile de sable. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine. [pause]</t>
+          <t>Le ballon sous la visière, dans le sac ! Nina refuse de creuser plus fort. Nina retrouve le grain, collé au bois. La casquette accueille le ballon, puis rentre. Le bouton de bois pince le grain, et tient. Le grain a parlé, comme une lanterne. La visière a fait un nid ! Le trou a failli tout garder. La visière garde un voile de sable. Tu reconnais le grain, du verre ? Il a glissé du verre, tout petit. [pause]</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
@@ -3627,15 +3627,15 @@
         <is>
           <t>enfant-f|Le ballon sous la visière, dans le sac !
 narrateur|Nina refuse de creuser plus fort.
-narrateur|Elle suit le grain de sel, jusqu'au bouton de bois.
+narrateur|Nina retrouve le grain, collé au bois.
 narrateur|La casquette accueille le ballon, puis rentre.
-narrateur|Le bouton ferme, net, sur le grain.
+narrateur|Le bouton de bois pince le grain, et tient.
 papa|Le grain a parlé, comme une lanterne.
 enfant-f|La visière a fait un nid !
 maman|Le trou a failli tout garder.
 narrateur|La visière garde un voile de sable.
-papa|Tu as vu le grain, sur le bouton ?
-enfant-f|Il était sur la vitre, à la cuisine.</t>
+papa|Tu reconnais le grain, du verre ?
+enfant-f|Il a glissé du verre, tout petit.</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
@@ -4244,17 +4244,17 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Le seau vide, puis la gourde dedans, dans le sac ! Nina penche le seau, loin du sable. Elle suit le grain de sel, jusqu'au bouton de bois. La gourde se tient, fraîche, au fond du seau. Le bouton ferme, net, sur le grain. Le grain a parlé, sur le bois. Le seau est un nid, pas un poids ! La sangle a failli tout enterrer. Le seau tient une goutte fraîche, collée au grain. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.</t>
+          <t>Le seau vide, puis la gourde dedans, dans le sac ! Nina penche le seau, loin du sable. Elle pose le doigt sur le grain, sans presser. La gourde se tient, fraîche, au fond du seau. Le bouton parle, contre le grain. Le grain a parlé, sur le bois. Le seau est un nid, pas un poids ! La sangle a failli tout enterrer. Le seau tient une goutte fraîche, collée au grain. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le seau vide, puis la gourde dedans, dans le sac ! Nina penche le seau, loin du sable. Elle suit le &lt;emphasis level="moderate"&gt;grain de sel&lt;/emphasis&gt;, jusqu'au bouton de bois. La gourde se tient, fraîche, au fond du seau. Le bouton ferme, net, sur le grain. Le grain a parlé, sur le bois. Le seau est un nid, pas un poids ! La sangle a failli tout enterrer. Le seau tient une goutte fraîche, collée au grain. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le seau vide, puis la gourde dedans, dans le sac ! Nina penche le seau, loin du sable. Elle pose le doigt sur le grain, sans presser. La gourde se tient, fraîche, au fond du seau. Le bouton parle, contre le grain. Le grain a parlé, sur le bois. Le seau est un nid, pas un poids ! La sangle a failli tout enterrer. Le seau tient une goutte fraîche, collée au grain. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Le seau vide, puis la gourde dedans, dans le sac ! Nina penche le seau, loin du sable. Elle suit le &lt;emphasis&gt;grain de sel&lt;/emphasis&gt;, jusqu'au bouton de bois. La gourde se tient, fraîche, au fond du seau. Le bouton ferme, net, sur le grain. Le grain a parlé, sur le bois. Le seau est un nid, pas un poids ! La sangle a failli tout enterrer. Le seau tient une goutte fraîche, collée au grain. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine. [pause]</t>
+          <t>Le seau vide, puis la gourde dedans, dans le sac ! Nina penche le seau, loin du sable. Elle pose le doigt sur le grain, sans presser. La gourde se tient, fraîche, au fond du seau. Le bouton parle, contre le grain. Le grain a parlé, sur le bois. Le seau est un nid, pas un poids ! La sangle a failli tout enterrer. Le seau tient une goutte fraîche, collée au grain. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine. [pause]</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
@@ -4390,9 +4390,9 @@
         <is>
           <t>enfant-f|Le seau vide, puis la gourde dedans, dans le sac !
 narrateur|Nina penche le seau, loin du sable.
-narrateur|Elle suit le grain de sel, jusqu'au bouton de bois.
+narrateur|Elle pose le doigt sur le grain, sans presser.
 narrateur|La gourde se tient, fraîche, au fond du seau.
-narrateur|Le bouton ferme, net, sur le grain.
+narrateur|Le bouton parle, contre le grain.
 papa|Le grain a parlé, sur le bois.
 enfant-f|Le seau est un nid, pas un poids !
 maman|La sangle a failli tout enterrer.
@@ -4617,17 +4617,17 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>La pomme dans le seau, puis le seau dans le sac ! Nina vide le sable, sans tirer. Elle suit le grain de sel, jusqu'au bouton de bois. La pomme se cale, et le seau rentre, léger. Le bouton ferme, net, sur le grain. Le grain a parlé, très bas. Le goûter a un seau, maintenant ! La sangle a failli tout enterrer. Une croûte de pain sent le sable, sous le grain. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.</t>
+          <t>La pomme dans le seau, puis le seau dans le sac ! Nina vide le sable, sans tirer. Le grain de sel montre le bouton, minuscule. La pomme se cale, et le seau rentre, léger. Le sac pèse, grain sous le bois. Le grain a parlé, très bas. Le goûter a un seau, maintenant ! La sangle a failli tout enterrer. Une croûte de pain sent le sable, sous le grain. Le grain est là, tu le sens ? Oui, c'est celui de la buée.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La pomme dans le seau, puis le seau dans le sac ! Nina vide le sable, sans tirer. Elle suit le &lt;emphasis level="moderate"&gt;grain de sel&lt;/emphasis&gt;, jusqu'au bouton de bois. La pomme se cale, et le seau rentre, léger. Le bouton ferme, net, sur le grain. Le grain a parlé, très bas. Le goûter a un seau, maintenant ! La sangle a failli tout enterrer. Une croûte de pain sent le sable, sous le grain. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La pomme dans le seau, puis le seau dans le sac ! Nina vide le sable, sans tirer. Le &lt;emphasis level="moderate"&gt;grain de sel&lt;/emphasis&gt; montre le bouton, minuscule. La pomme se cale, et le seau rentre, léger. Le sac pèse, grain sous le bois. Le grain a parlé, très bas. Le goûter a un seau, maintenant ! La sangle a failli tout enterrer. Une croûte de pain sent le sable, sous le grain. Le grain est là, tu le sens ? Oui, c'est celui de la buée.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>La pomme dans le seau, puis le seau dans le sac ! Nina vide le sable, sans tirer. Elle suit le &lt;emphasis&gt;grain de sel&lt;/emphasis&gt;, jusqu'au bouton de bois. La pomme se cale, et le seau rentre, léger. Le bouton ferme, net, sur le grain. Le grain a parlé, très bas. Le goûter a un seau, maintenant ! La sangle a failli tout enterrer. Une croûte de pain sent le sable, sous le grain. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine. [pause]</t>
+          <t>La pomme dans le seau, puis le seau dans le sac ! Nina vide le sable, sans tirer. Le &lt;emphasis&gt;grain de sel&lt;/emphasis&gt; montre le bouton, minuscule. La pomme se cale, et le seau rentre, léger. Le sac pèse, grain sous le bois. Le grain a parlé, très bas. Le goûter a un seau, maintenant ! La sangle a failli tout enterrer. Une croûte de pain sent le sable, sous le grain. Le grain est là, tu le sens ? Oui, c'est celui de la buée. [pause]</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
@@ -4763,15 +4763,15 @@
         <is>
           <t>enfant-f|La pomme dans le seau, puis le seau dans le sac !
 narrateur|Nina vide le sable, sans tirer.
-narrateur|Elle suit le grain de sel, jusqu'au bouton de bois.
+narrateur|Le grain de sel montre le bouton, minuscule.
 narrateur|La pomme se cale, et le seau rentre, léger.
-narrateur|Le bouton ferme, net, sur le grain.
+narrateur|Le sac pèse, grain sous le bois.
 papa|Le grain a parlé, très bas.
 enfant-f|Le goûter a un seau, maintenant !
 maman|La sangle a failli tout enterrer.
 narrateur|Une croûte de pain sent le sable, sous le grain.
-papa|Tu as vu le grain, sur le bouton ?
-enfant-f|Il était sur la vitre, à la cuisine.</t>
+papa|Le grain est là, tu le sens ?
+enfant-f|Oui, c'est celui de la buée.</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
@@ -4990,17 +4990,17 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>La casquette en couvercle, sur le seau, dans le sac ! Nina pose la visière, sans presser le sable. Elle suit le grain de sel, jusqu'au bouton de bois. Le seau rentre, chapeau dessus, léger. Le bouton ferme, net, sur le grain. Le grain a parlé, comme une lanterne. La visière a tenu le seau ! La sangle a failli tout enterrer. La visière sert de couvercle au seau, grain dessus. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.</t>
+          <t>La casquette en couvercle, sur le seau, dans le sac ! Nina pose la visière, sans presser le sable. Elle écoute le sac, et retrouve le grain. Le seau rentre, chapeau dessus, léger. Le bouton rentre, et le grain reste. Le grain a parlé, comme une lanterne. La visière a tenu le seau ! La sangle a failli tout enterrer. La visière sert de couvercle au seau, grain dessus. Tu reconnais le grain, du verre ? Il a glissé du verre, tout petit.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La casquette en couvercle, sur le seau, dans le sac ! Nina pose la visière, sans presser le sable. Elle suit le &lt;emphasis level="moderate"&gt;grain de sel&lt;/emphasis&gt;, jusqu'au bouton de bois. Le seau rentre, chapeau dessus, léger. Le bouton ferme, net, sur le grain. Le grain a parlé, comme une lanterne. La visière a tenu le seau ! La sangle a failli tout enterrer. La visière sert de couvercle au seau, grain dessus. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La casquette en couvercle, sur le seau, dans le sac ! Nina pose la visière, sans presser le sable. Elle écoute le sac, et retrouve le grain. Le seau rentre, chapeau dessus, léger. Le bouton rentre, et le grain reste. Le grain a parlé, comme une lanterne. La visière a tenu le seau ! La sangle a failli tout enterrer. La visière sert de couvercle au seau, grain dessus. Tu reconnais le grain, du verre ? Il a glissé du verre, tout petit.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>La casquette en couvercle, sur le seau, dans le sac ! Nina pose la visière, sans presser le sable. Elle suit le &lt;emphasis&gt;grain de sel&lt;/emphasis&gt;, jusqu'au bouton de bois. Le seau rentre, chapeau dessus, léger. Le bouton ferme, net, sur le grain. Le grain a parlé, comme une lanterne. La visière a tenu le seau ! La sangle a failli tout enterrer. La visière sert de couvercle au seau, grain dessus. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine. [pause]</t>
+          <t>La casquette en couvercle, sur le seau, dans le sac ! Nina pose la visière, sans presser le sable. Elle écoute le sac, et retrouve le grain. Le seau rentre, chapeau dessus, léger. Le bouton rentre, et le grain reste. Le grain a parlé, comme une lanterne. La visière a tenu le seau ! La sangle a failli tout enterrer. La visière sert de couvercle au seau, grain dessus. Tu reconnais le grain, du verre ? Il a glissé du verre, tout petit. [pause]</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
@@ -5136,15 +5136,15 @@
         <is>
           <t>enfant-f|La casquette en couvercle, sur le seau, dans le sac !
 narrateur|Nina pose la visière, sans presser le sable.
-narrateur|Elle suit le grain de sel, jusqu'au bouton de bois.
+narrateur|Elle écoute le sac, et retrouve le grain.
 narrateur|Le seau rentre, chapeau dessus, léger.
-narrateur|Le bouton ferme, net, sur le grain.
+narrateur|Le bouton rentre, et le grain reste.
 papa|Le grain a parlé, comme une lanterne.
 enfant-f|La visière a tenu le seau !
 maman|La sangle a failli tout enterrer.
 narrateur|La visière sert de couvercle au seau, grain dessus.
-papa|Tu as vu le grain, sur le bouton ?
-enfant-f|Il était sur la vitre, à la cuisine.</t>
+papa|Tu reconnais le grain, du verre ?
+enfant-f|Il a glissé du verre, tout petit.</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
@@ -5753,17 +5753,17 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Le doudou dans le sac, la gourde à côté ! Nina soulève le tissu, grain après grain. Elle suit le grain de sel, jusqu'au bouton de bois. Le doudou rentre, la gourde se cale, fraîche. Le bouton ferme, net, sur le grain. Le grain a parlé, sur le bois. Il a un nid, plus le rebord ! Le sable a failli tout garder. L'oreille du doudou a un fil de sable, près du grain. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.</t>
+          <t>Le doudou dans le sac, la gourde à côté ! Nina soulève le tissu, grain après grain. Nina regarde le grain, collé au bois rêche. Le doudou rentre, la gourde se cale, fraîche. Le bois ferme, grain coincé, gentiment. Le grain a parlé, sur le bois. Il a un nid, plus le rebord ! Le sable a failli tout garder. L'oreille du doudou a un fil de sable, près du grain. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le doudou dans le sac, la gourde à côté ! Nina soulève le tissu, grain après grain. Elle suit le &lt;emphasis level="moderate"&gt;grain de sel&lt;/emphasis&gt;, jusqu'au bouton de bois. Le doudou rentre, la gourde se cale, fraîche. Le bouton ferme, net, sur le grain. Le grain a parlé, sur le bois. Il a un nid, plus le rebord ! Le sable a failli tout garder. L'oreille du doudou a un fil de sable, près du grain. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le doudou dans le sac, la gourde à côté ! Nina soulève le tissu, grain après grain. Nina regarde le grain, collé au bois rêche. Le doudou rentre, la gourde se cale, fraîche. Le bois ferme, grain coincé, gentiment. Le grain a parlé, sur le bois. Il a un nid, plus le rebord ! Le sable a failli tout garder. L'oreille du doudou a un fil de sable, près du grain. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Le doudou dans le sac, la gourde à côté ! Nina soulève le tissu, grain après grain. Elle suit le &lt;emphasis&gt;grain de sel&lt;/emphasis&gt;, jusqu'au bouton de bois. Le doudou rentre, la gourde se cale, fraîche. Le bouton ferme, net, sur le grain. Le grain a parlé, sur le bois. Il a un nid, plus le rebord ! Le sable a failli tout garder. L'oreille du doudou a un fil de sable, près du grain. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine. [pause]</t>
+          <t>Le doudou dans le sac, la gourde à côté ! Nina soulève le tissu, grain après grain. Nina regarde le grain, collé au bois rêche. Le doudou rentre, la gourde se cale, fraîche. Le bois ferme, grain coincé, gentiment. Le grain a parlé, sur le bois. Il a un nid, plus le rebord ! Le sable a failli tout garder. L'oreille du doudou a un fil de sable, près du grain. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine. [pause]</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr"/>
@@ -5899,9 +5899,9 @@
         <is>
           <t>enfant-f|Le doudou dans le sac, la gourde à côté !
 narrateur|Nina soulève le tissu, grain après grain.
-narrateur|Elle suit le grain de sel, jusqu'au bouton de bois.
+narrateur|Nina regarde le grain, collé au bois rêche.
 narrateur|Le doudou rentre, la gourde se cale, fraîche.
-narrateur|Le bouton ferme, net, sur le grain.
+narrateur|Le bois ferme, grain coincé, gentiment.
 papa|Le grain a parlé, sur le bois.
 enfant-f|Il a un nid, plus le rebord !
 maman|Le sable a failli tout garder.
@@ -6122,17 +6122,17 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>La pomme dans les bras du doudou, dans le sac ! Nina souffle le sable, sans vider le bac. Elle suit le grain de sel, jusqu'au bouton de bois. Le doudou rentre, la pomme au creux, ronde. Le bouton ferme, net, sur le grain. Le grain a parlé, très bas. Il tient le goûter, maintenant ! Le sable a failli tout garder. La pomme chauffe dans les bras du doudou. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.</t>
+          <t>La pomme dans les bras du doudou, dans le sac ! Nina souffle le sable, sans vider le bac. Le grain brille, et sa main ralentit. Le doudou rentre, la pomme au creux, ronde. Le bouton tient, grain au chaud. Le grain a parlé, très bas. Il tient le goûter, maintenant ! Le sable a failli tout garder. La pomme chauffe dans les bras du doudou. Le grain est là, tu le sens ? Oui, c'est celui de la buée.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La pomme dans les bras du doudou, dans le sac ! Nina souffle le sable, sans vider le bac. Elle suit le &lt;emphasis level="moderate"&gt;grain de sel&lt;/emphasis&gt;, jusqu'au bouton de bois. Le doudou rentre, la pomme au creux, ronde. Le bouton ferme, net, sur le grain. Le grain a parlé, très bas. Il tient le goûter, maintenant ! Le sable a failli tout garder. La pomme chauffe dans les bras du doudou. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La pomme dans les bras du doudou, dans le sac ! Nina souffle le sable, sans vider le bac. Le grain brille, et sa main ralentit. Le doudou rentre, la pomme au creux, ronde. Le bouton tient, grain au chaud. Le grain a parlé, très bas. Il tient le goûter, maintenant ! Le sable a failli tout garder. La pomme chauffe dans les bras du doudou. Le grain est là, tu le sens ? Oui, c'est celui de la buée.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>La pomme dans les bras du doudou, dans le sac ! Nina souffle le sable, sans vider le bac. Elle suit le &lt;emphasis&gt;grain de sel&lt;/emphasis&gt;, jusqu'au bouton de bois. Le doudou rentre, la pomme au creux, ronde. Le bouton ferme, net, sur le grain. Le grain a parlé, très bas. Il tient le goûter, maintenant ! Le sable a failli tout garder. La pomme chauffe dans les bras du doudou. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine. [pause]</t>
+          <t>La pomme dans les bras du doudou, dans le sac ! Nina souffle le sable, sans vider le bac. Le grain brille, et sa main ralentit. Le doudou rentre, la pomme au creux, ronde. Le bouton tient, grain au chaud. Le grain a parlé, très bas. Il tient le goûter, maintenant ! Le sable a failli tout garder. La pomme chauffe dans les bras du doudou. Le grain est là, tu le sens ? Oui, c'est celui de la buée. [pause]</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr"/>
@@ -6268,15 +6268,15 @@
         <is>
           <t>enfant-f|La pomme dans les bras du doudou, dans le sac !
 narrateur|Nina souffle le sable, sans vider le bac.
-narrateur|Elle suit le grain de sel, jusqu'au bouton de bois.
+narrateur|Le grain brille, et sa main ralentit.
 narrateur|Le doudou rentre, la pomme au creux, ronde.
-narrateur|Le bouton ferme, net, sur le grain.
+narrateur|Le bouton tient, grain au chaud.
 papa|Le grain a parlé, très bas.
 enfant-f|Il tient le goûter, maintenant !
 maman|Le sable a failli tout garder.
 narrateur|La pomme chauffe dans les bras du doudou.
-papa|Tu as vu le grain, sur le bouton ?
-enfant-f|Il était sur la vitre, à la cuisine.</t>
+papa|Le grain est là, tu le sens ?
+enfant-f|Oui, c'est celui de la buée.</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
@@ -6491,17 +6491,17 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>La casquette sur le doudou, puis dans le sac ! Nina refuse de tout vider d'un coup. Elle suit le grain de sel, jusqu'au bouton de bois. Le doudou rentre, casquette sur l'oreille. Le bouton ferme, net, sur le grain. Le grain a parlé, comme une lanterne. Il a un chapeau, et un nid ! Le sable a failli tout garder. Le doudou porte la casquette, grain sur la visière. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.</t>
+          <t>La casquette sur le doudou, puis dans le sac ! Nina refuse de tout vider d'un coup. Elle cherche le grain, du doigt, sur le bois. Le doudou rentre, casquette sur l'oreille. Le sac se cale, grain vers le tissu. Le grain a parlé, comme une lanterne. Il a un chapeau, et un nid ! Le sable a failli tout garder. Le doudou porte la casquette, grain sur la visière. Tu reconnais le grain, du verre ? Il a glissé du verre, tout petit.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La casquette sur le doudou, puis dans le sac ! Nina refuse de tout vider d'un coup. Elle suit le &lt;emphasis level="moderate"&gt;grain de sel&lt;/emphasis&gt;, jusqu'au bouton de bois. Le doudou rentre, casquette sur l'oreille. Le bouton ferme, net, sur le grain. Le grain a parlé, comme une lanterne. Il a un chapeau, et un nid ! Le sable a failli tout garder. Le doudou porte la casquette, grain sur la visière. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La casquette sur le doudou, puis dans le sac ! Nina refuse de tout vider d'un coup. Elle cherche le grain, du doigt, sur le bois. Le doudou rentre, casquette sur l'oreille. Le sac se cale, grain vers le tissu. Le grain a parlé, comme une lanterne. Il a un chapeau, et un nid ! Le sable a failli tout garder. Le doudou porte la casquette, grain sur la visière. Tu reconnais le grain, du verre ? Il a glissé du verre, tout petit.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>La casquette sur le doudou, puis dans le sac ! Nina refuse de tout vider d'un coup. Elle suit le &lt;emphasis&gt;grain de sel&lt;/emphasis&gt;, jusqu'au bouton de bois. Le doudou rentre, casquette sur l'oreille. Le bouton ferme, net, sur le grain. Le grain a parlé, comme une lanterne. Il a un chapeau, et un nid ! Le sable a failli tout garder. Le doudou porte la casquette, grain sur la visière. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine. [pause]</t>
+          <t>La casquette sur le doudou, puis dans le sac ! Nina refuse de tout vider d'un coup. Elle cherche le grain, du doigt, sur le bois. Le doudou rentre, casquette sur l'oreille. Le sac se cale, grain vers le tissu. Le grain a parlé, comme une lanterne. Il a un chapeau, et un nid ! Le sable a failli tout garder. Le doudou porte la casquette, grain sur la visière. Tu reconnais le grain, du verre ? Il a glissé du verre, tout petit. [pause]</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
@@ -6637,15 +6637,15 @@
         <is>
           <t>enfant-f|La casquette sur le doudou, puis dans le sac !
 narrateur|Nina refuse de tout vider d'un coup.
-narrateur|Elle suit le grain de sel, jusqu'au bouton de bois.
+narrateur|Elle cherche le grain, du doigt, sur le bois.
 narrateur|Le doudou rentre, casquette sur l'oreille.
-narrateur|Le bouton ferme, net, sur le grain.
+narrateur|Le sac se cale, grain vers le tissu.
 papa|Le grain a parlé, comme une lanterne.
 enfant-f|Il a un chapeau, et un nid !
 maman|Le sable a failli tout garder.
 narrateur|Le doudou porte la casquette, grain sur la visière.
-papa|Tu as vu le grain, sur le bouton ?
-enfant-f|Il était sur la vitre, à la cuisine.</t>
+papa|Tu reconnais le grain, du verre ?
+enfant-f|Il a glissé du verre, tout petit.</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
@@ -8009,17 +8009,17 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Le ballon dans le sac, la gourde pour le caler ! Nina se penche sous la rampe, sans se faufiler. Elle suit le grain de sel, jusqu'au bouton de bois. Le ballon rentre, la gourde le cale, tiède. Le bouton ferme, net, sur le grain. Le grain a parlé, sur le bois. La gourde a tenu le ballon ! Le dessous a failli tout garder. La gourde est tiède, comme la rampe, sous le grain. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.</t>
+          <t>Le ballon dans le sac, la gourde pour le caler ! Nina se penche sous la rampe, sans se faufiler. Nina aligne le grain, face à la rampe. Le ballon rentre, la gourde le cale, tiède. Le bouton ferme, tiède, sur le grain. Le grain a parlé, sur le bois. La gourde a tenu le ballon ! Le dessous a failli tout garder. La gourde est tiède, comme la rampe, sous le grain. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le ballon dans le sac, la gourde pour le caler ! Nina se penche sous la rampe, sans se faufiler. Elle suit le &lt;emphasis level="moderate"&gt;grain de sel&lt;/emphasis&gt;, jusqu'au bouton de bois. Le ballon rentre, la gourde le cale, tiède. Le bouton ferme, net, sur le grain. Le grain a parlé, sur le bois. La gourde a tenu le ballon ! Le dessous a failli tout garder. La gourde est tiède, comme la rampe, sous le grain. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le ballon dans le sac, la gourde pour le caler ! Nina se penche sous la rampe, sans se faufiler. Nina aligne le grain, face à la rampe. Le ballon rentre, la gourde le cale, tiède. Le bouton ferme, tiède, sur le grain. Le grain a parlé, sur le bois. La gourde a tenu le ballon ! Le dessous a failli tout garder. La gourde est tiède, comme la rampe, sous le grain. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Le ballon dans le sac, la gourde pour le caler ! Nina se penche sous la rampe, sans se faufiler. Elle suit le &lt;emphasis&gt;grain de sel&lt;/emphasis&gt;, jusqu'au bouton de bois. Le ballon rentre, la gourde le cale, tiède. Le bouton ferme, net, sur le grain. Le grain a parlé, sur le bois. La gourde a tenu le ballon ! Le dessous a failli tout garder. La gourde est tiède, comme la rampe, sous le grain. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine. [pause]</t>
+          <t>Le ballon dans le sac, la gourde pour le caler ! Nina se penche sous la rampe, sans se faufiler. Nina aligne le grain, face à la rampe. Le ballon rentre, la gourde le cale, tiède. Le bouton ferme, tiède, sur le grain. Le grain a parlé, sur le bois. La gourde a tenu le ballon ! Le dessous a failli tout garder. La gourde est tiède, comme la rampe, sous le grain. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine. [pause]</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr"/>
@@ -8155,9 +8155,9 @@
         <is>
           <t>enfant-f|Le ballon dans le sac, la gourde pour le caler !
 narrateur|Nina se penche sous la rampe, sans se faufiler.
-narrateur|Elle suit le grain de sel, jusqu'au bouton de bois.
+narrateur|Nina aligne le grain, face à la rampe.
 narrateur|Le ballon rentre, la gourde le cale, tiède.
-narrateur|Le bouton ferme, net, sur le grain.
+narrateur|Le bouton ferme, tiède, sur le grain.
 papa|Le grain a parlé, sur le bois.
 enfant-f|La gourde a tenu le ballon !
 maman|Le dessous a failli tout garder.
@@ -8382,17 +8382,17 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Le ballon dans le sac, la pomme pour le peser ! Nina tend le bras, sans ramper. Elle suit le grain de sel, jusqu'au bouton de bois. Le ballon rentre, la pomme pèse, ronde. Le bouton ferme, net, sur le grain. Le grain a parlé, très bas. La pomme a tenu le ballon ! Le dessous a failli tout garder. La pomme a un trait lisse, collé au grain de sel. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.</t>
+          <t>Le ballon dans le sac, la pomme pour le peser ! Nina tend le bras, sans ramper. Le grain de sel attend, sur le bouton de bois. Le ballon rentre, la pomme pèse, ronde. Le sac se ferme, grain contre la pomme. Le grain a parlé, très bas. La pomme a tenu le ballon ! Le dessous a failli tout garder. La pomme a un trait lisse, collé au grain de sel. Le grain est là, tu le sens ? Oui, c'est celui de la buée.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le ballon dans le sac, la pomme pour le peser ! Nina tend le bras, sans ramper. Elle suit le &lt;emphasis level="moderate"&gt;grain de sel&lt;/emphasis&gt;, jusqu'au bouton de bois. Le ballon rentre, la pomme pèse, ronde. Le bouton ferme, net, sur le grain. Le grain a parlé, très bas. La pomme a tenu le ballon ! Le dessous a failli tout garder. La pomme a un trait lisse, collé au grain de sel. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le ballon dans le sac, la pomme pour le peser ! Nina tend le bras, sans ramper. Le &lt;emphasis level="moderate"&gt;grain de sel&lt;/emphasis&gt; attend, sur le bouton de bois. Le ballon rentre, la pomme pèse, ronde. Le sac se ferme, grain contre la pomme. Le grain a parlé, très bas. La pomme a tenu le ballon ! Le dessous a failli tout garder. La pomme a un trait lisse, collé au grain de sel. Le grain est là, tu le sens ? Oui, c'est celui de la buée.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Le ballon dans le sac, la pomme pour le peser ! Nina tend le bras, sans ramper. Elle suit le &lt;emphasis&gt;grain de sel&lt;/emphasis&gt;, jusqu'au bouton de bois. Le ballon rentre, la pomme pèse, ronde. Le bouton ferme, net, sur le grain. Le grain a parlé, très bas. La pomme a tenu le ballon ! Le dessous a failli tout garder. La pomme a un trait lisse, collé au grain de sel. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine. [pause]</t>
+          <t>Le ballon dans le sac, la pomme pour le peser ! Nina tend le bras, sans ramper. Le &lt;emphasis&gt;grain de sel&lt;/emphasis&gt; attend, sur le bouton de bois. Le ballon rentre, la pomme pèse, ronde. Le sac se ferme, grain contre la pomme. Le grain a parlé, très bas. La pomme a tenu le ballon ! Le dessous a failli tout garder. La pomme a un trait lisse, collé au grain de sel. Le grain est là, tu le sens ? Oui, c'est celui de la buée. [pause]</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr"/>
@@ -8528,15 +8528,15 @@
         <is>
           <t>enfant-f|Le ballon dans le sac, la pomme pour le peser !
 narrateur|Nina tend le bras, sans ramper.
-narrateur|Elle suit le grain de sel, jusqu'au bouton de bois.
+narrateur|Le grain de sel attend, sur le bouton de bois.
 narrateur|Le ballon rentre, la pomme pèse, ronde.
-narrateur|Le bouton ferme, net, sur le grain.
+narrateur|Le sac se ferme, grain contre la pomme.
 papa|Le grain a parlé, très bas.
 enfant-f|La pomme a tenu le ballon !
 maman|Le dessous a failli tout garder.
 narrateur|La pomme a un trait lisse, collé au grain de sel.
-papa|Tu as vu le grain, sur le bouton ?
-enfant-f|Il était sur la vitre, à la cuisine.</t>
+papa|Le grain est là, tu le sens ?
+enfant-f|Oui, c'est celui de la buée.</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
@@ -8755,17 +8755,17 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>La casquette comme un filet, pour le ballon ! Nina glisse la visière sous la rampe, lentement. Elle suit le grain de sel, jusqu'au bouton de bois. Le ballon roule dans la visière, puis dans le sac. Le bouton ferme, net, sur le grain. Le grain a parlé, comme une lanterne. La visière a attrapé, sans foncer ! Le dessous a failli tout garder. La visière tient une poussière de rampe, près du grain. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.</t>
+          <t>La casquette comme un filet, pour le ballon ! Nina glisse la visière sous la rampe, lentement. Elle touche le grain, puis le bouton. Le ballon roule dans la visière, puis dans le sac. Le bouton de bois serre le grain, sans pincer. Le grain a parlé, comme une lanterne. La visière a attrapé, sans foncer ! Le dessous a failli tout garder. La visière tient une poussière de rampe, près du grain. Tu reconnais le grain, du verre ? Il a glissé du verre, tout petit.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La casquette comme un filet, pour le ballon ! Nina glisse la visière sous la rampe, lentement. Elle suit le &lt;emphasis level="moderate"&gt;grain de sel&lt;/emphasis&gt;, jusqu'au bouton de bois. Le ballon roule dans la visière, puis dans le sac. Le bouton ferme, net, sur le grain. Le grain a parlé, comme une lanterne. La visière a attrapé, sans foncer ! Le dessous a failli tout garder. La visière tient une poussière de rampe, près du grain. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La casquette comme un filet, pour le ballon ! Nina glisse la visière sous la rampe, lentement. Elle touche le grain, puis le bouton. Le ballon roule dans la visière, puis dans le sac. Le bouton de bois serre le grain, sans pincer. Le grain a parlé, comme une lanterne. La visière a attrapé, sans foncer ! Le dessous a failli tout garder. La visière tient une poussière de rampe, près du grain. Tu reconnais le grain, du verre ? Il a glissé du verre, tout petit.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>La casquette comme un filet, pour le ballon ! Nina glisse la visière sous la rampe, lentement. Elle suit le &lt;emphasis&gt;grain de sel&lt;/emphasis&gt;, jusqu'au bouton de bois. Le ballon roule dans la visière, puis dans le sac. Le bouton ferme, net, sur le grain. Le grain a parlé, comme une lanterne. La visière a attrapé, sans foncer ! Le dessous a failli tout garder. La visière tient une poussière de rampe, près du grain. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine. [pause]</t>
+          <t>La casquette comme un filet, pour le ballon ! Nina glisse la visière sous la rampe, lentement. Elle touche le grain, puis le bouton. Le ballon roule dans la visière, puis dans le sac. Le bouton de bois serre le grain, sans pincer. Le grain a parlé, comme une lanterne. La visière a attrapé, sans foncer ! Le dessous a failli tout garder. La visière tient une poussière de rampe, près du grain. Tu reconnais le grain, du verre ? Il a glissé du verre, tout petit. [pause]</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr"/>
@@ -8901,15 +8901,15 @@
         <is>
           <t>enfant-f|La casquette comme un filet, pour le ballon !
 narrateur|Nina glisse la visière sous la rampe, lentement.
-narrateur|Elle suit le grain de sel, jusqu'au bouton de bois.
+narrateur|Elle touche le grain, puis le bouton.
 narrateur|Le ballon roule dans la visière, puis dans le sac.
-narrateur|Le bouton ferme, net, sur le grain.
+narrateur|Le bouton de bois serre le grain, sans pincer.
 papa|Le grain a parlé, comme une lanterne.
 enfant-f|La visière a attrapé, sans foncer !
 maman|Le dessous a failli tout garder.
 narrateur|La visière tient une poussière de rampe, près du grain.
-papa|Tu as vu le grain, sur le bouton ?
-enfant-f|Il était sur la vitre, à la cuisine.</t>
+papa|Tu reconnais le grain, du verre ?
+enfant-f|Il a glissé du verre, tout petit.</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
@@ -9514,17 +9514,17 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Le seau en bas, la gourde pour l'accueillir ! Nina descend, une marche après l'autre. Elle suit le grain de sel, jusqu'au bouton de bois. Le seau rentre, la gourde au fond, fraîche. Le bouton ferme, net, sur le grain. Le grain a parlé, sur le bois. Le seau a un nid, plus la pente ! La rampe a failli tout garder. Le seau garde une goutte de rampe, sous le grain. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.</t>
+          <t>Le seau en bas, la gourde pour l'accueillir ! Nina descend, une marche après l'autre. Nina suit le grain, du pied au bois. Le seau rentre, la gourde au fond, fraîche. Le bouton parle, au pied de la rampe. Le grain a parlé, sur le bois. Le seau a un nid, plus la pente ! La rampe a failli tout garder. Le seau garde une goutte de rampe, sous le grain. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le seau en bas, la gourde pour l'accueillir ! Nina descend, une marche après l'autre. Elle suit le &lt;emphasis level="moderate"&gt;grain de sel&lt;/emphasis&gt;, jusqu'au bouton de bois. Le seau rentre, la gourde au fond, fraîche. Le bouton ferme, net, sur le grain. Le grain a parlé, sur le bois. Le seau a un nid, plus la pente ! La rampe a failli tout garder. Le seau garde une goutte de rampe, sous le grain. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le seau en bas, la gourde pour l'accueillir ! Nina descend, une marche après l'autre. Nina suit le grain, du pied au bois. Le seau rentre, la gourde au fond, fraîche. Le bouton parle, au pied de la rampe. Le grain a parlé, sur le bois. Le seau a un nid, plus la pente ! La rampe a failli tout garder. Le seau garde une goutte de rampe, sous le grain. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Le seau en bas, la gourde pour l'accueillir ! Nina descend, une marche après l'autre. Elle suit le &lt;emphasis&gt;grain de sel&lt;/emphasis&gt;, jusqu'au bouton de bois. Le seau rentre, la gourde au fond, fraîche. Le bouton ferme, net, sur le grain. Le grain a parlé, sur le bois. Le seau a un nid, plus la pente ! La rampe a failli tout garder. Le seau garde une goutte de rampe, sous le grain. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine. [pause]</t>
+          <t>Le seau en bas, la gourde pour l'accueillir ! Nina descend, une marche après l'autre. Nina suit le grain, du pied au bois. Le seau rentre, la gourde au fond, fraîche. Le bouton parle, au pied de la rampe. Le grain a parlé, sur le bois. Le seau a un nid, plus la pente ! La rampe a failli tout garder. Le seau garde une goutte de rampe, sous le grain. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine. [pause]</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
@@ -9660,9 +9660,9 @@
         <is>
           <t>enfant-f|Le seau en bas, la gourde pour l'accueillir !
 narrateur|Nina descend, une marche après l'autre.
-narrateur|Elle suit le grain de sel, jusqu'au bouton de bois.
+narrateur|Nina suit le grain, du pied au bois.
 narrateur|Le seau rentre, la gourde au fond, fraîche.
-narrateur|Le bouton ferme, net, sur le grain.
+narrateur|Le bouton parle, au pied de la rampe.
 papa|Le grain a parlé, sur le bois.
 enfant-f|Le seau a un nid, plus la pente !
 maman|La rampe a failli tout garder.
@@ -9887,17 +9887,17 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>La pomme dans le seau, après la rampe ! Nina attend que le seau se taise. Elle suit le grain de sel, jusqu'au bouton de bois. La pomme se cale, le seau rentre, tiède. Le bouton ferme, net, sur le grain. Le grain a parlé, très bas. Le goûter a voyagé, sans glisser ! La rampe a failli tout garder. Une croûte tiède sent le plastique, près du grain. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.</t>
+          <t>La pomme dans le seau, après la rampe ! Nina attend que le seau se taise. Le grain de sel tremble, et elle s'arrête. La pomme se cale, le seau rentre, tiède. Le sac pèse, grain sous la croûte. Le grain a parlé, très bas. Le goûter a voyagé, sans glisser ! La rampe a failli tout garder. Une croûte tiède sent le plastique, près du grain. Le grain est là, tu le sens ? Oui, c'est celui de la buée.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La pomme dans le seau, après la rampe ! Nina attend que le seau se taise. Elle suit le &lt;emphasis level="moderate"&gt;grain de sel&lt;/emphasis&gt;, jusqu'au bouton de bois. La pomme se cale, le seau rentre, tiède. Le bouton ferme, net, sur le grain. Le grain a parlé, très bas. Le goûter a voyagé, sans glisser ! La rampe a failli tout garder. Une croûte tiède sent le plastique, près du grain. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La pomme dans le seau, après la rampe ! Nina attend que le seau se taise. Le &lt;emphasis level="moderate"&gt;grain de sel&lt;/emphasis&gt; tremble, et elle s'arrête. La pomme se cale, le seau rentre, tiède. Le sac pèse, grain sous la croûte. Le grain a parlé, très bas. Le goûter a voyagé, sans glisser ! La rampe a failli tout garder. Une croûte tiède sent le plastique, près du grain. Le grain est là, tu le sens ? Oui, c'est celui de la buée.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>La pomme dans le seau, après la rampe ! Nina attend que le seau se taise. Elle suit le &lt;emphasis&gt;grain de sel&lt;/emphasis&gt;, jusqu'au bouton de bois. La pomme se cale, le seau rentre, tiède. Le bouton ferme, net, sur le grain. Le grain a parlé, très bas. Le goûter a voyagé, sans glisser ! La rampe a failli tout garder. Une croûte tiède sent le plastique, près du grain. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine. [pause]</t>
+          <t>La pomme dans le seau, après la rampe ! Nina attend que le seau se taise. Le &lt;emphasis&gt;grain de sel&lt;/emphasis&gt; tremble, et elle s'arrête. La pomme se cale, le seau rentre, tiède. Le sac pèse, grain sous la croûte. Le grain a parlé, très bas. Le goûter a voyagé, sans glisser ! La rampe a failli tout garder. Une croûte tiède sent le plastique, près du grain. Le grain est là, tu le sens ? Oui, c'est celui de la buée. [pause]</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr"/>
@@ -10033,15 +10033,15 @@
         <is>
           <t>enfant-f|La pomme dans le seau, après la rampe !
 narrateur|Nina attend que le seau se taise.
-narrateur|Elle suit le grain de sel, jusqu'au bouton de bois.
+narrateur|Le grain de sel tremble, et elle s'arrête.
 narrateur|La pomme se cale, le seau rentre, tiède.
-narrateur|Le bouton ferme, net, sur le grain.
+narrateur|Le sac pèse, grain sous la croûte.
 papa|Le grain a parlé, très bas.
 enfant-f|Le goûter a voyagé, sans glisser !
 maman|La rampe a failli tout garder.
 narrateur|Une croûte tiède sent le plastique, près du grain.
-papa|Tu as vu le grain, sur le bouton ?
-enfant-f|Il était sur la vitre, à la cuisine.</t>
+papa|Le grain est là, tu le sens ?
+enfant-f|Oui, c'est celui de la buée.</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
@@ -10260,17 +10260,17 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>La casquette dans le seau, puis le seau dans le sac ! Nina refuse de relancer le seau. Elle suit le grain de sel, jusqu'au bouton de bois. La visière se cale, le seau rentre, léger. Le bouton ferme, net, sur le grain. Le grain a parlé, comme une lanterne. La visière a voyagé, sans voile ! La rampe a failli tout garder. La visière a voyagé dans le seau, grain au bord. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.</t>
+          <t>La casquette dans le seau, puis le seau dans le sac ! Nina refuse de relancer le seau. Elle retrouve le grain, au milieu du bouton. La visière se cale, le seau rentre, léger. Le bouton rentre, visière au bord. Le grain a parlé, comme une lanterne. La visière a voyagé, sans voile ! La rampe a failli tout garder. La visière a voyagé dans le seau, grain au bord. Tu reconnais le grain, du verre ? Il a glissé du verre, tout petit.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La casquette dans le seau, puis le seau dans le sac ! Nina refuse de relancer le seau. Elle suit le &lt;emphasis level="moderate"&gt;grain de sel&lt;/emphasis&gt;, jusqu'au bouton de bois. La visière se cale, le seau rentre, léger. Le bouton ferme, net, sur le grain. Le grain a parlé, comme une lanterne. La visière a voyagé, sans voile ! La rampe a failli tout garder. La visière a voyagé dans le seau, grain au bord. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La casquette dans le seau, puis le seau dans le sac ! Nina refuse de relancer le seau. Elle retrouve le grain, au milieu du bouton. La visière se cale, le seau rentre, léger. Le bouton rentre, visière au bord. Le grain a parlé, comme une lanterne. La visière a voyagé, sans voile ! La rampe a failli tout garder. La visière a voyagé dans le seau, grain au bord. Tu reconnais le grain, du verre ? Il a glissé du verre, tout petit.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>La casquette dans le seau, puis le seau dans le sac ! Nina refuse de relancer le seau. Elle suit le &lt;emphasis&gt;grain de sel&lt;/emphasis&gt;, jusqu'au bouton de bois. La visière se cale, le seau rentre, léger. Le bouton ferme, net, sur le grain. Le grain a parlé, comme une lanterne. La visière a voyagé, sans voile ! La rampe a failli tout garder. La visière a voyagé dans le seau, grain au bord. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine. [pause]</t>
+          <t>La casquette dans le seau, puis le seau dans le sac ! Nina refuse de relancer le seau. Elle retrouve le grain, au milieu du bouton. La visière se cale, le seau rentre, léger. Le bouton rentre, visière au bord. Le grain a parlé, comme une lanterne. La visière a voyagé, sans voile ! La rampe a failli tout garder. La visière a voyagé dans le seau, grain au bord. Tu reconnais le grain, du verre ? Il a glissé du verre, tout petit. [pause]</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr"/>
@@ -10406,15 +10406,15 @@
         <is>
           <t>enfant-f|La casquette dans le seau, puis le seau dans le sac !
 narrateur|Nina refuse de relancer le seau.
-narrateur|Elle suit le grain de sel, jusqu'au bouton de bois.
+narrateur|Elle retrouve le grain, au milieu du bouton.
 narrateur|La visière se cale, le seau rentre, léger.
-narrateur|Le bouton ferme, net, sur le grain.
+narrateur|Le bouton rentre, visière au bord.
 papa|Le grain a parlé, comme une lanterne.
 enfant-f|La visière a voyagé, sans voile !
 maman|La rampe a failli tout garder.
 narrateur|La visière a voyagé dans le seau, grain au bord.
-papa|Tu as vu le grain, sur le bouton ?
-enfant-f|Il était sur la vitre, à la cuisine.</t>
+papa|Tu reconnais le grain, du verre ?
+enfant-f|Il a glissé du verre, tout petit.</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
@@ -11023,17 +11023,17 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Le doudou dans le sac, la gourde contre l'oreille ! Nina pose le tissu, sans le lancer. Elle suit le grain de sel, jusqu'au bouton de bois. Le doudou rentre, la gourde le cale, tiède. Le bouton ferme, net, sur le grain. Le grain a parlé, sur le bois. Il a un nid, plus le vent ! La rampe a failli l'emporter. Le doudou sent la rampe, grain de sel dans un pli. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.</t>
+          <t>Le doudou dans le sac, la gourde contre l'oreille ! Nina pose le tissu, sans le lancer. Nina pose l'oreille près du sac, et voit le grain. Le doudou rentre, la gourde le cale, tiède. Le bois ferme, grain dans un pli. Le grain a parlé, sur le bois. Il a un nid, plus le vent ! La rampe a failli l'emporter. Le doudou sent la rampe, grain de sel dans un pli. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le doudou dans le sac, la gourde contre l'oreille ! Nina pose le tissu, sans le lancer. Elle suit le &lt;emphasis level="moderate"&gt;grain de sel&lt;/emphasis&gt;, jusqu'au bouton de bois. Le doudou rentre, la gourde le cale, tiède. Le bouton ferme, net, sur le grain. Le grain a parlé, sur le bois. Il a un nid, plus le vent ! La rampe a failli l'emporter. Le doudou sent la rampe, grain de sel dans un pli. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le doudou dans le sac, la gourde contre l'oreille ! Nina pose le tissu, sans le lancer. Nina pose l'oreille près du sac, et voit le grain. Le doudou rentre, la gourde le cale, tiède. Le bois ferme, grain dans un pli. Le grain a parlé, sur le bois. Il a un nid, plus le vent ! La rampe a failli l'emporter. Le doudou sent la rampe, &lt;emphasis level="moderate"&gt;grain de sel&lt;/emphasis&gt; dans un pli. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Le doudou dans le sac, la gourde contre l'oreille ! Nina pose le tissu, sans le lancer. Elle suit le &lt;emphasis&gt;grain de sel&lt;/emphasis&gt;, jusqu'au bouton de bois. Le doudou rentre, la gourde le cale, tiède. Le bouton ferme, net, sur le grain. Le grain a parlé, sur le bois. Il a un nid, plus le vent ! La rampe a failli l'emporter. Le doudou sent la rampe, grain de sel dans un pli. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine. [pause]</t>
+          <t>Le doudou dans le sac, la gourde contre l'oreille ! Nina pose le tissu, sans le lancer. Nina pose l'oreille près du sac, et voit le grain. Le doudou rentre, la gourde le cale, tiède. Le bois ferme, grain dans un pli. Le grain a parlé, sur le bois. Il a un nid, plus le vent ! La rampe a failli l'emporter. Le doudou sent la rampe, &lt;emphasis&gt;grain de sel&lt;/emphasis&gt; dans un pli. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine. [pause]</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr"/>
@@ -11169,9 +11169,9 @@
         <is>
           <t>enfant-f|Le doudou dans le sac, la gourde contre l'oreille !
 narrateur|Nina pose le tissu, sans le lancer.
-narrateur|Elle suit le grain de sel, jusqu'au bouton de bois.
+narrateur|Nina pose l'oreille près du sac, et voit le grain.
 narrateur|Le doudou rentre, la gourde le cale, tiède.
-narrateur|Le bouton ferme, net, sur le grain.
+narrateur|Le bois ferme, grain dans un pli.
 papa|Le grain a parlé, sur le bois.
 enfant-f|Il a un nid, plus le vent !
 maman|La rampe a failli l'emporter.
@@ -11396,17 +11396,17 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>La pomme pour le doudou, dans le sac ! Nina serre moins fort, et avance. Elle suit le grain de sel, jusqu'au bouton de bois. Le doudou rentre, la pomme au creux, ronde. Le bouton ferme, net, sur le grain. Le grain a parlé, très bas. Il tient le goûter, sans le vent ! La rampe a failli l'emporter. La pomme sent le tissu du doudou, sous le grain. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.</t>
+          <t>La pomme pour le doudou, dans le sac ! Nina serre moins fort, et avance. Le grain de sel luit, contre le bois rêche. Le doudou rentre, la pomme au creux, ronde. Le bouton tient, grain contre la pomme. Le grain a parlé, très bas. Il tient le goûter, sans le vent ! La rampe a failli l'emporter. La pomme sent le tissu du doudou, sous le grain. Le grain est là, tu le sens ? Oui, c'est celui de la buée.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La pomme pour le doudou, dans le sac ! Nina serre moins fort, et avance. Elle suit le &lt;emphasis level="moderate"&gt;grain de sel&lt;/emphasis&gt;, jusqu'au bouton de bois. Le doudou rentre, la pomme au creux, ronde. Le bouton ferme, net, sur le grain. Le grain a parlé, très bas. Il tient le goûter, sans le vent ! La rampe a failli l'emporter. La pomme sent le tissu du doudou, sous le grain. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La pomme pour le doudou, dans le sac ! Nina serre moins fort, et avance. Le &lt;emphasis level="moderate"&gt;grain de sel&lt;/emphasis&gt; luit, contre le bois rêche. Le doudou rentre, la pomme au creux, ronde. Le bouton tient, grain contre la pomme. Le grain a parlé, très bas. Il tient le goûter, sans le vent ! La rampe a failli l'emporter. La pomme sent le tissu du doudou, sous le grain. Le grain est là, tu le sens ? Oui, c'est celui de la buée.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>La pomme pour le doudou, dans le sac ! Nina serre moins fort, et avance. Elle suit le &lt;emphasis&gt;grain de sel&lt;/emphasis&gt;, jusqu'au bouton de bois. Le doudou rentre, la pomme au creux, ronde. Le bouton ferme, net, sur le grain. Le grain a parlé, très bas. Il tient le goûter, sans le vent ! La rampe a failli l'emporter. La pomme sent le tissu du doudou, sous le grain. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine. [pause]</t>
+          <t>La pomme pour le doudou, dans le sac ! Nina serre moins fort, et avance. Le &lt;emphasis&gt;grain de sel&lt;/emphasis&gt; luit, contre le bois rêche. Le doudou rentre, la pomme au creux, ronde. Le bouton tient, grain contre la pomme. Le grain a parlé, très bas. Il tient le goûter, sans le vent ! La rampe a failli l'emporter. La pomme sent le tissu du doudou, sous le grain. Le grain est là, tu le sens ? Oui, c'est celui de la buée. [pause]</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
@@ -11542,15 +11542,15 @@
         <is>
           <t>enfant-f|La pomme pour le doudou, dans le sac !
 narrateur|Nina serre moins fort, et avance.
-narrateur|Elle suit le grain de sel, jusqu'au bouton de bois.
+narrateur|Le grain de sel luit, contre le bois rêche.
 narrateur|Le doudou rentre, la pomme au creux, ronde.
-narrateur|Le bouton ferme, net, sur le grain.
+narrateur|Le bouton tient, grain contre la pomme.
 papa|Le grain a parlé, très bas.
 enfant-f|Il tient le goûter, sans le vent !
 maman|La rampe a failli l'emporter.
 narrateur|La pomme sent le tissu du doudou, sous le grain.
-papa|Tu as vu le grain, sur le bouton ?
-enfant-f|Il était sur la vitre, à la cuisine.</t>
+papa|Le grain est là, tu le sens ?
+enfant-f|Oui, c'est celui de la buée.</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
@@ -11769,17 +11769,17 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>La casquette sur le doudou, avant le sac ! Nina pose la visière, oreille à l'abri. Elle suit le grain de sel, jusqu'au bouton de bois. Le doudou rentre, casquette contre le vent. Le bouton ferme, net, sur le grain. Le grain a parlé, comme une lanterne. Il a un chapeau, et un nid ! La rampe a failli l'emporter. Un poil de doudou colle à la visière, près du grain. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.</t>
+          <t>La casquette sur le doudou, avant le sac ! Nina pose la visière, oreille à l'abri. Elle garde le grain, sous l'ongle, une seconde. Le doudou rentre, casquette contre le vent. Le sac se cale, grain sous la visière. Le grain a parlé, comme une lanterne. Il a un chapeau, et un nid ! La rampe a failli l'emporter. Un poil de doudou colle à la visière, près du grain. Tu reconnais le grain, du verre ? Il a glissé du verre, tout petit.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La casquette sur le doudou, avant le sac ! Nina pose la visière, oreille à l'abri. Elle suit le &lt;emphasis level="moderate"&gt;grain de sel&lt;/emphasis&gt;, jusqu'au bouton de bois. Le doudou rentre, casquette contre le vent. Le bouton ferme, net, sur le grain. Le grain a parlé, comme une lanterne. Il a un chapeau, et un nid ! La rampe a failli l'emporter. Un poil de doudou colle à la visière, près du grain. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La casquette sur le doudou, avant le sac ! Nina pose la visière, oreille à l'abri. Elle garde le grain, sous l'ongle, une seconde. Le doudou rentre, casquette contre le vent. Le sac se cale, grain sous la visière. Le grain a parlé, comme une lanterne. Il a un chapeau, et un nid ! La rampe a failli l'emporter. Un poil de doudou colle à la visière, près du grain. Tu reconnais le grain, du verre ? Il a glissé du verre, tout petit.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>La casquette sur le doudou, avant le sac ! Nina pose la visière, oreille à l'abri. Elle suit le &lt;emphasis&gt;grain de sel&lt;/emphasis&gt;, jusqu'au bouton de bois. Le doudou rentre, casquette contre le vent. Le bouton ferme, net, sur le grain. Le grain a parlé, comme une lanterne. Il a un chapeau, et un nid ! La rampe a failli l'emporter. Un poil de doudou colle à la visière, près du grain. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine. [pause]</t>
+          <t>La casquette sur le doudou, avant le sac ! Nina pose la visière, oreille à l'abri. Elle garde le grain, sous l'ongle, une seconde. Le doudou rentre, casquette contre le vent. Le sac se cale, grain sous la visière. Le grain a parlé, comme une lanterne. Il a un chapeau, et un nid ! La rampe a failli l'emporter. Un poil de doudou colle à la visière, près du grain. Tu reconnais le grain, du verre ? Il a glissé du verre, tout petit. [pause]</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
@@ -11915,15 +11915,15 @@
         <is>
           <t>enfant-f|La casquette sur le doudou, avant le sac !
 narrateur|Nina pose la visière, oreille à l'abri.
-narrateur|Elle suit le grain de sel, jusqu'au bouton de bois.
+narrateur|Elle garde le grain, sous l'ongle, une seconde.
 narrateur|Le doudou rentre, casquette contre le vent.
-narrateur|Le bouton ferme, net, sur le grain.
+narrateur|Le sac se cale, grain sous la visière.
 papa|Le grain a parlé, comme une lanterne.
 enfant-f|Il a un chapeau, et un nid !
 maman|La rampe a failli l'emporter.
 narrateur|Un poil de doudou colle à la visière, près du grain.
-papa|Tu as vu le grain, sur le bouton ?
-enfant-f|Il était sur la vitre, à la cuisine.</t>
+papa|Tu reconnais le grain, du verre ?
+enfant-f|Il a glissé du verre, tout petit.</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
@@ -13283,17 +13283,17 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Le ballon dans le sac, la gourde pour le nid ! Nina contourne le siège, sans ramper. Elle suit le grain de sel, jusqu'au bouton de bois. Le ballon rentre, la gourde le cale, fraîche. Le bouton ferme, net, sur le grain. Le grain a parlé, sur le bois. La gourde a fait le nid ! L'ombre a failli tout garder. La gourde a une marque d'herbe, sous le grain de sel. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.</t>
+          <t>Le ballon dans le sac, la gourde pour le nid ! Nina contourne le siège, sans ramper. Nina contourne le grain, puis le bouton. Le ballon rentre, la gourde le cale, fraîche. Le bouton ferme, frais, sur le grain. Le grain a parlé, sur le bois. La gourde a fait le nid ! L'ombre a failli tout garder. La gourde a une marque d'herbe, sous le grain de sel. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le ballon dans le sac, la gourde pour le nid ! Nina contourne le siège, sans ramper. Elle suit le &lt;emphasis level="moderate"&gt;grain de sel&lt;/emphasis&gt;, jusqu'au bouton de bois. Le ballon rentre, la gourde le cale, fraîche. Le bouton ferme, net, sur le grain. Le grain a parlé, sur le bois. La gourde a fait le nid ! L'ombre a failli tout garder. La gourde a une marque d'herbe, sous le grain de sel. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le ballon dans le sac, la gourde pour le nid ! Nina contourne le siège, sans ramper. Nina contourne le grain, puis le bouton. Le ballon rentre, la gourde le cale, fraîche. Le bouton ferme, frais, sur le grain. Le grain a parlé, sur le bois. La gourde a fait le nid ! L'ombre a failli tout garder. La gourde a une marque d'herbe, sous le &lt;emphasis level="moderate"&gt;grain de sel&lt;/emphasis&gt;. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Le ballon dans le sac, la gourde pour le nid ! Nina contourne le siège, sans ramper. Elle suit le &lt;emphasis&gt;grain de sel&lt;/emphasis&gt;, jusqu'au bouton de bois. Le ballon rentre, la gourde le cale, fraîche. Le bouton ferme, net, sur le grain. Le grain a parlé, sur le bois. La gourde a fait le nid ! L'ombre a failli tout garder. La gourde a une marque d'herbe, sous le grain de sel. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine. [pause]</t>
+          <t>Le ballon dans le sac, la gourde pour le nid ! Nina contourne le siège, sans ramper. Nina contourne le grain, puis le bouton. Le ballon rentre, la gourde le cale, fraîche. Le bouton ferme, frais, sur le grain. Le grain a parlé, sur le bois. La gourde a fait le nid ! L'ombre a failli tout garder. La gourde a une marque d'herbe, sous le &lt;emphasis&gt;grain de sel&lt;/emphasis&gt;. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine. [pause]</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr"/>
@@ -13429,9 +13429,9 @@
         <is>
           <t>enfant-f|Le ballon dans le sac, la gourde pour le nid !
 narrateur|Nina contourne le siège, sans ramper.
-narrateur|Elle suit le grain de sel, jusqu'au bouton de bois.
+narrateur|Nina contourne le grain, puis le bouton.
 narrateur|Le ballon rentre, la gourde le cale, fraîche.
-narrateur|Le bouton ferme, net, sur le grain.
+narrateur|Le bouton ferme, frais, sur le grain.
 papa|Le grain a parlé, sur le bois.
 enfant-f|La gourde a fait le nid !
 maman|L'ombre a failli tout garder.
@@ -13656,17 +13656,17 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>La pomme comme un siège, pour le ballon, dans le sac ! Nina tend le bras derrière, sans se coucher. Elle suit le grain de sel, jusqu'au bouton de bois. Le ballon rentre, la pomme le cale, froide. Le bouton ferme, net, sur le grain. Le grain a parlé, très bas. La pomme a tenu le ballon ! L'ombre a failli tout garder. La pomme est froide, comme la chaîne, près du grain. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.</t>
+          <t>La pomme comme un siège, pour le ballon, dans le sac ! Nina tend le bras derrière, sans se coucher. Le grain de sel pique, comme à la vitre. Le ballon rentre, la pomme le cale, froide. Le sac se ferme, grain contre la chaîne. Le grain a parlé, très bas. La pomme a tenu le ballon ! L'ombre a failli tout garder. La pomme est froide, comme la chaîne, près du grain. Le grain est là, tu le sens ? Oui, c'est celui de la buée.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La pomme comme un siège, pour le ballon, dans le sac ! Nina tend le bras derrière, sans se coucher. Elle suit le &lt;emphasis level="moderate"&gt;grain de sel&lt;/emphasis&gt;, jusqu'au bouton de bois. Le ballon rentre, la pomme le cale, froide. Le bouton ferme, net, sur le grain. Le grain a parlé, très bas. La pomme a tenu le ballon ! L'ombre a failli tout garder. La pomme est froide, comme la chaîne, près du grain. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La pomme comme un siège, pour le ballon, dans le sac ! Nina tend le bras derrière, sans se coucher. Le &lt;emphasis level="moderate"&gt;grain de sel&lt;/emphasis&gt; pique, comme à la vitre. Le ballon rentre, la pomme le cale, froide. Le sac se ferme, grain contre la chaîne. Le grain a parlé, très bas. La pomme a tenu le ballon ! L'ombre a failli tout garder. La pomme est froide, comme la chaîne, près du grain. Le grain est là, tu le sens ? Oui, c'est celui de la buée.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>La pomme comme un siège, pour le ballon, dans le sac ! Nina tend le bras derrière, sans se coucher. Elle suit le &lt;emphasis&gt;grain de sel&lt;/emphasis&gt;, jusqu'au bouton de bois. Le ballon rentre, la pomme le cale, froide. Le bouton ferme, net, sur le grain. Le grain a parlé, très bas. La pomme a tenu le ballon ! L'ombre a failli tout garder. La pomme est froide, comme la chaîne, près du grain. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine. [pause]</t>
+          <t>La pomme comme un siège, pour le ballon, dans le sac ! Nina tend le bras derrière, sans se coucher. Le &lt;emphasis&gt;grain de sel&lt;/emphasis&gt; pique, comme à la vitre. Le ballon rentre, la pomme le cale, froide. Le sac se ferme, grain contre la chaîne. Le grain a parlé, très bas. La pomme a tenu le ballon ! L'ombre a failli tout garder. La pomme est froide, comme la chaîne, près du grain. Le grain est là, tu le sens ? Oui, c'est celui de la buée. [pause]</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr"/>
@@ -13802,15 +13802,15 @@
         <is>
           <t>enfant-f|La pomme comme un siège, pour le ballon, dans le sac !
 narrateur|Nina tend le bras derrière, sans se coucher.
-narrateur|Elle suit le grain de sel, jusqu'au bouton de bois.
+narrateur|Le grain de sel pique, comme à la vitre.
 narrateur|Le ballon rentre, la pomme le cale, froide.
-narrateur|Le bouton ferme, net, sur le grain.
+narrateur|Le sac se ferme, grain contre la chaîne.
 papa|Le grain a parlé, très bas.
 enfant-f|La pomme a tenu le ballon !
 maman|L'ombre a failli tout garder.
 narrateur|La pomme est froide, comme la chaîne, près du grain.
-papa|Tu as vu le grain, sur le bouton ?
-enfant-f|Il était sur la vitre, à la cuisine.</t>
+papa|Le grain est là, tu le sens ?
+enfant-f|Oui, c'est celui de la buée.</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
@@ -14025,17 +14025,17 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>La casquette comme un hamac, pour le ballon ! Nina glisse la visière sous le siège, lentement. Elle suit le grain de sel, jusqu'au bouton de bois. Le ballon roule dans la visière, puis dans le sac. Le bouton ferme, net, sur le grain. Le grain a parlé, comme une lanterne. La visière a attrapé, sans ramper ! L'ombre a failli tout garder. La visière a un pli de chaîne, sous le grain de sel. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.</t>
+          <t>La casquette comme un hamac, pour le ballon ! Nina glisse la visière sous le siège, lentement. Elle reconnaît le grain, minuscule, sur le bois. Le ballon roule dans la visière, puis dans le sac. Le bouton de bois accueille le grain, et tient. Le grain a parlé, comme une lanterne. La visière a attrapé, sans ramper ! L'ombre a failli tout garder. La visière a un pli de chaîne, sous le grain de sel. Tu reconnais le grain, du verre ? Il a glissé du verre, tout petit.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La casquette comme un hamac, pour le ballon ! Nina glisse la visière sous le siège, lentement. Elle suit le &lt;emphasis level="moderate"&gt;grain de sel&lt;/emphasis&gt;, jusqu'au bouton de bois. Le ballon roule dans la visière, puis dans le sac. Le bouton ferme, net, sur le grain. Le grain a parlé, comme une lanterne. La visière a attrapé, sans ramper ! L'ombre a failli tout garder. La visière a un pli de chaîne, sous le grain de sel. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La casquette comme un hamac, pour le ballon ! Nina glisse la visière sous le siège, lentement. Elle reconnaît le grain, minuscule, sur le bois. Le ballon roule dans la visière, puis dans le sac. Le bouton de bois accueille le grain, et tient. Le grain a parlé, comme une lanterne. La visière a attrapé, sans ramper ! L'ombre a failli tout garder. La visière a un pli de chaîne, sous le &lt;emphasis level="moderate"&gt;grain de sel&lt;/emphasis&gt;. Tu reconnais le grain, du verre ? Il a glissé du verre, tout petit.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>La casquette comme un hamac, pour le ballon ! Nina glisse la visière sous le siège, lentement. Elle suit le &lt;emphasis&gt;grain de sel&lt;/emphasis&gt;, jusqu'au bouton de bois. Le ballon roule dans la visière, puis dans le sac. Le bouton ferme, net, sur le grain. Le grain a parlé, comme une lanterne. La visière a attrapé, sans ramper ! L'ombre a failli tout garder. La visière a un pli de chaîne, sous le grain de sel. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine. [pause]</t>
+          <t>La casquette comme un hamac, pour le ballon ! Nina glisse la visière sous le siège, lentement. Elle reconnaît le grain, minuscule, sur le bois. Le ballon roule dans la visière, puis dans le sac. Le bouton de bois accueille le grain, et tient. Le grain a parlé, comme une lanterne. La visière a attrapé, sans ramper ! L'ombre a failli tout garder. La visière a un pli de chaîne, sous le &lt;emphasis&gt;grain de sel&lt;/emphasis&gt;. Tu reconnais le grain, du verre ? Il a glissé du verre, tout petit. [pause]</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr"/>
@@ -14171,15 +14171,15 @@
         <is>
           <t>enfant-f|La casquette comme un hamac, pour le ballon !
 narrateur|Nina glisse la visière sous le siège, lentement.
-narrateur|Elle suit le grain de sel, jusqu'au bouton de bois.
+narrateur|Elle reconnaît le grain, minuscule, sur le bois.
 narrateur|Le ballon roule dans la visière, puis dans le sac.
-narrateur|Le bouton ferme, net, sur le grain.
+narrateur|Le bouton de bois accueille le grain, et tient.
 papa|Le grain a parlé, comme une lanterne.
 enfant-f|La visière a attrapé, sans ramper !
 maman|L'ombre a failli tout garder.
 narrateur|La visière a un pli de chaîne, sous le grain de sel.
-papa|Tu as vu le grain, sur le bouton ?
-enfant-f|Il était sur la vitre, à la cuisine.</t>
+papa|Tu reconnais le grain, du verre ?
+enfant-f|Il a glissé du verre, tout petit.</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
@@ -14788,17 +14788,17 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Je décroche le seau, puis la gourde dans le sac ! Nina tourne la sangle, sans tirer. Elle suit le grain de sel, jusqu'au bouton de bois. Le seau rentre, la gourde au fond, fraîche. Le bouton ferme, net, sur le grain. Le grain a parlé, sur le bois. Le seau est libre, et dedans ! La chaîne a failli tout garder. Le seau sent l'herbe, grain de sel au fond. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.</t>
+          <t>Je décroche le seau, puis la gourde dans le sac ! Nina tourne la sangle, sans tirer. Nina souffle sur le grain, collé au bouton. Le seau rentre, la gourde au fond, fraîche. Le bouton parle, seau libre. Le grain a parlé, sur le bois. Le seau est libre, et dedans ! La chaîne a failli tout garder. Le seau sent l'herbe, grain de sel au fond. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Je décroche le seau, puis la gourde dans le sac ! Nina tourne la sangle, sans tirer. Elle suit le &lt;emphasis level="moderate"&gt;grain de sel&lt;/emphasis&gt;, jusqu'au bouton de bois. Le seau rentre, la gourde au fond, fraîche. Le bouton ferme, net, sur le grain. Le grain a parlé, sur le bois. Le seau est libre, et dedans ! La chaîne a failli tout garder. Le seau sent l'herbe, grain de sel au fond. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Je décroche le seau, puis la gourde dans le sac ! Nina tourne la sangle, sans tirer. Nina souffle sur le grain, collé au bouton. Le seau rentre, la gourde au fond, fraîche. Le bouton parle, seau libre. Le grain a parlé, sur le bois. Le seau est libre, et dedans ! La chaîne a failli tout garder. Le seau sent l'herbe, &lt;emphasis level="moderate"&gt;grain de sel&lt;/emphasis&gt; au fond. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Je décroche le seau, puis la gourde dans le sac ! Nina tourne la sangle, sans tirer. Elle suit le &lt;emphasis&gt;grain de sel&lt;/emphasis&gt;, jusqu'au bouton de bois. Le seau rentre, la gourde au fond, fraîche. Le bouton ferme, net, sur le grain. Le grain a parlé, sur le bois. Le seau est libre, et dedans ! La chaîne a failli tout garder. Le seau sent l'herbe, grain de sel au fond. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine. [pause]</t>
+          <t>Je décroche le seau, puis la gourde dans le sac ! Nina tourne la sangle, sans tirer. Nina souffle sur le grain, collé au bouton. Le seau rentre, la gourde au fond, fraîche. Le bouton parle, seau libre. Le grain a parlé, sur le bois. Le seau est libre, et dedans ! La chaîne a failli tout garder. Le seau sent l'herbe, &lt;emphasis&gt;grain de sel&lt;/emphasis&gt; au fond. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine. [pause]</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr"/>
@@ -14934,9 +14934,9 @@
         <is>
           <t>enfant-f|Je décroche le seau, puis la gourde dans le sac !
 narrateur|Nina tourne la sangle, sans tirer.
-narrateur|Elle suit le grain de sel, jusqu'au bouton de bois.
+narrateur|Nina souffle sur le grain, collé au bouton.
 narrateur|Le seau rentre, la gourde au fond, fraîche.
-narrateur|Le bouton ferme, net, sur le grain.
+narrateur|Le bouton parle, seau libre.
 papa|Le grain a parlé, sur le bois.
 enfant-f|Le seau est libre, et dedans !
 maman|La chaîne a failli tout garder.
@@ -15161,17 +15161,17 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>La pomme dans le seau, quand la sangle est libre ! Nina attend que la chaîne se taise. Elle suit le grain de sel, jusqu'au bouton de bois. La pomme se cale, le seau rentre, léger. Le bouton ferme, net, sur le grain. Le grain a parlé, très bas. Le goûter a un seau, sans chaîne ! La chaîne a failli tout garder. Une croûte garde l'ombre de la chaîne, près du grain. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.</t>
+          <t>La pomme dans le seau, quand la sangle est libre ! Nina attend que la chaîne se taise. Le grain de sel reste, malgré la chaîne. La pomme se cale, le seau rentre, léger. Le sac pèse, grain près de la croûte. Le grain a parlé, très bas. Le goûter a un seau, sans chaîne ! La chaîne a failli tout garder. Une croûte garde l'ombre de la chaîne, près du grain. Le grain est là, tu le sens ? Oui, c'est celui de la buée.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La pomme dans le seau, quand la sangle est libre ! Nina attend que la chaîne se taise. Elle suit le &lt;emphasis level="moderate"&gt;grain de sel&lt;/emphasis&gt;, jusqu'au bouton de bois. La pomme se cale, le seau rentre, léger. Le bouton ferme, net, sur le grain. Le grain a parlé, très bas. Le goûter a un seau, sans chaîne ! La chaîne a failli tout garder. Une croûte garde l'ombre de la chaîne, près du grain. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La pomme dans le seau, quand la sangle est libre ! Nina attend que la chaîne se taise. Le &lt;emphasis level="moderate"&gt;grain de sel&lt;/emphasis&gt; reste, malgré la chaîne. La pomme se cale, le seau rentre, léger. Le sac pèse, grain près de la croûte. Le grain a parlé, très bas. Le goûter a un seau, sans chaîne ! La chaîne a failli tout garder. Une croûte garde l'ombre de la chaîne, près du grain. Le grain est là, tu le sens ? Oui, c'est celui de la buée.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>La pomme dans le seau, quand la sangle est libre ! Nina attend que la chaîne se taise. Elle suit le &lt;emphasis&gt;grain de sel&lt;/emphasis&gt;, jusqu'au bouton de bois. La pomme se cale, le seau rentre, léger. Le bouton ferme, net, sur le grain. Le grain a parlé, très bas. Le goûter a un seau, sans chaîne ! La chaîne a failli tout garder. Une croûte garde l'ombre de la chaîne, près du grain. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine. [pause]</t>
+          <t>La pomme dans le seau, quand la sangle est libre ! Nina attend que la chaîne se taise. Le &lt;emphasis&gt;grain de sel&lt;/emphasis&gt; reste, malgré la chaîne. La pomme se cale, le seau rentre, léger. Le sac pèse, grain près de la croûte. Le grain a parlé, très bas. Le goûter a un seau, sans chaîne ! La chaîne a failli tout garder. Une croûte garde l'ombre de la chaîne, près du grain. Le grain est là, tu le sens ? Oui, c'est celui de la buée. [pause]</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr"/>
@@ -15307,15 +15307,15 @@
         <is>
           <t>enfant-f|La pomme dans le seau, quand la sangle est libre !
 narrateur|Nina attend que la chaîne se taise.
-narrateur|Elle suit le grain de sel, jusqu'au bouton de bois.
+narrateur|Le grain de sel reste, malgré la chaîne.
 narrateur|La pomme se cale, le seau rentre, léger.
-narrateur|Le bouton ferme, net, sur le grain.
+narrateur|Le sac pèse, grain près de la croûte.
 papa|Le grain a parlé, très bas.
 enfant-f|Le goûter a un seau, sans chaîne !
 maman|La chaîne a failli tout garder.
 narrateur|Une croûte garde l'ombre de la chaîne, près du grain.
-papa|Tu as vu le grain, sur le bouton ?
-enfant-f|Il était sur la vitre, à la cuisine.</t>
+papa|Le grain est là, tu le sens ?
+enfant-f|Oui, c'est celui de la buée.</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
@@ -15530,17 +15530,17 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>La casquette pour ombrer le seau, dans le sac ! Nina décroche, puis pose la visière. Elle suit le grain de sel, jusqu'au bouton de bois. Le seau rentre, casquette dessus, léger. Le bouton ferme, net, sur le grain. Le grain a parlé, comme une lanterne. La visière a ombré, sans tirer ! La chaîne a failli tout garder. La visière ombre le seau, grain de sel au milieu. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.</t>
+          <t>La casquette pour ombrer le seau, dans le sac ! Nina décroche, puis pose la visière. Elle suit le grain, de l'herbe au bois. Le seau rentre, casquette dessus, léger. Le bouton rentre, visière au milieu. Le grain a parlé, comme une lanterne. La visière a ombré, sans tirer ! La chaîne a failli tout garder. La visière ombre le seau, grain de sel au milieu. Tu reconnais le grain, du verre ? Il a glissé du verre, tout petit.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La casquette pour ombrer le seau, dans le sac ! Nina décroche, puis pose la visière. Elle suit le &lt;emphasis level="moderate"&gt;grain de sel&lt;/emphasis&gt;, jusqu'au bouton de bois. Le seau rentre, casquette dessus, léger. Le bouton ferme, net, sur le grain. Le grain a parlé, comme une lanterne. La visière a ombré, sans tirer ! La chaîne a failli tout garder. La visière ombre le seau, grain de sel au milieu. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La casquette pour ombrer le seau, dans le sac ! Nina décroche, puis pose la visière. Elle suit le grain, de l'herbe au bois. Le seau rentre, casquette dessus, léger. Le bouton rentre, visière au milieu. Le grain a parlé, comme une lanterne. La visière a ombré, sans tirer ! La chaîne a failli tout garder. La visière ombre le seau, &lt;emphasis level="moderate"&gt;grain de sel&lt;/emphasis&gt; au milieu. Tu reconnais le grain, du verre ? Il a glissé du verre, tout petit.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>La casquette pour ombrer le seau, dans le sac ! Nina décroche, puis pose la visière. Elle suit le &lt;emphasis&gt;grain de sel&lt;/emphasis&gt;, jusqu'au bouton de bois. Le seau rentre, casquette dessus, léger. Le bouton ferme, net, sur le grain. Le grain a parlé, comme une lanterne. La visière a ombré, sans tirer ! La chaîne a failli tout garder. La visière ombre le seau, grain de sel au milieu. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine. [pause]</t>
+          <t>La casquette pour ombrer le seau, dans le sac ! Nina décroche, puis pose la visière. Elle suit le grain, de l'herbe au bois. Le seau rentre, casquette dessus, léger. Le bouton rentre, visière au milieu. Le grain a parlé, comme une lanterne. La visière a ombré, sans tirer ! La chaîne a failli tout garder. La visière ombre le seau, &lt;emphasis&gt;grain de sel&lt;/emphasis&gt; au milieu. Tu reconnais le grain, du verre ? Il a glissé du verre, tout petit. [pause]</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr"/>
@@ -15676,15 +15676,15 @@
         <is>
           <t>enfant-f|La casquette pour ombrer le seau, dans le sac !
 narrateur|Nina décroche, puis pose la visière.
-narrateur|Elle suit le grain de sel, jusqu'au bouton de bois.
+narrateur|Elle suit le grain, de l'herbe au bois.
 narrateur|Le seau rentre, casquette dessus, léger.
-narrateur|Le bouton ferme, net, sur le grain.
+narrateur|Le bouton rentre, visière au milieu.
 papa|Le grain a parlé, comme une lanterne.
 enfant-f|La visière a ombré, sans tirer !
 maman|La chaîne a failli tout garder.
 narrateur|La visière ombre le seau, grain de sel au milieu.
-papa|Tu as vu le grain, sur le bouton ?
-enfant-f|Il était sur la vitre, à la cuisine.</t>
+papa|Tu reconnais le grain, du verre ?
+enfant-f|Il a glissé du verre, tout petit.</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
@@ -16293,17 +16293,17 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Je libère l'oreille, puis la gourde dans le sac ! Nina ouvre la chaîne, sans arracher. Elle suit le grain de sel, jusqu'au bouton de bois. Le doudou rentre, la gourde contre l'oreille. Le bouton ferme, net, sur le grain. Le grain a parlé, sur le bois. L'oreille est libre, et au nid ! La chaîne a failli tout garder. L'oreille du doudou sent l'herbe, sous le grain de sel. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.</t>
+          <t>Je libère l'oreille, puis la gourde dans le sac ! Nina ouvre la chaîne, sans arracher. Nina libère l'oreille, puis voit le grain. Le doudou rentre, la gourde contre l'oreille. Le bois ferme, grain contre l'oreille. Le grain a parlé, sur le bois. L'oreille est libre, et au nid ! La chaîne a failli tout garder. L'oreille du doudou sent l'herbe, sous le grain de sel. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Je libère l'oreille, puis la gourde dans le sac ! Nina ouvre la chaîne, sans arracher. Elle suit le &lt;emphasis level="moderate"&gt;grain de sel&lt;/emphasis&gt;, jusqu'au bouton de bois. Le doudou rentre, la gourde contre l'oreille. Le bouton ferme, net, sur le grain. Le grain a parlé, sur le bois. L'oreille est libre, et au nid ! La chaîne a failli tout garder. L'oreille du doudou sent l'herbe, sous le grain de sel. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Je libère l'oreille, puis la gourde dans le sac ! Nina ouvre la chaîne, sans arracher. Nina libère l'oreille, puis voit le grain. Le doudou rentre, la gourde contre l'oreille. Le bois ferme, grain contre l'oreille. Le grain a parlé, sur le bois. L'oreille est libre, et au nid ! La chaîne a failli tout garder. L'oreille du doudou sent l'herbe, sous le &lt;emphasis level="moderate"&gt;grain de sel&lt;/emphasis&gt;. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Je libère l'oreille, puis la gourde dans le sac ! Nina ouvre la chaîne, sans arracher. Elle suit le &lt;emphasis&gt;grain de sel&lt;/emphasis&gt;, jusqu'au bouton de bois. Le doudou rentre, la gourde contre l'oreille. Le bouton ferme, net, sur le grain. Le grain a parlé, sur le bois. L'oreille est libre, et au nid ! La chaîne a failli tout garder. L'oreille du doudou sent l'herbe, sous le grain de sel. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine. [pause]</t>
+          <t>Je libère l'oreille, puis la gourde dans le sac ! Nina ouvre la chaîne, sans arracher. Nina libère l'oreille, puis voit le grain. Le doudou rentre, la gourde contre l'oreille. Le bois ferme, grain contre l'oreille. Le grain a parlé, sur le bois. L'oreille est libre, et au nid ! La chaîne a failli tout garder. L'oreille du doudou sent l'herbe, sous le &lt;emphasis&gt;grain de sel&lt;/emphasis&gt;. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine. [pause]</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr"/>
@@ -16439,9 +16439,9 @@
         <is>
           <t>enfant-f|Je libère l'oreille, puis la gourde dans le sac !
 narrateur|Nina ouvre la chaîne, sans arracher.
-narrateur|Elle suit le grain de sel, jusqu'au bouton de bois.
+narrateur|Nina libère l'oreille, puis voit le grain.
 narrateur|Le doudou rentre, la gourde contre l'oreille.
-narrateur|Le bouton ferme, net, sur le grain.
+narrateur|Le bois ferme, grain contre l'oreille.
 papa|Le grain a parlé, sur le bois.
 enfant-f|L'oreille est libre, et au nid !
 maman|La chaîne a failli tout garder.
@@ -16666,17 +16666,17 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>La pomme pour réchauffer l'oreille, dans le sac ! Nina ouvre la chaîne, un maillon après l'autre. Elle suit le grain de sel, jusqu'au bouton de bois. Le doudou rentre, la pomme contre l'oreille. Le bouton ferme, net, sur le grain. Le grain a parlé, très bas. L'oreille a un goûter, maintenant ! La chaîne a failli tout garder. La pomme a réchauffé l'oreille, près du grain de sel. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.</t>
+          <t>La pomme pour réchauffer l'oreille, dans le sac ! Nina ouvre la chaîne, un maillon après l'autre. Le grain de sel chauffe, sous son doigt. Le doudou rentre, la pomme contre l'oreille. Le bouton tient, grain près de la pomme. Le grain a parlé, très bas. L'oreille a un goûter, maintenant ! La chaîne a failli tout garder. La pomme a réchauffé l'oreille, près du grain de sel. Le grain est là, tu le sens ? Oui, c'est celui de la buée.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La pomme pour réchauffer l'oreille, dans le sac ! Nina ouvre la chaîne, un maillon après l'autre. Elle suit le &lt;emphasis level="moderate"&gt;grain de sel&lt;/emphasis&gt;, jusqu'au bouton de bois. Le doudou rentre, la pomme contre l'oreille. Le bouton ferme, net, sur le grain. Le grain a parlé, très bas. L'oreille a un goûter, maintenant ! La chaîne a failli tout garder. La pomme a réchauffé l'oreille, près du grain de sel. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La pomme pour réchauffer l'oreille, dans le sac ! Nina ouvre la chaîne, un maillon après l'autre. Le &lt;emphasis level="moderate"&gt;grain de sel&lt;/emphasis&gt; chauffe, sous son doigt. Le doudou rentre, la pomme contre l'oreille. Le bouton tient, grain près de la pomme. Le grain a parlé, très bas. L'oreille a un goûter, maintenant ! La chaîne a failli tout garder. La pomme a réchauffé l'oreille, près du grain de sel. Le grain est là, tu le sens ? Oui, c'est celui de la buée.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>La pomme pour réchauffer l'oreille, dans le sac ! Nina ouvre la chaîne, un maillon après l'autre. Elle suit le &lt;emphasis&gt;grain de sel&lt;/emphasis&gt;, jusqu'au bouton de bois. Le doudou rentre, la pomme contre l'oreille. Le bouton ferme, net, sur le grain. Le grain a parlé, très bas. L'oreille a un goûter, maintenant ! La chaîne a failli tout garder. La pomme a réchauffé l'oreille, près du grain de sel. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine. [pause]</t>
+          <t>La pomme pour réchauffer l'oreille, dans le sac ! Nina ouvre la chaîne, un maillon après l'autre. Le &lt;emphasis&gt;grain de sel&lt;/emphasis&gt; chauffe, sous son doigt. Le doudou rentre, la pomme contre l'oreille. Le bouton tient, grain près de la pomme. Le grain a parlé, très bas. L'oreille a un goûter, maintenant ! La chaîne a failli tout garder. La pomme a réchauffé l'oreille, près du grain de sel. Le grain est là, tu le sens ? Oui, c'est celui de la buée. [pause]</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr"/>
@@ -16812,15 +16812,15 @@
         <is>
           <t>enfant-f|La pomme pour réchauffer l'oreille, dans le sac !
 narrateur|Nina ouvre la chaîne, un maillon après l'autre.
-narrateur|Elle suit le grain de sel, jusqu'au bouton de bois.
+narrateur|Le grain de sel chauffe, sous son doigt.
 narrateur|Le doudou rentre, la pomme contre l'oreille.
-narrateur|Le bouton ferme, net, sur le grain.
+narrateur|Le bouton tient, grain près de la pomme.
 papa|Le grain a parlé, très bas.
 enfant-f|L'oreille a un goûter, maintenant !
 maman|La chaîne a failli tout garder.
 narrateur|La pomme a réchauffé l'oreille, près du grain de sel.
-papa|Tu as vu le grain, sur le bouton ?
-enfant-f|Il était sur la vitre, à la cuisine.</t>
+papa|Le grain est là, tu le sens ?
+enfant-f|Oui, c'est celui de la buée.</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
@@ -17039,17 +17039,17 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>La casquette sur l'oreille, puis dans le sac ! Nina ouvre la chaîne, sans tirer le tissu. Elle suit le grain de sel, jusqu'au bouton de bois. Le doudou rentre, casquette sur l'oreille libre. Le bouton ferme, net, sur le grain. Le grain a parlé, comme une lanterne. Il a un chapeau, et un nid ! La chaîne a failli tout garder. Un dessin de chaîne reste sur la visière, sous le grain. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.</t>
+          <t>La casquette sur l'oreille, puis dans le sac ! Nina ouvre la chaîne, sans tirer le tissu. Elle pose le doigt au centre du bouton, sur le grain. Le doudou rentre, casquette sur l'oreille libre. Le sac se cale, grain sous le dessin. Le grain a parlé, comme une lanterne. Il a un chapeau, et un nid ! La chaîne a failli tout garder. Un dessin de chaîne reste sur la visière, sous le grain. Tu reconnais le grain, du verre ? Il a glissé du verre, tout petit.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La casquette sur l'oreille, puis dans le sac ! Nina ouvre la chaîne, sans tirer le tissu. Elle suit le &lt;emphasis level="moderate"&gt;grain de sel&lt;/emphasis&gt;, jusqu'au bouton de bois. Le doudou rentre, casquette sur l'oreille libre. Le bouton ferme, net, sur le grain. Le grain a parlé, comme une lanterne. Il a un chapeau, et un nid ! La chaîne a failli tout garder. Un dessin de chaîne reste sur la visière, sous le grain. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La casquette sur l'oreille, puis dans le sac ! Nina ouvre la chaîne, sans tirer le tissu. Elle pose le doigt au centre du bouton, sur le grain. Le doudou rentre, casquette sur l'oreille libre. Le sac se cale, grain sous le dessin. Le grain a parlé, comme une lanterne. Il a un chapeau, et un nid ! La chaîne a failli tout garder. Un dessin de chaîne reste sur la visière, sous le grain. Tu reconnais le grain, du verre ? Il a glissé du verre, tout petit.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>La casquette sur l'oreille, puis dans le sac ! Nina ouvre la chaîne, sans tirer le tissu. Elle suit le &lt;emphasis&gt;grain de sel&lt;/emphasis&gt;, jusqu'au bouton de bois. Le doudou rentre, casquette sur l'oreille libre. Le bouton ferme, net, sur le grain. Le grain a parlé, comme une lanterne. Il a un chapeau, et un nid ! La chaîne a failli tout garder. Un dessin de chaîne reste sur la visière, sous le grain. Tu as vu le grain, sur le bouton ? Il était sur la vitre, à la cuisine. [pause]</t>
+          <t>La casquette sur l'oreille, puis dans le sac ! Nina ouvre la chaîne, sans tirer le tissu. Elle pose le doigt au centre du bouton, sur le grain. Le doudou rentre, casquette sur l'oreille libre. Le sac se cale, grain sous le dessin. Le grain a parlé, comme une lanterne. Il a un chapeau, et un nid ! La chaîne a failli tout garder. Un dessin de chaîne reste sur la visière, sous le grain. Tu reconnais le grain, du verre ? Il a glissé du verre, tout petit. [pause]</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr"/>
@@ -17185,15 +17185,15 @@
         <is>
           <t>enfant-f|La casquette sur l'oreille, puis dans le sac !
 narrateur|Nina ouvre la chaîne, sans tirer le tissu.
-narrateur|Elle suit le grain de sel, jusqu'au bouton de bois.
+narrateur|Elle pose le doigt au centre du bouton, sur le grain.
 narrateur|Le doudou rentre, casquette sur l'oreille libre.
-narrateur|Le bouton ferme, net, sur le grain.
+narrateur|Le sac se cale, grain sous le dessin.
 papa|Le grain a parlé, comme une lanterne.
 enfant-f|Il a un chapeau, et un nid !
 maman|La chaîne a failli tout garder.
 narrateur|Un dessin de chaîne reste sur la visière, sous le grain.
-papa|Tu as vu le grain, sur le bouton ?
-enfant-f|Il était sur la vitre, à la cuisine.</t>
+papa|Tu reconnais le grain, du verre ?
+enfant-f|Il a glissé du verre, tout petit.</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
@@ -17406,7 +17406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A19"/>
+  <dimension ref="A1:A20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -17540,6 +17540,13 @@
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
